--- a/templates/finance/wacc-calculator.xlsx
+++ b/templates/finance/wacc-calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sheetxl\private\docsite\static\examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sheetxl\workbook-templates\templates\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D513E0-C7E8-49A2-A0ED-745415C8D194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
+    <workbookView xWindow="-23595" yWindow="2115" windowWidth="22695" windowHeight="12375" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
   </bookViews>
   <sheets>
     <sheet name="WACC" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="CLV" sheetId="4" r:id="rId3"/>
     <sheet name="VC Valuation" sheetId="5" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">WACC!$B$2:$U$34</definedName>
   </definedNames>
@@ -2185,15 +2182,7 @@
           <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>[1]clv!$B$24</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>CLV</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>CLV</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -2208,31 +2197,28 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:val>
-            <c:numRef>
-              <c:f>[1]clv!$D$24:$I$24</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>-300</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>166.66666666666669</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>222.22222222222223</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>208.33333333333337</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>162.03703703703707</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>101.27314814814815</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="6"/>
+              <c:pt idx="0">
+                <c:v>-300</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>166.66666666666669</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>222.22222222222223</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>208.33333333333337</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>162.03703703703707</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>101.27314814814815</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2244,15 +2230,7 @@
           <c:idx val="2"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>[1]clv!$B$25</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Cumulative CLV</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Cumulative CLV</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -2265,31 +2243,28 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:val>
-            <c:numRef>
-              <c:f>[1]clv!$D$25:$I$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>-300</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-133.33333333333331</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>88.888888888888914</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>297.22222222222229</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>459.25925925925935</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>560.5324074074075</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="6"/>
+              <c:pt idx="0">
+                <c:v>-300</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>-133.33333333333331</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>88.888888888888914</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>297.22222222222229</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>459.25925925925935</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>560.5324074074075</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2316,15 +2291,7 @@
           <c:idx val="3"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>[1]clv!$B$26</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>CLV/CAC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>CLV/CAC</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -2407,31 +2374,28 @@
             </c:extLst>
           </c:dLbls>
           <c:val>
-            <c:numRef>
-              <c:f>[1]clv!$D$26:$I$26</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.44444444444444436</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.29629629629629639</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.99074074074074092</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.5308641975308646</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.8684413580246917</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="6"/>
+              <c:pt idx="0">
+                <c:v>-1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>-0.44444444444444436</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>0.29629629629629639</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>0.99074074074074092</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1.5308641975308646</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1.8684413580246917</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
@@ -3333,92 +3297,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="clv"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>CLV</v>
-          </cell>
-          <cell r="D24">
-            <v>-300</v>
-          </cell>
-          <cell r="E24">
-            <v>166.66666666666669</v>
-          </cell>
-          <cell r="F24">
-            <v>222.22222222222223</v>
-          </cell>
-          <cell r="G24">
-            <v>208.33333333333337</v>
-          </cell>
-          <cell r="H24">
-            <v>162.03703703703707</v>
-          </cell>
-          <cell r="I24">
-            <v>101.27314814814815</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>Cumulative CLV</v>
-          </cell>
-          <cell r="D25">
-            <v>-300</v>
-          </cell>
-          <cell r="E25">
-            <v>-133.33333333333331</v>
-          </cell>
-          <cell r="F25">
-            <v>88.888888888888914</v>
-          </cell>
-          <cell r="G25">
-            <v>297.22222222222229</v>
-          </cell>
-          <cell r="H25">
-            <v>459.25925925925935</v>
-          </cell>
-          <cell r="I25">
-            <v>560.5324074074075</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>CLV/CAC</v>
-          </cell>
-          <cell r="D26">
-            <v>-1</v>
-          </cell>
-          <cell r="E26">
-            <v>-0.44444444444444436</v>
-          </cell>
-          <cell r="F26">
-            <v>0.29629629629629639</v>
-          </cell>
-          <cell r="G26">
-            <v>0.99074074074074092</v>
-          </cell>
-          <cell r="H26">
-            <v>1.5308641975308646</v>
-          </cell>
-          <cell r="I26">
-            <v>1.8684413580246917</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>

--- a/templates/finance/wacc-calculator.xlsx
+++ b/templates/finance/wacc-calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sheetxl\workbook-templates\templates\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D513E0-C7E8-49A2-A0ED-745415C8D194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DFA176-C64C-4BF9-9D7B-9242E6B19797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23595" yWindow="2115" windowWidth="22695" windowHeight="12375" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
+    <workbookView xWindow="3330" yWindow="210" windowWidth="22695" windowHeight="12375" activeTab="3" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
   </bookViews>
   <sheets>
     <sheet name="WACC" sheetId="1" r:id="rId1"/>
@@ -283,9 +283,6 @@
     <t>Powered by</t>
   </si>
   <si>
-    <t>www.efinancialmodels.com</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Consumer Liftime Value &amp; Consumer Acquisition Cost Calculator</t>
   </si>
   <si>
@@ -482,6 +479,9 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>https://www.efinancialmodels.com</t>
   </si>
 </sst>
 </file>
@@ -509,7 +509,7 @@
     <numFmt numFmtId="179" formatCode="_(* #,##0.0\x_);_(* \(#,##0.0\x\);_(* &quot;-&quot;?_);_(@_)"/>
     <numFmt numFmtId="180" formatCode="_(* #,##0.0%_);_(* \(#,##0.0%\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="70">
+  <fonts count="69">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -774,13 +774,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color indexed="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1655,7 +1648,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1893,9 +1886,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="5" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1"/>
@@ -1917,11 +1907,11 @@
     <xf numFmtId="165" fontId="28" fillId="59" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="44" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="43" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="5" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="5" applyBorder="1"/>
@@ -1943,37 +1933,37 @@
     <xf numFmtId="165" fontId="29" fillId="60" borderId="15" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="29" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="5" applyBorder="1"/>
-    <xf numFmtId="172" fontId="46" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="45" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="5" applyBorder="1"/>
-    <xf numFmtId="173" fontId="47" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="62" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="48" fillId="62" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="50" fillId="61" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="51" fillId="61" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="62" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="49" fillId="61" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="173" fontId="50" fillId="61" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="47" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="47" fillId="0" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="47" fillId="0" borderId="18" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="18" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="47" fillId="0" borderId="19" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="19" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="47" fillId="0" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="37" fontId="54" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="37" fontId="53" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1982,98 +1972,98 @@
     <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="37" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="37" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="174" fontId="10" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="55" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="54" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="11"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="11"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="58" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="58" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="65" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="64" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="65" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="64" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="63" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="53" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="52" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="60" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="61" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="65" fillId="59" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="64" fillId="59" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="65" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="64" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="60" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="60" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="60" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="60" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="60" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="61" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="60" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="60" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="60" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="60" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="64" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="63" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="19" fillId="60" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="59" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="19" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="60" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="60" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="60" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="19" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2088,7 +2078,7 @@
     </xf>
     <xf numFmtId="3" fontId="19" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="11" applyFont="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="11" applyFont="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2105,22 +2095,25 @@
     <xf numFmtId="37" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="49" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="48" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="49" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="48" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="49" fillId="0" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="48" fillId="0" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="59" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="59" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="59" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="59" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="59" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="59" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3886,14 +3879,14 @@
       <c r="B14" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="286" t="s">
+      <c r="C14" s="285" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="286"/>
-      <c r="E14" s="286"/>
-      <c r="F14" s="286"/>
-      <c r="G14" s="286"/>
-      <c r="H14" s="286"/>
+      <c r="D14" s="285"/>
+      <c r="E14" s="285"/>
+      <c r="F14" s="285"/>
+      <c r="G14" s="285"/>
+      <c r="H14" s="285"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -3927,7 +3920,7 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="2:21">
-      <c r="B16" s="285" t="s">
+      <c r="B16" s="284" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="58">
@@ -3962,7 +3955,7 @@
       <c r="U16"/>
     </row>
     <row r="17" spans="2:21">
-      <c r="B17" s="285"/>
+      <c r="B17" s="284"/>
       <c r="C17" s="58">
         <f>+C16+5%</f>
         <v>0.1</v>
@@ -4008,7 +4001,7 @@
       <c r="U17"/>
     </row>
     <row r="18" spans="2:21">
-      <c r="B18" s="285"/>
+      <c r="B18" s="284"/>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C26" si="1">+C17+10%</f>
         <v>0.2</v>
@@ -4056,7 +4049,7 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21">
-      <c r="B19" s="285"/>
+      <c r="B19" s="284"/>
       <c r="C19" s="58">
         <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
@@ -4104,7 +4097,7 @@
       <c r="U19"/>
     </row>
     <row r="20" spans="2:21">
-      <c r="B20" s="285"/>
+      <c r="B20" s="284"/>
       <c r="C20" s="58">
         <f t="shared" si="1"/>
         <v>0.4</v>
@@ -4152,7 +4145,7 @@
       <c r="U20"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="B21" s="285"/>
+      <c r="B21" s="284"/>
       <c r="C21" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
@@ -4200,7 +4193,7 @@
       <c r="U21"/>
     </row>
     <row r="22" spans="2:21">
-      <c r="B22" s="285"/>
+      <c r="B22" s="284"/>
       <c r="C22" s="58">
         <f t="shared" si="1"/>
         <v>0.6</v>
@@ -4248,7 +4241,7 @@
       <c r="U22"/>
     </row>
     <row r="23" spans="2:21">
-      <c r="B23" s="285"/>
+      <c r="B23" s="284"/>
       <c r="C23" s="58">
         <f t="shared" si="1"/>
         <v>0.7</v>
@@ -4294,7 +4287,7 @@
       <c r="U23"/>
     </row>
     <row r="24" spans="2:21">
-      <c r="B24" s="285"/>
+      <c r="B24" s="284"/>
       <c r="C24" s="58">
         <f t="shared" si="1"/>
         <v>0.79999999999999993</v>
@@ -4319,7 +4312,7 @@
       <c r="U24"/>
     </row>
     <row r="25" spans="2:21">
-      <c r="B25" s="285"/>
+      <c r="B25" s="284"/>
       <c r="C25" s="58">
         <f t="shared" si="1"/>
         <v>0.89999999999999991</v>
@@ -4351,7 +4344,7 @@
       <c r="U25"/>
     </row>
     <row r="26" spans="2:21">
-      <c r="B26" s="285"/>
+      <c r="B26" s="284"/>
       <c r="C26" s="58">
         <f t="shared" si="1"/>
         <v>0.99999999999999989</v>
@@ -4568,7 +4561,7 @@
     </row>
     <row r="2" spans="2:32" ht="26.25">
       <c r="B2" s="112"/>
-      <c r="C2" s="179" t="s">
+      <c r="C2" s="178" t="s">
         <v>47</v>
       </c>
       <c r="D2" s="112"/>
@@ -4596,12 +4589,12 @@
       <c r="Z2" s="112"/>
       <c r="AA2" s="112"/>
       <c r="AB2" s="112"/>
-      <c r="AC2" s="199" t="s">
+      <c r="AC2" s="198" t="s">
         <v>48</v>
       </c>
       <c r="AD2" s="112"/>
       <c r="AE2" s="112"/>
-      <c r="AF2" s="166" t="e">
+      <c r="AF2" s="165" t="e">
         <v>#REF!</v>
       </c>
     </row>
@@ -4688,16 +4681,16 @@
       <c r="M5" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="N5" s="190"/>
-      <c r="O5" s="191" t="s">
+      <c r="N5" s="189"/>
+      <c r="O5" s="190" t="s">
         <v>51</v>
       </c>
       <c r="P5" s="114"/>
-      <c r="Q5" s="191" t="s">
+      <c r="Q5" s="190" t="s">
         <v>52</v>
       </c>
       <c r="R5" s="114"/>
-      <c r="S5" s="190"/>
+      <c r="S5" s="189"/>
       <c r="T5" s="114"/>
       <c r="U5" s="114"/>
       <c r="V5" s="114"/>
@@ -4710,16 +4703,16 @@
       <c r="AC5" s="114"/>
       <c r="AD5" s="114"/>
       <c r="AE5" s="116"/>
-      <c r="AF5" s="163"/>
+      <c r="AF5" s="162"/>
     </row>
     <row r="6" spans="2:32">
-      <c r="B6" s="151"/>
-      <c r="C6" s="152"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="151"/>
       <c r="D6" s="130"/>
       <c r="E6" s="130"/>
       <c r="F6" s="130"/>
       <c r="G6" s="130"/>
-      <c r="H6" s="153"/>
+      <c r="H6" s="152"/>
       <c r="I6" s="116"/>
       <c r="J6" s="116"/>
       <c r="K6" s="116"/>
@@ -4741,12 +4734,12 @@
       <c r="AA6" s="116"/>
       <c r="AB6" s="116"/>
       <c r="AC6" s="116"/>
-      <c r="AD6" s="155"/>
+      <c r="AD6" s="154"/>
       <c r="AE6" s="116"/>
-      <c r="AF6" s="163"/>
+      <c r="AF6" s="162"/>
     </row>
     <row r="7" spans="2:32" ht="60">
-      <c r="B7" s="154"/>
+      <c r="B7" s="153"/>
       <c r="C7" s="145" t="s">
         <v>53</v>
       </c>
@@ -4755,11 +4748,11 @@
       <c r="F7" s="116"/>
       <c r="G7" s="116"/>
       <c r="H7" s="115"/>
-      <c r="I7" s="192" t="s">
+      <c r="I7" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="192"/>
-      <c r="K7" s="193"/>
+      <c r="J7" s="191"/>
+      <c r="K7" s="192"/>
       <c r="L7" s="116"/>
       <c r="M7" s="116"/>
       <c r="N7" s="116"/>
@@ -4778,12 +4771,12 @@
       <c r="AA7" s="116"/>
       <c r="AB7" s="116"/>
       <c r="AC7" s="116"/>
-      <c r="AD7" s="155"/>
+      <c r="AD7" s="154"/>
       <c r="AE7" s="116"/>
-      <c r="AF7" s="163"/>
+      <c r="AF7" s="162"/>
     </row>
     <row r="8" spans="2:32" ht="61.5">
-      <c r="B8" s="154"/>
+      <c r="B8" s="153"/>
       <c r="C8" s="116" t="s">
         <v>55</v>
       </c>
@@ -4794,9 +4787,9 @@
       <c r="F8" s="116"/>
       <c r="G8" s="116"/>
       <c r="H8" s="115"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="189"/>
-      <c r="K8" s="195"/>
+      <c r="I8" s="193"/>
+      <c r="J8" s="188"/>
+      <c r="K8" s="194"/>
       <c r="L8" s="116"/>
       <c r="M8" s="116"/>
       <c r="N8" s="116"/>
@@ -4815,12 +4808,12 @@
       <c r="AA8" s="116"/>
       <c r="AB8" s="116"/>
       <c r="AC8" s="116"/>
-      <c r="AD8" s="155"/>
+      <c r="AD8" s="154"/>
       <c r="AE8" s="116"/>
-      <c r="AF8" s="163"/>
+      <c r="AF8" s="162"/>
     </row>
     <row r="9" spans="2:32">
-      <c r="B9" s="154"/>
+      <c r="B9" s="153"/>
       <c r="C9" s="146" t="s">
         <v>49</v>
       </c>
@@ -4831,11 +4824,11 @@
       <c r="F9" s="116"/>
       <c r="G9" s="116"/>
       <c r="H9" s="115"/>
-      <c r="I9" s="287">
+      <c r="I9" s="286">
         <v>4.2087912087912089</v>
       </c>
-      <c r="J9" s="288"/>
-      <c r="K9" s="289"/>
+      <c r="J9" s="287"/>
+      <c r="K9" s="288"/>
       <c r="L9" s="116"/>
       <c r="M9" s="116"/>
       <c r="N9" s="116"/>
@@ -4854,12 +4847,12 @@
       <c r="AA9" s="116"/>
       <c r="AB9" s="116"/>
       <c r="AC9" s="116"/>
-      <c r="AD9" s="155"/>
+      <c r="AD9" s="154"/>
       <c r="AE9" s="116"/>
-      <c r="AF9" s="163"/>
+      <c r="AF9" s="162"/>
     </row>
     <row r="10" spans="2:32">
-      <c r="B10" s="154"/>
+      <c r="B10" s="153"/>
       <c r="C10" s="147" t="s">
         <v>58</v>
       </c>
@@ -4870,9 +4863,9 @@
       <c r="F10" s="116"/>
       <c r="G10" s="116"/>
       <c r="H10" s="115"/>
-      <c r="I10" s="287"/>
-      <c r="J10" s="288"/>
-      <c r="K10" s="289"/>
+      <c r="I10" s="286"/>
+      <c r="J10" s="287"/>
+      <c r="K10" s="288"/>
       <c r="L10" s="116"/>
       <c r="M10" s="116"/>
       <c r="N10" s="116"/>
@@ -4891,21 +4884,21 @@
       <c r="AA10" s="116"/>
       <c r="AB10" s="116"/>
       <c r="AC10" s="116"/>
-      <c r="AD10" s="155"/>
+      <c r="AD10" s="154"/>
       <c r="AE10" s="116"/>
-      <c r="AF10" s="163"/>
+      <c r="AF10" s="162"/>
     </row>
     <row r="11" spans="2:32">
-      <c r="B11" s="154"/>
+      <c r="B11" s="153"/>
       <c r="C11" s="116"/>
       <c r="D11" s="116"/>
       <c r="E11" s="116"/>
       <c r="F11" s="116"/>
       <c r="G11" s="116"/>
       <c r="H11" s="115"/>
-      <c r="I11" s="287"/>
-      <c r="J11" s="288"/>
-      <c r="K11" s="289"/>
+      <c r="I11" s="286"/>
+      <c r="J11" s="287"/>
+      <c r="K11" s="288"/>
       <c r="L11" s="116"/>
       <c r="M11" s="116"/>
       <c r="N11" s="116"/>
@@ -4924,21 +4917,21 @@
       <c r="AA11" s="116"/>
       <c r="AB11" s="116"/>
       <c r="AC11" s="116"/>
-      <c r="AD11" s="155"/>
+      <c r="AD11" s="154"/>
       <c r="AE11" s="116"/>
-      <c r="AF11" s="163"/>
+      <c r="AF11" s="162"/>
     </row>
     <row r="12" spans="2:32">
-      <c r="B12" s="154"/>
+      <c r="B12" s="153"/>
       <c r="C12" s="116"/>
       <c r="D12" s="116"/>
       <c r="E12" s="116"/>
       <c r="F12" s="116"/>
       <c r="G12" s="116"/>
       <c r="H12" s="115"/>
-      <c r="I12" s="287"/>
-      <c r="J12" s="288"/>
-      <c r="K12" s="289"/>
+      <c r="I12" s="286"/>
+      <c r="J12" s="287"/>
+      <c r="K12" s="288"/>
       <c r="L12" s="116"/>
       <c r="M12" s="116"/>
       <c r="N12" s="116"/>
@@ -4957,12 +4950,12 @@
       <c r="AA12" s="116"/>
       <c r="AB12" s="116"/>
       <c r="AC12" s="116"/>
-      <c r="AD12" s="155"/>
+      <c r="AD12" s="154"/>
       <c r="AE12" s="116"/>
-      <c r="AF12" s="163"/>
+      <c r="AF12" s="162"/>
     </row>
     <row r="13" spans="2:32">
-      <c r="B13" s="154"/>
+      <c r="B13" s="153"/>
       <c r="C13" s="145" t="s">
         <v>60</v>
       </c>
@@ -4971,9 +4964,9 @@
       <c r="F13" s="116"/>
       <c r="G13" s="116"/>
       <c r="H13" s="115"/>
-      <c r="I13" s="287"/>
-      <c r="J13" s="288"/>
-      <c r="K13" s="289"/>
+      <c r="I13" s="286"/>
+      <c r="J13" s="287"/>
+      <c r="K13" s="288"/>
       <c r="L13" s="116"/>
       <c r="M13" s="116"/>
       <c r="N13" s="116"/>
@@ -4992,12 +4985,12 @@
       <c r="AA13" s="116"/>
       <c r="AB13" s="116"/>
       <c r="AC13" s="116"/>
-      <c r="AD13" s="155"/>
+      <c r="AD13" s="154"/>
       <c r="AE13" s="116"/>
-      <c r="AF13" s="163"/>
+      <c r="AF13" s="162"/>
     </row>
     <row r="14" spans="2:32">
-      <c r="B14" s="154"/>
+      <c r="B14" s="153"/>
       <c r="C14" s="116" t="s">
         <v>61</v>
       </c>
@@ -5008,9 +5001,9 @@
       <c r="F14" s="116"/>
       <c r="G14" s="116"/>
       <c r="H14" s="115"/>
-      <c r="I14" s="287"/>
-      <c r="J14" s="288"/>
-      <c r="K14" s="289"/>
+      <c r="I14" s="286"/>
+      <c r="J14" s="287"/>
+      <c r="K14" s="288"/>
       <c r="L14" s="116"/>
       <c r="M14" s="116"/>
       <c r="N14" s="116"/>
@@ -5029,21 +5022,21 @@
       <c r="AA14" s="116"/>
       <c r="AB14" s="116"/>
       <c r="AC14" s="116"/>
-      <c r="AD14" s="155"/>
+      <c r="AD14" s="154"/>
       <c r="AE14" s="116"/>
-      <c r="AF14" s="163"/>
+      <c r="AF14" s="162"/>
     </row>
     <row r="15" spans="2:32">
-      <c r="B15" s="154"/>
+      <c r="B15" s="153"/>
       <c r="C15" s="116"/>
       <c r="D15" s="116"/>
       <c r="E15" s="116"/>
       <c r="F15" s="116"/>
       <c r="G15" s="116"/>
       <c r="H15" s="115"/>
-      <c r="I15" s="287"/>
-      <c r="J15" s="288"/>
-      <c r="K15" s="289"/>
+      <c r="I15" s="286"/>
+      <c r="J15" s="287"/>
+      <c r="K15" s="288"/>
       <c r="L15" s="116"/>
       <c r="M15" s="116"/>
       <c r="N15" s="116"/>
@@ -5062,14 +5055,14 @@
       <c r="AA15" s="116"/>
       <c r="AB15" s="116"/>
       <c r="AC15" s="116"/>
-      <c r="AD15" s="155"/>
+      <c r="AD15" s="154"/>
       <c r="AE15" s="116"/>
-      <c r="AF15" s="167" t="e">
+      <c r="AF15" s="166" t="e">
         <v>#REF!</v>
       </c>
     </row>
     <row r="16" spans="2:32">
-      <c r="B16" s="154"/>
+      <c r="B16" s="153"/>
       <c r="C16" s="145" t="s">
         <v>63</v>
       </c>
@@ -5078,9 +5071,9 @@
       <c r="F16" s="116"/>
       <c r="G16" s="120"/>
       <c r="H16" s="115"/>
-      <c r="I16" s="287"/>
-      <c r="J16" s="288"/>
-      <c r="K16" s="289"/>
+      <c r="I16" s="286"/>
+      <c r="J16" s="287"/>
+      <c r="K16" s="288"/>
       <c r="L16" s="116"/>
       <c r="M16" s="116"/>
       <c r="N16" s="116"/>
@@ -5099,12 +5092,12 @@
       <c r="AA16" s="116"/>
       <c r="AB16" s="116"/>
       <c r="AC16" s="116"/>
-      <c r="AD16" s="155"/>
+      <c r="AD16" s="154"/>
       <c r="AE16" s="116"/>
-      <c r="AF16" s="163"/>
+      <c r="AF16" s="162"/>
     </row>
     <row r="17" spans="2:32">
-      <c r="B17" s="154"/>
+      <c r="B17" s="153"/>
       <c r="C17" s="121" t="s">
         <v>64</v>
       </c>
@@ -5117,9 +5110,9 @@
         <v>100000</v>
       </c>
       <c r="H17" s="115"/>
-      <c r="I17" s="287"/>
-      <c r="J17" s="288"/>
-      <c r="K17" s="289"/>
+      <c r="I17" s="286"/>
+      <c r="J17" s="287"/>
+      <c r="K17" s="288"/>
       <c r="L17" s="116"/>
       <c r="M17" s="116"/>
       <c r="N17" s="116"/>
@@ -5138,12 +5131,12 @@
       <c r="AA17" s="116"/>
       <c r="AB17" s="116"/>
       <c r="AC17" s="116"/>
-      <c r="AD17" s="155"/>
+      <c r="AD17" s="154"/>
       <c r="AE17" s="116"/>
-      <c r="AF17" s="163"/>
+      <c r="AF17" s="162"/>
     </row>
     <row r="18" spans="2:32">
-      <c r="B18" s="154"/>
+      <c r="B18" s="153"/>
       <c r="C18" s="121" t="s">
         <v>65</v>
       </c>
@@ -5156,9 +5149,9 @@
         <v>20000</v>
       </c>
       <c r="H18" s="115"/>
-      <c r="I18" s="287"/>
-      <c r="J18" s="288"/>
-      <c r="K18" s="289"/>
+      <c r="I18" s="286"/>
+      <c r="J18" s="287"/>
+      <c r="K18" s="288"/>
       <c r="L18" s="116"/>
       <c r="M18" s="116"/>
       <c r="N18" s="116"/>
@@ -5177,12 +5170,12 @@
       <c r="AA18" s="116"/>
       <c r="AB18" s="116"/>
       <c r="AC18" s="116"/>
-      <c r="AD18" s="155"/>
+      <c r="AD18" s="154"/>
       <c r="AE18" s="116"/>
-      <c r="AF18" s="163"/>
+      <c r="AF18" s="162"/>
     </row>
     <row r="19" spans="2:32">
-      <c r="B19" s="154"/>
+      <c r="B19" s="153"/>
       <c r="C19" s="121"/>
       <c r="D19" s="116"/>
       <c r="E19" s="116" t="s">
@@ -5193,9 +5186,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="115"/>
-      <c r="I19" s="287"/>
-      <c r="J19" s="288"/>
-      <c r="K19" s="289"/>
+      <c r="I19" s="286"/>
+      <c r="J19" s="287"/>
+      <c r="K19" s="288"/>
       <c r="L19" s="116"/>
       <c r="M19" s="116"/>
       <c r="N19" s="116"/>
@@ -5214,12 +5207,12 @@
       <c r="AA19" s="116"/>
       <c r="AB19" s="116"/>
       <c r="AC19" s="116"/>
-      <c r="AD19" s="155"/>
+      <c r="AD19" s="154"/>
       <c r="AE19" s="116"/>
-      <c r="AF19" s="163"/>
+      <c r="AF19" s="162"/>
     </row>
     <row r="20" spans="2:32">
-      <c r="B20" s="154"/>
+      <c r="B20" s="153"/>
       <c r="C20" s="121"/>
       <c r="D20" s="116"/>
       <c r="E20" s="116" t="s">
@@ -5230,9 +5223,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="115"/>
-      <c r="I20" s="287"/>
-      <c r="J20" s="288"/>
-      <c r="K20" s="289"/>
+      <c r="I20" s="286"/>
+      <c r="J20" s="287"/>
+      <c r="K20" s="288"/>
       <c r="L20" s="116"/>
       <c r="M20" s="116"/>
       <c r="N20" s="116"/>
@@ -5251,21 +5244,21 @@
       <c r="AA20" s="116"/>
       <c r="AB20" s="116"/>
       <c r="AC20" s="116"/>
-      <c r="AD20" s="155"/>
+      <c r="AD20" s="154"/>
       <c r="AE20" s="116"/>
-      <c r="AF20" s="163"/>
+      <c r="AF20" s="162"/>
     </row>
     <row r="21" spans="2:32" ht="62.25" thickBot="1">
-      <c r="B21" s="154"/>
+      <c r="B21" s="153"/>
       <c r="C21" s="116"/>
       <c r="D21" s="116"/>
       <c r="E21" s="116"/>
       <c r="F21" s="116"/>
       <c r="G21" s="120"/>
       <c r="H21" s="116"/>
-      <c r="I21" s="196"/>
-      <c r="J21" s="197"/>
-      <c r="K21" s="198"/>
+      <c r="I21" s="195"/>
+      <c r="J21" s="196"/>
+      <c r="K21" s="197"/>
       <c r="L21" s="116"/>
       <c r="M21" s="116"/>
       <c r="N21" s="116"/>
@@ -5284,12 +5277,12 @@
       <c r="AA21" s="116"/>
       <c r="AB21" s="116"/>
       <c r="AC21" s="116"/>
-      <c r="AD21" s="155"/>
+      <c r="AD21" s="154"/>
       <c r="AE21" s="116"/>
-      <c r="AF21" s="163"/>
+      <c r="AF21" s="162"/>
     </row>
     <row r="22" spans="2:32" ht="61.5">
-      <c r="B22" s="154"/>
+      <c r="B22" s="153"/>
       <c r="C22" s="123" t="s">
         <v>66</v>
       </c>
@@ -5303,8 +5296,8 @@
       </c>
       <c r="H22" s="125"/>
       <c r="I22" s="116"/>
-      <c r="J22" s="189"/>
-      <c r="K22" s="189"/>
+      <c r="J22" s="188"/>
+      <c r="K22" s="188"/>
       <c r="L22" s="116"/>
       <c r="M22" s="116"/>
       <c r="N22" s="116"/>
@@ -5323,42 +5316,42 @@
       <c r="AA22" s="116"/>
       <c r="AB22" s="116"/>
       <c r="AC22" s="116"/>
-      <c r="AD22" s="155"/>
+      <c r="AD22" s="154"/>
       <c r="AE22" s="116"/>
-      <c r="AF22" s="163"/>
+      <c r="AF22" s="162"/>
     </row>
     <row r="23" spans="2:32">
-      <c r="B23" s="156"/>
-      <c r="C23" s="157"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
-      <c r="F23" s="157"/>
-      <c r="G23" s="158"/>
-      <c r="H23" s="159"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="157"/>
-      <c r="K23" s="157"/>
-      <c r="L23" s="157"/>
-      <c r="M23" s="157"/>
-      <c r="N23" s="157"/>
-      <c r="O23" s="157"/>
-      <c r="P23" s="157"/>
-      <c r="Q23" s="157"/>
-      <c r="R23" s="157"/>
-      <c r="S23" s="157"/>
-      <c r="T23" s="157"/>
-      <c r="U23" s="157"/>
-      <c r="V23" s="157"/>
-      <c r="W23" s="157"/>
+      <c r="B23" s="155"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="157"/>
+      <c r="H23" s="158"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="156"/>
+      <c r="K23" s="156"/>
+      <c r="L23" s="156"/>
+      <c r="M23" s="156"/>
+      <c r="N23" s="156"/>
+      <c r="O23" s="156"/>
+      <c r="P23" s="156"/>
+      <c r="Q23" s="156"/>
+      <c r="R23" s="156"/>
+      <c r="S23" s="156"/>
+      <c r="T23" s="156"/>
+      <c r="U23" s="156"/>
+      <c r="V23" s="156"/>
+      <c r="W23" s="156"/>
       <c r="X23" s="116"/>
       <c r="Y23" s="116"/>
       <c r="Z23" s="116"/>
       <c r="AA23" s="116"/>
-      <c r="AB23" s="157"/>
-      <c r="AC23" s="157"/>
-      <c r="AD23" s="160"/>
+      <c r="AB23" s="156"/>
+      <c r="AC23" s="156"/>
+      <c r="AD23" s="159"/>
       <c r="AE23" s="116"/>
-      <c r="AF23" s="163"/>
+      <c r="AF23" s="162"/>
     </row>
     <row r="24" spans="2:32">
       <c r="B24" s="116"/>
@@ -5391,7 +5384,7 @@
       <c r="AC24" s="116"/>
       <c r="AD24" s="116"/>
       <c r="AE24" s="116"/>
-      <c r="AF24" s="163"/>
+      <c r="AF24" s="162"/>
     </row>
     <row r="25" spans="2:32">
       <c r="B25" s="114"/>
@@ -5470,10 +5463,10 @@
       </c>
       <c r="AD25" s="126"/>
       <c r="AE25" s="116"/>
-      <c r="AF25" s="163"/>
+      <c r="AF25" s="162"/>
     </row>
     <row r="26" spans="2:32">
-      <c r="B26" s="154"/>
+      <c r="B26" s="153"/>
       <c r="C26" s="116"/>
       <c r="D26" s="116"/>
       <c r="E26" s="116"/>
@@ -5500,13 +5493,13 @@
       <c r="Z26" s="116"/>
       <c r="AA26" s="116"/>
       <c r="AB26" s="116"/>
-      <c r="AC26" s="181"/>
-      <c r="AD26" s="155"/>
+      <c r="AC26" s="180"/>
+      <c r="AD26" s="154"/>
       <c r="AE26" s="116"/>
-      <c r="AF26" s="163"/>
+      <c r="AF26" s="162"/>
     </row>
     <row r="27" spans="2:32">
-      <c r="B27" s="154"/>
+      <c r="B27" s="153"/>
       <c r="C27" s="145" t="s">
         <v>69</v>
       </c>
@@ -5535,13 +5528,13 @@
       <c r="Z27" s="116"/>
       <c r="AA27" s="116"/>
       <c r="AB27" s="116"/>
-      <c r="AC27" s="181"/>
-      <c r="AD27" s="155"/>
+      <c r="AC27" s="180"/>
+      <c r="AD27" s="154"/>
       <c r="AE27" s="116"/>
-      <c r="AF27" s="163"/>
+      <c r="AF27" s="162"/>
     </row>
     <row r="28" spans="2:32">
-      <c r="B28" s="154"/>
+      <c r="B28" s="153"/>
       <c r="C28" s="127" t="s">
         <v>70</v>
       </c>
@@ -5592,15 +5585,15 @@
       <c r="Z28" s="129"/>
       <c r="AA28" s="129"/>
       <c r="AB28" s="116"/>
-      <c r="AC28" s="182">
+      <c r="AC28" s="181">
         <v>590000</v>
       </c>
-      <c r="AD28" s="155"/>
+      <c r="AD28" s="154"/>
       <c r="AE28" s="116"/>
-      <c r="AF28" s="163"/>
+      <c r="AF28" s="162"/>
     </row>
     <row r="29" spans="2:32">
-      <c r="B29" s="154"/>
+      <c r="B29" s="153"/>
       <c r="C29" s="127" t="s">
         <v>71</v>
       </c>
@@ -5631,15 +5624,15 @@
       <c r="Z29" s="129"/>
       <c r="AA29" s="129"/>
       <c r="AB29" s="116"/>
-      <c r="AC29" s="182">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="155"/>
+      <c r="AC29" s="181">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="154"/>
       <c r="AE29" s="116"/>
-      <c r="AF29" s="163"/>
+      <c r="AF29" s="162"/>
     </row>
     <row r="30" spans="2:32">
-      <c r="B30" s="154"/>
+      <c r="B30" s="153"/>
       <c r="C30" s="119"/>
       <c r="D30" s="116"/>
       <c r="E30" s="116"/>
@@ -5666,13 +5659,13 @@
       <c r="Z30" s="128"/>
       <c r="AA30" s="128"/>
       <c r="AB30" s="116"/>
-      <c r="AC30" s="181"/>
-      <c r="AD30" s="155"/>
+      <c r="AC30" s="180"/>
+      <c r="AD30" s="154"/>
       <c r="AE30" s="116"/>
-      <c r="AF30" s="163"/>
+      <c r="AF30" s="162"/>
     </row>
     <row r="31" spans="2:32">
-      <c r="B31" s="154"/>
+      <c r="B31" s="153"/>
       <c r="C31" s="130" t="s">
         <v>69</v>
       </c>
@@ -5743,15 +5736,15 @@
         <v>0</v>
       </c>
       <c r="AB31" s="116"/>
-      <c r="AC31" s="183">
+      <c r="AC31" s="182">
         <v>590000</v>
       </c>
-      <c r="AD31" s="155"/>
+      <c r="AD31" s="154"/>
       <c r="AE31" s="116"/>
-      <c r="AF31" s="163"/>
+      <c r="AF31" s="162"/>
     </row>
     <row r="32" spans="2:32">
-      <c r="B32" s="154"/>
+      <c r="B32" s="153"/>
       <c r="C32" s="119"/>
       <c r="D32" s="116"/>
       <c r="E32" s="116"/>
@@ -5778,13 +5771,13 @@
       <c r="Z32" s="128"/>
       <c r="AA32" s="128"/>
       <c r="AB32" s="116"/>
-      <c r="AC32" s="181"/>
-      <c r="AD32" s="155"/>
+      <c r="AC32" s="180"/>
+      <c r="AD32" s="154"/>
       <c r="AE32" s="116"/>
-      <c r="AF32" s="163"/>
+      <c r="AF32" s="162"/>
     </row>
     <row r="33" spans="2:32">
-      <c r="B33" s="154"/>
+      <c r="B33" s="153"/>
       <c r="C33" s="145" t="s">
         <v>72</v>
       </c>
@@ -5813,13 +5806,13 @@
       <c r="Z33" s="128"/>
       <c r="AA33" s="128"/>
       <c r="AB33" s="116"/>
-      <c r="AC33" s="181"/>
-      <c r="AD33" s="155"/>
+      <c r="AC33" s="180"/>
+      <c r="AD33" s="154"/>
       <c r="AE33" s="116"/>
-      <c r="AF33" s="163"/>
+      <c r="AF33" s="162"/>
     </row>
     <row r="34" spans="2:32">
-      <c r="B34" s="154"/>
+      <c r="B34" s="153"/>
       <c r="C34" s="127" t="s">
         <v>73</v>
       </c>
@@ -5890,15 +5883,15 @@
         <v>0</v>
       </c>
       <c r="AB34" s="116"/>
-      <c r="AC34" s="182">
+      <c r="AC34" s="181">
         <v>177000</v>
       </c>
-      <c r="AD34" s="155"/>
+      <c r="AD34" s="154"/>
       <c r="AE34" s="116"/>
-      <c r="AF34" s="163"/>
+      <c r="AF34" s="162"/>
     </row>
     <row r="35" spans="2:32">
-      <c r="B35" s="154"/>
+      <c r="B35" s="153"/>
       <c r="C35" s="127" t="s">
         <v>74</v>
       </c>
@@ -5969,15 +5962,15 @@
         <v>0</v>
       </c>
       <c r="AB35" s="116"/>
-      <c r="AC35" s="182">
+      <c r="AC35" s="181">
         <v>29500</v>
       </c>
-      <c r="AD35" s="155"/>
+      <c r="AD35" s="154"/>
       <c r="AE35" s="116"/>
-      <c r="AF35" s="163"/>
+      <c r="AF35" s="162"/>
     </row>
     <row r="36" spans="2:32">
-      <c r="B36" s="154"/>
+      <c r="B36" s="153"/>
       <c r="C36" s="127" t="s">
         <v>71</v>
       </c>
@@ -6008,15 +6001,15 @@
       <c r="Z36" s="129"/>
       <c r="AA36" s="129"/>
       <c r="AB36" s="116"/>
-      <c r="AC36" s="182">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="155"/>
+      <c r="AC36" s="181">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="154"/>
       <c r="AE36" s="116"/>
-      <c r="AF36" s="163"/>
+      <c r="AF36" s="162"/>
     </row>
     <row r="37" spans="2:32">
-      <c r="B37" s="154"/>
+      <c r="B37" s="153"/>
       <c r="C37" s="127" t="s">
         <v>71</v>
       </c>
@@ -6047,15 +6040,15 @@
       <c r="Z37" s="129"/>
       <c r="AA37" s="129"/>
       <c r="AB37" s="116"/>
-      <c r="AC37" s="182">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="155"/>
+      <c r="AC37" s="181">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="154"/>
       <c r="AE37" s="116"/>
-      <c r="AF37" s="163"/>
+      <c r="AF37" s="162"/>
     </row>
     <row r="38" spans="2:32">
-      <c r="B38" s="154"/>
+      <c r="B38" s="153"/>
       <c r="C38" s="116"/>
       <c r="D38" s="116"/>
       <c r="E38" s="116"/>
@@ -6082,13 +6075,13 @@
       <c r="Z38" s="128"/>
       <c r="AA38" s="128"/>
       <c r="AB38" s="116"/>
-      <c r="AC38" s="181"/>
-      <c r="AD38" s="155"/>
+      <c r="AC38" s="180"/>
+      <c r="AD38" s="154"/>
       <c r="AE38" s="116"/>
-      <c r="AF38" s="163"/>
+      <c r="AF38" s="162"/>
     </row>
     <row r="39" spans="2:32">
-      <c r="B39" s="154"/>
+      <c r="B39" s="153"/>
       <c r="C39" s="130" t="s">
         <v>72</v>
       </c>
@@ -6161,15 +6154,15 @@
         <v>0</v>
       </c>
       <c r="AB39" s="116"/>
-      <c r="AC39" s="183">
+      <c r="AC39" s="182">
         <v>-206500</v>
       </c>
-      <c r="AD39" s="155"/>
+      <c r="AD39" s="154"/>
       <c r="AE39" s="116"/>
-      <c r="AF39" s="163"/>
+      <c r="AF39" s="162"/>
     </row>
     <row r="40" spans="2:32">
-      <c r="B40" s="154"/>
+      <c r="B40" s="153"/>
       <c r="C40" s="116"/>
       <c r="D40" s="116"/>
       <c r="E40" s="116"/>
@@ -6196,13 +6189,13 @@
       <c r="Z40" s="128"/>
       <c r="AA40" s="128"/>
       <c r="AB40" s="116"/>
-      <c r="AC40" s="181"/>
-      <c r="AD40" s="155"/>
+      <c r="AC40" s="180"/>
+      <c r="AD40" s="154"/>
       <c r="AE40" s="116"/>
-      <c r="AF40" s="163"/>
+      <c r="AF40" s="162"/>
     </row>
     <row r="41" spans="2:32">
-      <c r="B41" s="154"/>
+      <c r="B41" s="153"/>
       <c r="C41" s="145" t="s">
         <v>66</v>
       </c>
@@ -6231,13 +6224,13 @@
       <c r="Z41" s="128"/>
       <c r="AA41" s="128"/>
       <c r="AB41" s="116"/>
-      <c r="AC41" s="181"/>
-      <c r="AD41" s="155"/>
+      <c r="AC41" s="180"/>
+      <c r="AD41" s="154"/>
       <c r="AE41" s="116"/>
-      <c r="AF41" s="163"/>
+      <c r="AF41" s="162"/>
     </row>
     <row r="42" spans="2:32">
-      <c r="B42" s="154"/>
+      <c r="B42" s="153"/>
       <c r="C42" s="116" t="s">
         <v>75</v>
       </c>
@@ -6246,13 +6239,13 @@
         <v>3</v>
       </c>
       <c r="F42" s="116"/>
-      <c r="G42" s="162">
+      <c r="G42" s="161">
         <v>0.8</v>
       </c>
-      <c r="H42" s="162">
+      <c r="H42" s="161">
         <v>0.2</v>
       </c>
-      <c r="I42" s="162">
+      <c r="I42" s="161">
         <v>0</v>
       </c>
       <c r="J42" s="128"/>
@@ -6274,17 +6267,17 @@
       <c r="Z42" s="128"/>
       <c r="AA42" s="128"/>
       <c r="AB42" s="116"/>
-      <c r="AC42" s="184">
+      <c r="AC42" s="183">
         <v>1</v>
       </c>
-      <c r="AD42" s="155"/>
+      <c r="AD42" s="154"/>
       <c r="AE42" s="116"/>
-      <c r="AF42" s="167">
+      <c r="AF42" s="166">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:32">
-      <c r="B43" s="154"/>
+      <c r="B43" s="153"/>
       <c r="C43" s="119"/>
       <c r="D43" s="116"/>
       <c r="E43" s="116"/>
@@ -6311,13 +6304,13 @@
       <c r="Z43" s="128"/>
       <c r="AA43" s="128"/>
       <c r="AB43" s="116"/>
-      <c r="AC43" s="181"/>
-      <c r="AD43" s="155"/>
+      <c r="AC43" s="180"/>
+      <c r="AD43" s="154"/>
       <c r="AE43" s="116"/>
-      <c r="AF43" s="163"/>
+      <c r="AF43" s="162"/>
     </row>
     <row r="44" spans="2:32">
-      <c r="B44" s="154"/>
+      <c r="B44" s="153"/>
       <c r="C44" s="116" t="s">
         <v>66</v>
       </c>
@@ -6354,15 +6347,15 @@
       <c r="Z44" s="128"/>
       <c r="AA44" s="128"/>
       <c r="AB44" s="116"/>
-      <c r="AC44" s="182">
+      <c r="AC44" s="181">
         <v>-120000</v>
       </c>
-      <c r="AD44" s="155"/>
+      <c r="AD44" s="154"/>
       <c r="AE44" s="116"/>
-      <c r="AF44" s="163"/>
+      <c r="AF44" s="162"/>
     </row>
     <row r="45" spans="2:32">
-      <c r="B45" s="154"/>
+      <c r="B45" s="153"/>
       <c r="C45" s="116"/>
       <c r="D45" s="116"/>
       <c r="E45" s="116"/>
@@ -6389,13 +6382,13 @@
       <c r="Z45" s="128"/>
       <c r="AA45" s="128"/>
       <c r="AB45" s="116"/>
-      <c r="AC45" s="181"/>
-      <c r="AD45" s="155"/>
+      <c r="AC45" s="180"/>
+      <c r="AD45" s="154"/>
       <c r="AE45" s="116"/>
-      <c r="AF45" s="163"/>
+      <c r="AF45" s="162"/>
     </row>
     <row r="46" spans="2:32">
-      <c r="B46" s="154"/>
+      <c r="B46" s="153"/>
       <c r="C46" s="145" t="s">
         <v>51</v>
       </c>
@@ -6424,13 +6417,13 @@
       <c r="Z46" s="128"/>
       <c r="AA46" s="128"/>
       <c r="AB46" s="116"/>
-      <c r="AC46" s="181"/>
-      <c r="AD46" s="155"/>
+      <c r="AC46" s="180"/>
+      <c r="AD46" s="154"/>
       <c r="AE46" s="116"/>
-      <c r="AF46" s="163"/>
+      <c r="AF46" s="162"/>
     </row>
     <row r="47" spans="2:32">
-      <c r="B47" s="168"/>
+      <c r="B47" s="167"/>
       <c r="C47" s="136" t="s">
         <v>51</v>
       </c>
@@ -6504,12 +6497,12 @@
       <c r="AC47" s="138">
         <v>263500</v>
       </c>
-      <c r="AD47" s="173"/>
+      <c r="AD47" s="172"/>
       <c r="AE47" s="119"/>
-      <c r="AF47" s="164"/>
+      <c r="AF47" s="163"/>
     </row>
     <row r="48" spans="2:32">
-      <c r="B48" s="169"/>
+      <c r="B48" s="168"/>
       <c r="C48" s="141" t="s">
         <v>52</v>
       </c>
@@ -6580,17 +6573,17 @@
         <v>263500</v>
       </c>
       <c r="AB48" s="140"/>
-      <c r="AC48" s="185">
+      <c r="AC48" s="184">
         <v>263500</v>
       </c>
-      <c r="AD48" s="174"/>
+      <c r="AD48" s="173"/>
       <c r="AE48" s="140"/>
-      <c r="AF48" s="167">
+      <c r="AF48" s="166">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="2:32">
-      <c r="B49" s="154"/>
+      <c r="B49" s="153"/>
       <c r="C49" s="116"/>
       <c r="D49" s="116"/>
       <c r="E49" s="116"/>
@@ -6617,13 +6610,13 @@
       <c r="Z49" s="128"/>
       <c r="AA49" s="128"/>
       <c r="AB49" s="116"/>
-      <c r="AC49" s="181"/>
-      <c r="AD49" s="155"/>
+      <c r="AC49" s="180"/>
+      <c r="AD49" s="154"/>
       <c r="AE49" s="116"/>
-      <c r="AF49" s="163"/>
+      <c r="AF49" s="162"/>
     </row>
     <row r="50" spans="2:32" ht="15.75">
-      <c r="B50" s="170"/>
+      <c r="B50" s="169"/>
       <c r="C50" s="145" t="s">
         <v>54</v>
       </c>
@@ -6652,13 +6645,13 @@
       <c r="Z50" s="112"/>
       <c r="AA50" s="112"/>
       <c r="AB50" s="112"/>
-      <c r="AC50" s="186"/>
-      <c r="AD50" s="175"/>
+      <c r="AC50" s="185"/>
+      <c r="AD50" s="174"/>
       <c r="AE50" s="112"/>
       <c r="AF50" s="112"/>
     </row>
     <row r="51" spans="2:32" ht="15.75">
-      <c r="B51" s="171"/>
+      <c r="B51" s="170"/>
       <c r="C51" s="148" t="s">
         <v>76</v>
       </c>
@@ -6668,76 +6661,76 @@
       </c>
       <c r="F51" s="148"/>
       <c r="G51" s="148"/>
-      <c r="H51" s="161">
+      <c r="H51" s="160">
         <v>1</v>
       </c>
-      <c r="I51" s="161">
+      <c r="I51" s="160">
         <v>2</v>
       </c>
-      <c r="J51" s="161">
+      <c r="J51" s="160">
         <v>3</v>
       </c>
-      <c r="K51" s="161">
+      <c r="K51" s="160">
         <v>4</v>
       </c>
-      <c r="L51" s="161">
+      <c r="L51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="M51" s="161">
+      <c r="M51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="N51" s="161">
+      <c r="N51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="O51" s="161">
+      <c r="O51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="P51" s="161">
+      <c r="P51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="Q51" s="161">
+      <c r="Q51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="R51" s="161">
+      <c r="R51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="S51" s="161">
+      <c r="S51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="T51" s="161">
+      <c r="T51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="U51" s="161">
+      <c r="U51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="V51" s="161">
+      <c r="V51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="W51" s="161">
+      <c r="W51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="X51" s="161">
+      <c r="X51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="Y51" s="161">
+      <c r="Y51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="Z51" s="161">
+      <c r="Z51" s="160">
         <v>4.2087912087912089</v>
       </c>
-      <c r="AA51" s="161">
+      <c r="AA51" s="160">
         <v>4.2087912087912089</v>
       </c>
       <c r="AB51" s="148"/>
-      <c r="AC51" s="187">
+      <c r="AC51" s="186">
         <v>4.2087912087912089</v>
       </c>
-      <c r="AD51" s="176"/>
+      <c r="AD51" s="175"/>
       <c r="AE51" s="148"/>
-      <c r="AF51" s="165"/>
+      <c r="AF51" s="164"/>
     </row>
     <row r="52" spans="2:32">
-      <c r="B52" s="154"/>
+      <c r="B52" s="153"/>
       <c r="C52" s="133"/>
       <c r="D52" s="134"/>
       <c r="E52" s="134"/>
@@ -6764,13 +6757,13 @@
       <c r="Z52" s="135"/>
       <c r="AA52" s="116"/>
       <c r="AB52" s="116"/>
-      <c r="AC52" s="181"/>
-      <c r="AD52" s="155"/>
+      <c r="AC52" s="180"/>
+      <c r="AD52" s="154"/>
       <c r="AE52" s="116"/>
-      <c r="AF52" s="163"/>
+      <c r="AF52" s="162"/>
     </row>
     <row r="53" spans="2:32">
-      <c r="B53" s="154"/>
+      <c r="B53" s="153"/>
       <c r="C53" s="145" t="s">
         <v>78</v>
       </c>
@@ -6799,18 +6792,18 @@
       <c r="Z53" s="135"/>
       <c r="AA53" s="116"/>
       <c r="AB53" s="116"/>
-      <c r="AC53" s="181"/>
-      <c r="AD53" s="155"/>
+      <c r="AC53" s="180"/>
+      <c r="AD53" s="154"/>
       <c r="AE53" s="116"/>
-      <c r="AF53" s="163"/>
+      <c r="AF53" s="162"/>
     </row>
     <row r="54" spans="2:32">
-      <c r="B54" s="154"/>
+      <c r="B54" s="153"/>
       <c r="C54" s="116" t="s">
         <v>51</v>
       </c>
       <c r="D54" s="134"/>
-      <c r="E54" s="180" t="b">
+      <c r="E54" s="179" t="b">
         <v>1</v>
       </c>
       <c r="F54" s="134"/>
@@ -6878,18 +6871,18 @@
         <v>0</v>
       </c>
       <c r="AB54" s="116"/>
-      <c r="AC54" s="181"/>
-      <c r="AD54" s="155"/>
+      <c r="AC54" s="180"/>
+      <c r="AD54" s="154"/>
       <c r="AE54" s="116"/>
-      <c r="AF54" s="163"/>
+      <c r="AF54" s="162"/>
     </row>
     <row r="55" spans="2:32">
-      <c r="B55" s="154"/>
+      <c r="B55" s="153"/>
       <c r="C55" s="116" t="s">
         <v>52</v>
       </c>
       <c r="D55" s="134"/>
-      <c r="E55" s="178" t="b">
+      <c r="E55" s="177" t="b">
         <v>1</v>
       </c>
       <c r="F55" s="134"/>
@@ -6957,47 +6950,47 @@
         <v>263500</v>
       </c>
       <c r="AB55" s="116"/>
-      <c r="AC55" s="181"/>
-      <c r="AD55" s="155"/>
+      <c r="AC55" s="180"/>
+      <c r="AD55" s="154"/>
       <c r="AE55" s="116"/>
-      <c r="AF55" s="163"/>
+      <c r="AF55" s="162"/>
     </row>
     <row r="56" spans="2:32" ht="15.75">
-      <c r="B56" s="172"/>
-      <c r="C56" s="150"/>
-      <c r="D56" s="150"/>
-      <c r="E56" s="150"/>
-      <c r="F56" s="150"/>
-      <c r="G56" s="150"/>
-      <c r="H56" s="150"/>
-      <c r="I56" s="150"/>
-      <c r="J56" s="150"/>
-      <c r="K56" s="150"/>
-      <c r="L56" s="150"/>
-      <c r="M56" s="150"/>
-      <c r="N56" s="150"/>
-      <c r="O56" s="150"/>
-      <c r="P56" s="150"/>
-      <c r="Q56" s="150"/>
-      <c r="R56" s="150"/>
-      <c r="S56" s="150"/>
-      <c r="T56" s="150"/>
-      <c r="U56" s="150"/>
-      <c r="V56" s="150"/>
-      <c r="W56" s="150"/>
-      <c r="X56" s="150"/>
-      <c r="Y56" s="150"/>
-      <c r="Z56" s="150"/>
-      <c r="AA56" s="150"/>
-      <c r="AB56" s="150"/>
-      <c r="AC56" s="188"/>
-      <c r="AD56" s="177"/>
+      <c r="B56" s="171"/>
+      <c r="C56" s="149"/>
+      <c r="D56" s="149"/>
+      <c r="E56" s="149"/>
+      <c r="F56" s="149"/>
+      <c r="G56" s="149"/>
+      <c r="H56" s="149"/>
+      <c r="I56" s="149"/>
+      <c r="J56" s="149"/>
+      <c r="K56" s="149"/>
+      <c r="L56" s="149"/>
+      <c r="M56" s="149"/>
+      <c r="N56" s="149"/>
+      <c r="O56" s="149"/>
+      <c r="P56" s="149"/>
+      <c r="Q56" s="149"/>
+      <c r="R56" s="149"/>
+      <c r="S56" s="149"/>
+      <c r="T56" s="149"/>
+      <c r="U56" s="149"/>
+      <c r="V56" s="149"/>
+      <c r="W56" s="149"/>
+      <c r="X56" s="149"/>
+      <c r="Y56" s="149"/>
+      <c r="Z56" s="149"/>
+      <c r="AA56" s="149"/>
+      <c r="AB56" s="149"/>
+      <c r="AC56" s="187"/>
+      <c r="AD56" s="176"/>
       <c r="AE56" s="112"/>
       <c r="AF56" s="112"/>
     </row>
     <row r="61" spans="2:32" ht="15.75">
       <c r="B61" s="112"/>
-      <c r="C61" s="200" t="s">
+      <c r="C61" s="199" t="s">
         <v>79</v>
       </c>
       <c r="D61" s="112"/>
@@ -7032,8 +7025,8 @@
     </row>
     <row r="62" spans="2:32" ht="15.75">
       <c r="B62" s="112"/>
-      <c r="C62" s="149" t="s">
-        <v>80</v>
+      <c r="C62" s="292" t="s">
+        <v>146</v>
       </c>
       <c r="D62" s="112"/>
       <c r="E62" s="112"/>
@@ -7090,7 +7083,7 @@
       <c r="AC76" s="116"/>
       <c r="AD76" s="116"/>
       <c r="AE76" s="116"/>
-      <c r="AF76" s="163"/>
+      <c r="AF76" s="162"/>
     </row>
     <row r="77" spans="8:32" ht="15.75">
       <c r="H77" s="113"/>
@@ -7146,108 +7139,108 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="23.25">
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="200" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="200"/>
+      <c r="I2" s="200"/>
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" s="201"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201">
+        <v>0</v>
+      </c>
+      <c r="E3" s="201">
+        <v>1</v>
+      </c>
+      <c r="F3" s="201">
+        <v>2</v>
+      </c>
+      <c r="G3" s="201">
+        <v>3</v>
+      </c>
+      <c r="H3" s="201">
+        <v>4</v>
+      </c>
+      <c r="I3" s="201">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" s="202"/>
+      <c r="C4" s="202"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="202"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="202"/>
+      <c r="H4" s="202"/>
+      <c r="I4" s="202"/>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" s="203" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-      <c r="G2" s="201"/>
-      <c r="H2" s="201"/>
-      <c r="I2" s="201"/>
-    </row>
-    <row r="3" spans="2:9">
-      <c r="B3" s="202"/>
-      <c r="C3" s="202"/>
-      <c r="D3" s="202">
-        <v>0</v>
-      </c>
-      <c r="E3" s="202">
-        <v>1</v>
-      </c>
-      <c r="F3" s="202">
-        <v>2</v>
-      </c>
-      <c r="G3" s="202">
-        <v>3</v>
-      </c>
-      <c r="H3" s="202">
-        <v>4</v>
-      </c>
-      <c r="I3" s="202">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="203"/>
-      <c r="C4" s="203"/>
-      <c r="D4" s="203"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
-      <c r="I4" s="203"/>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="204" t="s">
+      <c r="C5" s="203"/>
+      <c r="D5" s="204" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="204"/>
-      <c r="D5" s="205" t="s">
+      <c r="E5" s="202"/>
+      <c r="F5" s="202"/>
+      <c r="G5" s="202"/>
+      <c r="H5" s="202"/>
+      <c r="I5" s="202"/>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="203" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="204" t="s">
+      <c r="C6" s="203"/>
+      <c r="D6" s="204" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="204"/>
-      <c r="D6" s="205" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="203"/>
-      <c r="F6" s="203"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="203"/>
-      <c r="I6" s="203"/>
+      <c r="E6" s="202"/>
+      <c r="F6" s="202"/>
+      <c r="G6" s="202"/>
+      <c r="H6" s="202"/>
+      <c r="I6" s="202"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="203"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="203"/>
-      <c r="E7" s="203"/>
-      <c r="F7" s="203"/>
-      <c r="G7" s="203"/>
-      <c r="H7" s="203"/>
-      <c r="I7" s="203"/>
+      <c r="B7" s="202"/>
+      <c r="C7" s="202"/>
+      <c r="D7" s="202"/>
+      <c r="E7" s="202"/>
+      <c r="F7" s="202"/>
+      <c r="G7" s="202"/>
+      <c r="H7" s="202"/>
+      <c r="I7" s="202"/>
     </row>
     <row r="8" spans="2:9" s="14" customFormat="1">
       <c r="B8" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="206">
+        <v>85</v>
+      </c>
+      <c r="D8" s="205">
         <v>150000</v>
       </c>
     </row>
     <row r="9" spans="2:9" s="14" customFormat="1">
       <c r="B9" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="206">
+        <v>86</v>
+      </c>
+      <c r="D9" s="205">
         <v>500</v>
       </c>
     </row>
     <row r="10" spans="2:9" s="14" customFormat="1">
       <c r="B10" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="206">
+        <v>87</v>
+      </c>
+      <c r="D10" s="205">
         <f>+D8/D9</f>
         <v>300</v>
       </c>
@@ -7255,96 +7248,96 @@
     <row r="11" spans="2:9" s="14" customFormat="1"/>
     <row r="12" spans="2:9" s="14" customFormat="1">
       <c r="B12" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="206">
+        <v>88</v>
+      </c>
+      <c r="E12" s="205">
         <v>500</v>
       </c>
-      <c r="F12" s="206">
+      <c r="F12" s="205">
         <f>+E12+500</f>
         <v>1000</v>
       </c>
-      <c r="G12" s="206">
+      <c r="G12" s="205">
         <f t="shared" ref="G12:I12" si="0">+F12+500</f>
         <v>1500</v>
       </c>
-      <c r="H12" s="206">
+      <c r="H12" s="205">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="I12" s="206">
+      <c r="I12" s="205">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
     </row>
     <row r="13" spans="2:9" s="14" customFormat="1">
       <c r="B13" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="206">
+        <v>89</v>
+      </c>
+      <c r="E13" s="205">
         <v>300</v>
       </c>
-      <c r="F13" s="206">
+      <c r="F13" s="205">
         <v>600</v>
       </c>
-      <c r="G13" s="206">
+      <c r="G13" s="205">
         <v>900</v>
       </c>
-      <c r="H13" s="206">
+      <c r="H13" s="205">
         <v>1200</v>
       </c>
-      <c r="I13" s="206">
+      <c r="I13" s="205">
         <v>1500</v>
       </c>
     </row>
     <row r="14" spans="2:9" s="14" customFormat="1">
       <c r="B14" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="207">
+        <v>90</v>
+      </c>
+      <c r="E14" s="206">
         <f>+E12-E13</f>
         <v>200</v>
       </c>
-      <c r="F14" s="207">
+      <c r="F14" s="206">
         <f>+F12-F13</f>
         <v>400</v>
       </c>
-      <c r="G14" s="207">
+      <c r="G14" s="206">
         <f>+G12-G13</f>
         <v>600</v>
       </c>
-      <c r="H14" s="207">
+      <c r="H14" s="206">
         <f>+H12-H13</f>
         <v>800</v>
       </c>
-      <c r="I14" s="207">
+      <c r="I14" s="206">
         <f>+I12-I13</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="2:9" s="210" customFormat="1" ht="16.5">
-      <c r="B15" s="208" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="208"/>
-      <c r="D15" s="208"/>
-      <c r="E15" s="209">
+    <row r="15" spans="2:9" s="209" customFormat="1" ht="16.5">
+      <c r="B15" s="207" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="207"/>
+      <c r="D15" s="207"/>
+      <c r="E15" s="208">
         <f>+E13/E12</f>
         <v>0.6</v>
       </c>
-      <c r="F15" s="209">
+      <c r="F15" s="208">
         <f t="shared" ref="F15:I15" si="1">+F13/F12</f>
         <v>0.6</v>
       </c>
-      <c r="G15" s="209">
+      <c r="G15" s="208">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H15" s="209">
+      <c r="H15" s="208">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="I15" s="209">
+      <c r="I15" s="208">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -7352,45 +7345,45 @@
     <row r="16" spans="2:9" s="14" customFormat="1"/>
     <row r="17" spans="2:9" s="14" customFormat="1">
       <c r="B17" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="211">
+        <v>92</v>
+      </c>
+      <c r="E17" s="210">
         <v>1</v>
       </c>
-      <c r="F17" s="211">
+      <c r="F17" s="210">
         <v>0.8</v>
       </c>
-      <c r="G17" s="211">
+      <c r="G17" s="210">
         <v>0.75</v>
       </c>
-      <c r="H17" s="211">
+      <c r="H17" s="210">
         <v>0.7</v>
       </c>
-      <c r="I17" s="211">
+      <c r="I17" s="210">
         <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="2:9" s="14" customFormat="1">
       <c r="B18" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="212">
+        <v>93</v>
+      </c>
+      <c r="E18" s="211">
         <f>+E17</f>
         <v>1</v>
       </c>
-      <c r="F18" s="213">
+      <c r="F18" s="212">
         <f>+F17*E18</f>
         <v>0.8</v>
       </c>
-      <c r="G18" s="213">
+      <c r="G18" s="212">
         <f>+G17*F18</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H18" s="213">
+      <c r="H18" s="212">
         <f t="shared" ref="H18" si="2">+H17*G18</f>
         <v>0.42000000000000004</v>
       </c>
-      <c r="I18" s="213">
+      <c r="I18" s="212">
         <f>+I17*H18</f>
         <v>0.252</v>
       </c>
@@ -7398,9 +7391,9 @@
     <row r="19" spans="2:9" s="14" customFormat="1"/>
     <row r="20" spans="2:9" s="14" customFormat="1">
       <c r="B20" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="214">
+        <v>94</v>
+      </c>
+      <c r="E20" s="213">
         <f>+E18*E14</f>
         <v>200</v>
       </c>
@@ -7424,28 +7417,28 @@
     <row r="21" spans="2:9" s="14" customFormat="1"/>
     <row r="22" spans="2:9" s="14" customFormat="1">
       <c r="B22" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" s="215">
+        <v>95</v>
+      </c>
+      <c r="D22" s="214">
         <v>0.2</v>
       </c>
-      <c r="E22" s="216">
+      <c r="E22" s="215">
         <f>1/(1+$D$22)^E3</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="F22" s="216">
+      <c r="F22" s="215">
         <f>1/(1+$D$22)^F3</f>
         <v>0.69444444444444442</v>
       </c>
-      <c r="G22" s="216">
+      <c r="G22" s="215">
         <f>1/(1+$D$22)^G3</f>
         <v>0.57870370370370372</v>
       </c>
-      <c r="H22" s="216">
+      <c r="H22" s="215">
         <f>1/(1+$D$22)^H3</f>
         <v>0.48225308641975312</v>
       </c>
-      <c r="I22" s="216">
+      <c r="I22" s="215">
         <f>1/(1+$D$22)^I3</f>
         <v>0.4018775720164609</v>
       </c>
@@ -7453,90 +7446,90 @@
     <row r="23" spans="2:9" s="14" customFormat="1"/>
     <row r="24" spans="2:9" s="14" customFormat="1">
       <c r="B24" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24" s="15"/>
-      <c r="D24" s="217">
+      <c r="D24" s="216">
         <f>+-D10</f>
         <v>-300</v>
       </c>
-      <c r="E24" s="218">
+      <c r="E24" s="217">
         <f>+E22*E20</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="F24" s="218">
+      <c r="F24" s="217">
         <f>+F22*F20</f>
         <v>222.22222222222223</v>
       </c>
-      <c r="G24" s="218">
+      <c r="G24" s="217">
         <f t="shared" ref="G24:I24" si="3">+G22*G20</f>
         <v>208.33333333333337</v>
       </c>
-      <c r="H24" s="218">
+      <c r="H24" s="217">
         <f t="shared" si="3"/>
         <v>162.03703703703707</v>
       </c>
-      <c r="I24" s="218">
+      <c r="I24" s="217">
         <f t="shared" si="3"/>
         <v>101.27314814814815</v>
       </c>
     </row>
     <row r="25" spans="2:9" s="14" customFormat="1">
       <c r="B25" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C25" s="15"/>
-      <c r="D25" s="219">
+      <c r="D25" s="218">
         <f>+D24</f>
         <v>-300</v>
       </c>
-      <c r="E25" s="219">
+      <c r="E25" s="218">
         <f>+D25+E24</f>
         <v>-133.33333333333331</v>
       </c>
-      <c r="F25" s="219">
+      <c r="F25" s="218">
         <f t="shared" ref="F25:I25" si="4">+E25+F24</f>
         <v>88.888888888888914</v>
       </c>
-      <c r="G25" s="219">
+      <c r="G25" s="218">
         <f t="shared" si="4"/>
         <v>297.22222222222229</v>
       </c>
-      <c r="H25" s="219">
+      <c r="H25" s="218">
         <f t="shared" si="4"/>
         <v>459.25925925925935</v>
       </c>
-      <c r="I25" s="219">
+      <c r="I25" s="218">
         <f t="shared" si="4"/>
         <v>560.5324074074075</v>
       </c>
     </row>
     <row r="26" spans="2:9" s="14" customFormat="1">
       <c r="B26" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C26" s="15"/>
-      <c r="D26" s="219">
+      <c r="D26" s="218">
         <f>+D25/-$D$25</f>
         <v>-1</v>
       </c>
-      <c r="E26" s="219">
+      <c r="E26" s="218">
         <f>+E25/-$D$25</f>
         <v>-0.44444444444444436</v>
       </c>
-      <c r="F26" s="219">
+      <c r="F26" s="218">
         <f>+F25/-$D$25</f>
         <v>0.29629629629629639</v>
       </c>
-      <c r="G26" s="219">
+      <c r="G26" s="218">
         <f t="shared" ref="G26:H26" si="5">+G25/-$D$25</f>
         <v>0.99074074074074092</v>
       </c>
-      <c r="H26" s="219">
+      <c r="H26" s="218">
         <f t="shared" si="5"/>
         <v>1.5308641975308646</v>
       </c>
-      <c r="I26" s="219">
+      <c r="I26" s="218">
         <f>+I25/-$D$25</f>
         <v>1.8684413580246917</v>
       </c>
@@ -7544,202 +7537,202 @@
     <row r="27" spans="2:9" s="14" customFormat="1">
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
-      <c r="D27" s="219"/>
-      <c r="E27" s="219"/>
-      <c r="F27" s="219"/>
-      <c r="G27" s="219"/>
-      <c r="H27" s="219"/>
-      <c r="I27" s="219"/>
+      <c r="D27" s="218"/>
+      <c r="E27" s="218"/>
+      <c r="F27" s="218"/>
+      <c r="G27" s="218"/>
+      <c r="H27" s="218"/>
+      <c r="I27" s="218"/>
     </row>
     <row r="28" spans="2:9" s="14" customFormat="1">
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
-      <c r="D28" s="219"/>
-      <c r="E28" s="219"/>
-      <c r="F28" s="219"/>
-      <c r="G28" s="219"/>
-      <c r="H28" s="219"/>
-      <c r="I28" s="219"/>
+      <c r="D28" s="218"/>
+      <c r="E28" s="218"/>
+      <c r="F28" s="218"/>
+      <c r="G28" s="218"/>
+      <c r="H28" s="218"/>
+      <c r="I28" s="218"/>
     </row>
     <row r="29" spans="2:9" s="14" customFormat="1">
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
-      <c r="D29" s="219"/>
-      <c r="E29" s="219"/>
-      <c r="F29" s="219"/>
-      <c r="G29" s="219"/>
-      <c r="H29" s="219"/>
-      <c r="I29" s="219"/>
+      <c r="D29" s="218"/>
+      <c r="E29" s="218"/>
+      <c r="F29" s="218"/>
+      <c r="G29" s="218"/>
+      <c r="H29" s="218"/>
+      <c r="I29" s="218"/>
     </row>
     <row r="30" spans="2:9" s="14" customFormat="1">
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
-      <c r="D30" s="219"/>
-      <c r="E30" s="219"/>
-      <c r="F30" s="219"/>
-      <c r="G30" s="219"/>
-      <c r="H30" s="219"/>
-      <c r="I30" s="219"/>
+      <c r="D30" s="218"/>
+      <c r="E30" s="218"/>
+      <c r="F30" s="218"/>
+      <c r="G30" s="218"/>
+      <c r="H30" s="218"/>
+      <c r="I30" s="218"/>
     </row>
     <row r="31" spans="2:9" s="14" customFormat="1">
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
-      <c r="D31" s="219"/>
-      <c r="E31" s="219"/>
-      <c r="F31" s="219"/>
-      <c r="G31" s="219"/>
-      <c r="H31" s="219"/>
-      <c r="I31" s="219"/>
+      <c r="D31" s="218"/>
+      <c r="E31" s="218"/>
+      <c r="F31" s="218"/>
+      <c r="G31" s="218"/>
+      <c r="H31" s="218"/>
+      <c r="I31" s="218"/>
     </row>
     <row r="32" spans="2:9" s="14" customFormat="1">
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
-      <c r="D32" s="219"/>
-      <c r="E32" s="219"/>
-      <c r="F32" s="219"/>
-      <c r="G32" s="219"/>
-      <c r="H32" s="219"/>
-      <c r="I32" s="219"/>
+      <c r="D32" s="218"/>
+      <c r="E32" s="218"/>
+      <c r="F32" s="218"/>
+      <c r="G32" s="218"/>
+      <c r="H32" s="218"/>
+      <c r="I32" s="218"/>
     </row>
     <row r="33" spans="2:9" s="14" customFormat="1">
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
-      <c r="D33" s="219"/>
-      <c r="E33" s="219"/>
-      <c r="F33" s="219"/>
-      <c r="G33" s="219"/>
-      <c r="H33" s="219"/>
-      <c r="I33" s="219"/>
+      <c r="D33" s="218"/>
+      <c r="E33" s="218"/>
+      <c r="F33" s="218"/>
+      <c r="G33" s="218"/>
+      <c r="H33" s="218"/>
+      <c r="I33" s="218"/>
     </row>
     <row r="34" spans="2:9" s="14" customFormat="1">
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
-      <c r="D34" s="219"/>
-      <c r="E34" s="219"/>
-      <c r="F34" s="219"/>
-      <c r="G34" s="219"/>
-      <c r="H34" s="219"/>
-      <c r="I34" s="219"/>
+      <c r="D34" s="218"/>
+      <c r="E34" s="218"/>
+      <c r="F34" s="218"/>
+      <c r="G34" s="218"/>
+      <c r="H34" s="218"/>
+      <c r="I34" s="218"/>
     </row>
     <row r="35" spans="2:9" s="14" customFormat="1">
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
-      <c r="D35" s="219"/>
-      <c r="E35" s="219"/>
-      <c r="F35" s="219"/>
-      <c r="G35" s="219"/>
-      <c r="H35" s="219"/>
-      <c r="I35" s="219"/>
+      <c r="D35" s="218"/>
+      <c r="E35" s="218"/>
+      <c r="F35" s="218"/>
+      <c r="G35" s="218"/>
+      <c r="H35" s="218"/>
+      <c r="I35" s="218"/>
     </row>
     <row r="36" spans="2:9" s="14" customFormat="1">
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
-      <c r="D36" s="219"/>
-      <c r="E36" s="219"/>
-      <c r="F36" s="219"/>
-      <c r="G36" s="219"/>
-      <c r="H36" s="219"/>
-      <c r="I36" s="219"/>
+      <c r="D36" s="218"/>
+      <c r="E36" s="218"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="218"/>
+      <c r="H36" s="218"/>
+      <c r="I36" s="218"/>
     </row>
     <row r="37" spans="2:9" s="14" customFormat="1">
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
-      <c r="D37" s="219"/>
-      <c r="E37" s="219"/>
-      <c r="F37" s="219"/>
-      <c r="G37" s="219"/>
-      <c r="H37" s="219"/>
-      <c r="I37" s="219"/>
+      <c r="D37" s="218"/>
+      <c r="E37" s="218"/>
+      <c r="F37" s="218"/>
+      <c r="G37" s="218"/>
+      <c r="H37" s="218"/>
+      <c r="I37" s="218"/>
     </row>
     <row r="38" spans="2:9" s="14" customFormat="1">
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
-      <c r="D38" s="219"/>
-      <c r="E38" s="219"/>
-      <c r="F38" s="219"/>
-      <c r="G38" s="219"/>
-      <c r="H38" s="219"/>
-      <c r="I38" s="219"/>
+      <c r="D38" s="218"/>
+      <c r="E38" s="218"/>
+      <c r="F38" s="218"/>
+      <c r="G38" s="218"/>
+      <c r="H38" s="218"/>
+      <c r="I38" s="218"/>
     </row>
     <row r="39" spans="2:9" s="14" customFormat="1">
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
-      <c r="D39" s="219"/>
-      <c r="E39" s="219"/>
-      <c r="F39" s="219"/>
-      <c r="G39" s="219"/>
-      <c r="H39" s="219"/>
-      <c r="I39" s="219"/>
+      <c r="D39" s="218"/>
+      <c r="E39" s="218"/>
+      <c r="F39" s="218"/>
+      <c r="G39" s="218"/>
+      <c r="H39" s="218"/>
+      <c r="I39" s="218"/>
     </row>
     <row r="40" spans="2:9" s="14" customFormat="1">
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
-      <c r="D40" s="219"/>
-      <c r="E40" s="219"/>
-      <c r="F40" s="219"/>
-      <c r="G40" s="219"/>
-      <c r="H40" s="219"/>
-      <c r="I40" s="219"/>
+      <c r="D40" s="218"/>
+      <c r="E40" s="218"/>
+      <c r="F40" s="218"/>
+      <c r="G40" s="218"/>
+      <c r="H40" s="218"/>
+      <c r="I40" s="218"/>
     </row>
     <row r="41" spans="2:9" s="14" customFormat="1">
       <c r="B41" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C41" s="15"/>
-      <c r="D41" s="219"/>
-      <c r="E41" s="219"/>
-      <c r="F41" s="219"/>
-      <c r="G41" s="219"/>
-      <c r="H41" s="219"/>
-      <c r="I41" s="219"/>
+      <c r="D41" s="218"/>
+      <c r="E41" s="218"/>
+      <c r="F41" s="218"/>
+      <c r="G41" s="218"/>
+      <c r="H41" s="218"/>
+      <c r="I41" s="218"/>
     </row>
     <row r="42" spans="2:9" s="14" customFormat="1">
       <c r="B42" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C42" s="15"/>
-      <c r="D42" s="219"/>
-      <c r="E42" s="219"/>
-      <c r="F42" s="219"/>
-      <c r="G42" s="219"/>
-      <c r="H42" s="219"/>
-      <c r="I42" s="219"/>
+      <c r="D42" s="218"/>
+      <c r="E42" s="218"/>
+      <c r="F42" s="218"/>
+      <c r="G42" s="218"/>
+      <c r="H42" s="218"/>
+      <c r="I42" s="218"/>
     </row>
     <row r="43" spans="2:9" s="14" customFormat="1">
       <c r="B43" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" s="15"/>
-      <c r="D43" s="219"/>
-      <c r="E43" s="219"/>
-      <c r="F43" s="219"/>
-      <c r="G43" s="219"/>
-      <c r="H43" s="219"/>
-      <c r="I43" s="219"/>
+      <c r="D43" s="218"/>
+      <c r="E43" s="218"/>
+      <c r="F43" s="218"/>
+      <c r="G43" s="218"/>
+      <c r="H43" s="218"/>
+      <c r="I43" s="218"/>
     </row>
     <row r="44" spans="2:9" s="14" customFormat="1">
       <c r="B44" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="15"/>
-      <c r="D44" s="219"/>
-      <c r="E44" s="219"/>
-      <c r="F44" s="219"/>
-      <c r="G44" s="219"/>
-      <c r="H44" s="219"/>
-      <c r="I44" s="219"/>
+      <c r="D44" s="218"/>
+      <c r="E44" s="218"/>
+      <c r="F44" s="218"/>
+      <c r="G44" s="218"/>
+      <c r="H44" s="218"/>
+      <c r="I44" s="218"/>
     </row>
     <row r="45" spans="2:9" s="14" customFormat="1">
       <c r="B45" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C45" s="15"/>
-      <c r="D45" s="219"/>
-      <c r="E45" s="219"/>
-      <c r="F45" s="219"/>
-      <c r="G45" s="219"/>
-      <c r="H45" s="219"/>
-      <c r="I45" s="219"/>
+      <c r="D45" s="218"/>
+      <c r="E45" s="218"/>
+      <c r="F45" s="218"/>
+      <c r="G45" s="218"/>
+      <c r="H45" s="218"/>
+      <c r="I45" s="218"/>
     </row>
     <row r="46" spans="2:9" ht="16.5" thickBot="1">
       <c r="B46" s="17"/>
@@ -7769,1099 +7762,1099 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:24" ht="26.25">
-      <c r="B3" s="224"/>
-      <c r="C3" s="224" t="s">
+      <c r="B3" s="223"/>
+      <c r="C3" s="223" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
+      <c r="M3" s="223"/>
+      <c r="N3" s="223"/>
+      <c r="O3" s="223"/>
+      <c r="P3" s="223"/>
+      <c r="Q3" s="223"/>
+      <c r="R3" s="223"/>
+      <c r="S3" s="223"/>
+      <c r="T3" s="223"/>
+      <c r="U3" s="223"/>
+      <c r="V3" s="223"/>
+      <c r="W3" s="223"/>
+      <c r="X3" s="223"/>
+    </row>
+    <row r="5" spans="2:24" ht="21">
+      <c r="C5" s="236" t="s">
         <v>103</v>
       </c>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
-      <c r="M3" s="224"/>
-      <c r="N3" s="224"/>
-      <c r="O3" s="224"/>
-      <c r="P3" s="224"/>
-      <c r="Q3" s="224"/>
-      <c r="R3" s="224"/>
-      <c r="S3" s="224"/>
-      <c r="T3" s="224"/>
-      <c r="U3" s="224"/>
-      <c r="V3" s="224"/>
-      <c r="W3" s="224"/>
-      <c r="X3" s="224"/>
-    </row>
-    <row r="5" spans="2:24" ht="21">
-      <c r="C5" s="237" t="s">
+      <c r="K5" s="236"/>
+      <c r="L5" s="237"/>
+    </row>
+    <row r="7" spans="2:24">
+      <c r="B7" s="254"/>
+      <c r="C7" s="273"/>
+      <c r="D7" s="273"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="273"/>
+      <c r="G7" s="273"/>
+      <c r="H7" s="273"/>
+      <c r="I7" s="225"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="225"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="254"/>
+      <c r="O7" s="254"/>
+      <c r="P7" s="254"/>
+      <c r="Q7" s="254"/>
+      <c r="R7" s="254"/>
+      <c r="S7" s="254"/>
+      <c r="T7" s="254"/>
+      <c r="U7" s="254">
+        <v>1905</v>
+      </c>
+      <c r="V7" s="254">
+        <v>1905</v>
+      </c>
+      <c r="W7" s="254">
+        <v>1905</v>
+      </c>
+      <c r="X7" s="254"/>
+    </row>
+    <row r="8" spans="2:24">
+      <c r="B8" s="254"/>
+      <c r="C8" s="273" t="s">
         <v>104</v>
       </c>
-      <c r="K5" s="237"/>
-      <c r="L5" s="238"/>
-    </row>
-    <row r="7" spans="2:24">
-      <c r="B7" s="255"/>
-      <c r="C7" s="274"/>
-      <c r="D7" s="274"/>
-      <c r="E7" s="274"/>
-      <c r="F7" s="274"/>
-      <c r="G7" s="274"/>
-      <c r="H7" s="274"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="255"/>
-      <c r="N7" s="255"/>
-      <c r="O7" s="255"/>
-      <c r="P7" s="255"/>
-      <c r="Q7" s="255"/>
-      <c r="R7" s="255"/>
-      <c r="S7" s="255"/>
-      <c r="T7" s="255"/>
-      <c r="U7" s="255">
-        <v>1905</v>
-      </c>
-      <c r="V7" s="255">
-        <v>1905</v>
-      </c>
-      <c r="W7" s="255">
-        <v>1905</v>
-      </c>
-      <c r="X7" s="255"/>
-    </row>
-    <row r="8" spans="2:24">
-      <c r="B8" s="255"/>
-      <c r="C8" s="274" t="s">
+      <c r="D8" s="289" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="290" t="s">
+      <c r="E8" s="290"/>
+      <c r="F8" s="290"/>
+      <c r="G8" s="291"/>
+      <c r="H8" s="273"/>
+      <c r="I8" s="225"/>
+      <c r="J8" s="225" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="291"/>
-      <c r="F8" s="291"/>
-      <c r="G8" s="292"/>
-      <c r="H8" s="274"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="226" t="s">
+      <c r="K8" s="225"/>
+      <c r="L8" s="225" t="s">
         <v>107</v>
       </c>
-      <c r="K8" s="226"/>
-      <c r="L8" s="226" t="s">
+      <c r="M8" s="254">
+        <v>2023</v>
+      </c>
+      <c r="N8" s="254">
+        <v>2024</v>
+      </c>
+      <c r="O8" s="254">
+        <v>2025</v>
+      </c>
+      <c r="P8" s="254">
+        <v>2026</v>
+      </c>
+      <c r="Q8" s="254">
+        <v>2027</v>
+      </c>
+      <c r="R8" s="254">
+        <v>2028</v>
+      </c>
+      <c r="S8" s="254">
+        <v>2029</v>
+      </c>
+      <c r="T8" s="254">
+        <v>2030</v>
+      </c>
+      <c r="U8" s="254">
+        <v>2031</v>
+      </c>
+      <c r="V8" s="254">
+        <v>2032</v>
+      </c>
+      <c r="W8" s="254">
+        <v>2033</v>
+      </c>
+      <c r="X8" s="254"/>
+    </row>
+    <row r="9" spans="2:24">
+      <c r="B9" s="229"/>
+      <c r="C9" s="273"/>
+      <c r="D9" s="273"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="273"/>
+      <c r="G9" s="273"/>
+      <c r="H9" s="273"/>
+      <c r="I9" s="225"/>
+      <c r="J9" s="225" t="s">
         <v>108</v>
       </c>
-      <c r="M8" s="255">
-        <v>2023</v>
-      </c>
-      <c r="N8" s="255">
-        <v>2024</v>
-      </c>
-      <c r="O8" s="255">
-        <v>2025</v>
-      </c>
-      <c r="P8" s="255">
-        <v>2026</v>
-      </c>
-      <c r="Q8" s="255">
-        <v>2027</v>
-      </c>
-      <c r="R8" s="255">
-        <v>2028</v>
-      </c>
-      <c r="S8" s="255">
-        <v>2029</v>
-      </c>
-      <c r="T8" s="255">
-        <v>2030</v>
-      </c>
-      <c r="U8" s="255">
-        <v>2031</v>
-      </c>
-      <c r="V8" s="255">
-        <v>2032</v>
-      </c>
-      <c r="W8" s="255">
-        <v>2033</v>
-      </c>
-      <c r="X8" s="255"/>
-    </row>
-    <row r="9" spans="2:24">
-      <c r="B9" s="230"/>
-      <c r="C9" s="274"/>
-      <c r="D9" s="274"/>
-      <c r="E9" s="274"/>
-      <c r="F9" s="274"/>
-      <c r="G9" s="274"/>
-      <c r="H9" s="274"/>
-      <c r="I9" s="226"/>
-      <c r="J9" s="226" t="s">
+      <c r="K9" s="225"/>
+      <c r="L9" s="225"/>
+      <c r="M9" s="229">
+        <v>45291</v>
+      </c>
+      <c r="N9" s="229">
+        <v>45657</v>
+      </c>
+      <c r="O9" s="229">
+        <v>46022</v>
+      </c>
+      <c r="P9" s="229">
+        <v>46387</v>
+      </c>
+      <c r="Q9" s="229">
+        <v>46752</v>
+      </c>
+      <c r="R9" s="229">
+        <v>47118</v>
+      </c>
+      <c r="S9" s="229">
+        <v>47483</v>
+      </c>
+      <c r="T9" s="229">
+        <v>47848</v>
+      </c>
+      <c r="U9" s="229">
+        <v>48213</v>
+      </c>
+      <c r="V9" s="229">
+        <v>48579</v>
+      </c>
+      <c r="W9" s="229">
+        <v>48944</v>
+      </c>
+      <c r="X9" s="229"/>
+    </row>
+    <row r="10" spans="2:24">
+      <c r="B10" s="232"/>
+      <c r="C10" s="234"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="234"/>
+      <c r="F10" s="234"/>
+      <c r="G10" s="234"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="234"/>
+      <c r="J10" s="234" t="s">
         <v>109</v>
       </c>
-      <c r="K9" s="226"/>
-      <c r="L9" s="226"/>
-      <c r="M9" s="230">
-        <v>45291</v>
-      </c>
-      <c r="N9" s="230">
-        <v>45657</v>
-      </c>
-      <c r="O9" s="230">
-        <v>46022</v>
-      </c>
-      <c r="P9" s="230">
-        <v>46387</v>
-      </c>
-      <c r="Q9" s="230">
-        <v>46752</v>
-      </c>
-      <c r="R9" s="230">
-        <v>47118</v>
-      </c>
-      <c r="S9" s="230">
-        <v>47483</v>
-      </c>
-      <c r="T9" s="230">
-        <v>47848</v>
-      </c>
-      <c r="U9" s="230">
-        <v>48213</v>
-      </c>
-      <c r="V9" s="230">
-        <v>48579</v>
-      </c>
-      <c r="W9" s="230">
-        <v>48944</v>
-      </c>
-      <c r="X9" s="230"/>
-    </row>
-    <row r="10" spans="2:24">
-      <c r="B10" s="233"/>
-      <c r="C10" s="235"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235" t="s">
+      <c r="K10" s="234"/>
+      <c r="L10" s="233"/>
+      <c r="M10" s="232">
+        <v>0</v>
+      </c>
+      <c r="N10" s="232">
+        <v>1</v>
+      </c>
+      <c r="O10" s="232">
+        <v>2</v>
+      </c>
+      <c r="P10" s="232">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="232">
+        <v>4</v>
+      </c>
+      <c r="R10" s="232">
+        <v>5</v>
+      </c>
+      <c r="S10" s="232">
+        <v>6</v>
+      </c>
+      <c r="T10" s="232">
+        <v>7</v>
+      </c>
+      <c r="U10" s="232">
+        <v>8</v>
+      </c>
+      <c r="V10" s="232">
+        <v>9</v>
+      </c>
+      <c r="W10" s="232">
+        <v>10</v>
+      </c>
+      <c r="X10" s="232"/>
+    </row>
+    <row r="12" spans="2:24">
+      <c r="C12" s="240" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="240" t="s">
         <v>110</v>
       </c>
-      <c r="K10" s="235"/>
-      <c r="L10" s="234"/>
-      <c r="M10" s="233">
-        <v>0</v>
-      </c>
-      <c r="N10" s="233">
+      <c r="K12" s="240"/>
+      <c r="L12" s="262"/>
+      <c r="M12" s="219"/>
+      <c r="N12" s="239"/>
+      <c r="O12" s="239"/>
+      <c r="P12" s="239"/>
+      <c r="Q12" s="239"/>
+      <c r="R12" s="239"/>
+      <c r="S12" s="239"/>
+      <c r="T12" s="239"/>
+      <c r="U12" s="239"/>
+      <c r="V12" s="239"/>
+      <c r="W12" s="239"/>
+    </row>
+    <row r="13" spans="2:24">
+      <c r="C13" s="219" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="227">
         <v>1</v>
       </c>
-      <c r="O10" s="233">
-        <v>2</v>
-      </c>
-      <c r="P10" s="233">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="233">
-        <v>4</v>
-      </c>
-      <c r="R10" s="233">
-        <v>5</v>
-      </c>
-      <c r="S10" s="233">
-        <v>6</v>
-      </c>
-      <c r="T10" s="233">
-        <v>7</v>
-      </c>
-      <c r="U10" s="233">
-        <v>8</v>
-      </c>
-      <c r="V10" s="233">
-        <v>9</v>
-      </c>
-      <c r="W10" s="233">
+      <c r="J13" s="247" t="s">
+        <v>112</v>
+      </c>
+      <c r="K13" s="247"/>
+      <c r="L13" s="247" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="275"/>
+      <c r="N13" s="266">
+        <v>0</v>
+      </c>
+      <c r="O13" s="266">
+        <v>0</v>
+      </c>
+      <c r="P13" s="266">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="266">
+        <v>0</v>
+      </c>
+      <c r="R13" s="266">
+        <v>0</v>
+      </c>
+      <c r="S13" s="266">
+        <v>0</v>
+      </c>
+      <c r="T13" s="266">
+        <v>10000000</v>
+      </c>
+      <c r="U13" s="266">
+        <v>0</v>
+      </c>
+      <c r="V13" s="266">
+        <v>0</v>
+      </c>
+      <c r="W13" s="266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24">
+      <c r="J14" s="244" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" s="244"/>
+      <c r="L14" s="245" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14" s="246"/>
+      <c r="N14" s="268">
+        <v>0</v>
+      </c>
+      <c r="O14" s="268">
+        <v>0</v>
+      </c>
+      <c r="P14" s="268">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="268">
+        <v>0</v>
+      </c>
+      <c r="R14" s="268">
+        <v>0</v>
+      </c>
+      <c r="S14" s="268">
+        <v>0</v>
+      </c>
+      <c r="T14" s="278">
         <v>10</v>
       </c>
-      <c r="X10" s="233"/>
-    </row>
-    <row r="12" spans="2:24">
-      <c r="C12" s="241" t="s">
-        <v>49</v>
-      </c>
-      <c r="J12" s="241" t="s">
-        <v>111</v>
-      </c>
-      <c r="K12" s="241"/>
-      <c r="L12" s="263"/>
-      <c r="M12" s="220"/>
-      <c r="N12" s="240"/>
-      <c r="O12" s="240"/>
-      <c r="P12" s="240"/>
-      <c r="Q12" s="240"/>
-      <c r="R12" s="240"/>
-      <c r="S12" s="240"/>
-      <c r="T12" s="240"/>
-      <c r="U12" s="240"/>
-      <c r="V12" s="240"/>
-      <c r="W12" s="240"/>
-    </row>
-    <row r="13" spans="2:24">
-      <c r="C13" s="220" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G13" s="228">
-        <v>1</v>
-      </c>
-      <c r="J13" s="248" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" s="248"/>
-      <c r="L13" s="248" t="s">
+      <c r="U14" s="268">
+        <v>0</v>
+      </c>
+      <c r="V14" s="268">
+        <v>0</v>
+      </c>
+      <c r="W14" s="268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24">
+      <c r="C15" s="219" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="250" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="250"/>
+      <c r="L15" s="275" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="276"/>
-      <c r="N13" s="267">
-        <v>0</v>
-      </c>
-      <c r="O13" s="267">
-        <v>0</v>
-      </c>
-      <c r="P13" s="267">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="267">
-        <v>0</v>
-      </c>
-      <c r="R13" s="267">
-        <v>0</v>
-      </c>
-      <c r="S13" s="267">
-        <v>0</v>
-      </c>
-      <c r="T13" s="267">
-        <v>10000000</v>
-      </c>
-      <c r="U13" s="267">
-        <v>0</v>
-      </c>
-      <c r="V13" s="267">
-        <v>0</v>
-      </c>
-      <c r="W13" s="267">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:24">
-      <c r="J14" s="245" t="s">
-        <v>114</v>
-      </c>
-      <c r="K14" s="245"/>
-      <c r="L14" s="246" t="s">
-        <v>115</v>
-      </c>
-      <c r="M14" s="247"/>
-      <c r="N14" s="269">
-        <v>0</v>
-      </c>
-      <c r="O14" s="269">
-        <v>0</v>
-      </c>
-      <c r="P14" s="269">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="269">
-        <v>0</v>
-      </c>
-      <c r="R14" s="269">
-        <v>0</v>
-      </c>
-      <c r="S14" s="269">
-        <v>0</v>
-      </c>
-      <c r="T14" s="279">
-        <v>10</v>
-      </c>
-      <c r="U14" s="269">
-        <v>0</v>
-      </c>
-      <c r="V14" s="269">
-        <v>0</v>
-      </c>
-      <c r="W14" s="269">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:24">
-      <c r="C15" s="220" t="s">
-        <v>116</v>
-      </c>
-      <c r="J15" s="251" t="s">
+      <c r="M15" s="250"/>
+      <c r="N15" s="258">
+        <v>0</v>
+      </c>
+      <c r="O15" s="258">
+        <v>0</v>
+      </c>
+      <c r="P15" s="258">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="258">
+        <v>0</v>
+      </c>
+      <c r="R15" s="258">
+        <v>0</v>
+      </c>
+      <c r="S15" s="258">
+        <v>0</v>
+      </c>
+      <c r="T15" s="266">
+        <v>100000000</v>
+      </c>
+      <c r="U15" s="258">
+        <v>0</v>
+      </c>
+      <c r="V15" s="258">
+        <v>0</v>
+      </c>
+      <c r="W15" s="258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="C16" s="221" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="221"/>
+      <c r="E16" s="221"/>
+      <c r="F16" s="221"/>
+      <c r="G16" s="227" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="K15" s="251"/>
-      <c r="L15" s="276" t="s">
+      <c r="K16" s="248"/>
+      <c r="L16" s="247" t="s">
         <v>62</v>
       </c>
-      <c r="M15" s="251"/>
-      <c r="N15" s="259">
-        <v>0</v>
-      </c>
-      <c r="O15" s="259">
-        <v>0</v>
-      </c>
-      <c r="P15" s="259">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="259">
-        <v>0</v>
-      </c>
-      <c r="R15" s="259">
-        <v>0</v>
-      </c>
-      <c r="S15" s="259">
-        <v>0</v>
-      </c>
-      <c r="T15" s="267">
-        <v>100000000</v>
-      </c>
-      <c r="U15" s="259">
-        <v>0</v>
-      </c>
-      <c r="V15" s="259">
-        <v>0</v>
-      </c>
-      <c r="W15" s="259">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:24">
-      <c r="C16" s="222" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
-      <c r="F16" s="222"/>
-      <c r="G16" s="228" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="249" t="s">
-        <v>118</v>
-      </c>
-      <c r="K16" s="249"/>
-      <c r="L16" s="248" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" s="251"/>
-      <c r="N16" s="268">
-        <v>0</v>
-      </c>
-      <c r="O16" s="268">
-        <v>0</v>
-      </c>
-      <c r="P16" s="268">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="268">
-        <v>0</v>
-      </c>
-      <c r="R16" s="268">
-        <v>0</v>
-      </c>
-      <c r="S16" s="268">
-        <v>0</v>
-      </c>
-      <c r="T16" s="268">
-        <v>0</v>
-      </c>
-      <c r="U16" s="268">
-        <v>0</v>
-      </c>
-      <c r="V16" s="268">
-        <v>0</v>
-      </c>
-      <c r="W16" s="268">
+      <c r="M16" s="250"/>
+      <c r="N16" s="267">
+        <v>0</v>
+      </c>
+      <c r="O16" s="267">
+        <v>0</v>
+      </c>
+      <c r="P16" s="267">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="267">
+        <v>0</v>
+      </c>
+      <c r="R16" s="267">
+        <v>0</v>
+      </c>
+      <c r="S16" s="267">
+        <v>0</v>
+      </c>
+      <c r="T16" s="267">
+        <v>0</v>
+      </c>
+      <c r="U16" s="267">
+        <v>0</v>
+      </c>
+      <c r="V16" s="267">
+        <v>0</v>
+      </c>
+      <c r="W16" s="267">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:24">
       <c r="C17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" t="s">
         <v>119</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" s="228">
+        <v>45291</v>
+      </c>
+      <c r="J17" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="229">
-        <v>45291</v>
-      </c>
-      <c r="J17" s="249" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" s="249"/>
-      <c r="L17" s="248" t="s">
+      <c r="K17" s="248"/>
+      <c r="L17" s="247" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="251"/>
-      <c r="N17" s="268">
-        <v>0</v>
-      </c>
-      <c r="O17" s="268">
-        <v>0</v>
-      </c>
-      <c r="P17" s="268">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="268">
-        <v>0</v>
-      </c>
-      <c r="R17" s="268">
-        <v>0</v>
-      </c>
-      <c r="S17" s="268">
-        <v>0</v>
-      </c>
-      <c r="T17" s="268">
-        <v>0</v>
-      </c>
-      <c r="U17" s="268">
-        <v>0</v>
-      </c>
-      <c r="V17" s="268">
-        <v>0</v>
-      </c>
-      <c r="W17" s="268">
+      <c r="M17" s="250"/>
+      <c r="N17" s="267">
+        <v>0</v>
+      </c>
+      <c r="O17" s="267">
+        <v>0</v>
+      </c>
+      <c r="P17" s="267">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="267">
+        <v>0</v>
+      </c>
+      <c r="R17" s="267">
+        <v>0</v>
+      </c>
+      <c r="S17" s="267">
+        <v>0</v>
+      </c>
+      <c r="T17" s="267">
+        <v>0</v>
+      </c>
+      <c r="U17" s="267">
+        <v>0</v>
+      </c>
+      <c r="V17" s="267">
+        <v>0</v>
+      </c>
+      <c r="W17" s="267">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:24">
       <c r="C18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" t="s">
         <v>122</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" s="227">
+        <v>7</v>
+      </c>
+      <c r="J18" s="251" t="s">
         <v>123</v>
       </c>
-      <c r="G18" s="228">
-        <v>7</v>
-      </c>
-      <c r="J18" s="252" t="s">
-        <v>124</v>
-      </c>
-      <c r="K18" s="252"/>
-      <c r="L18" s="253" t="s">
+      <c r="K18" s="251"/>
+      <c r="L18" s="252" t="s">
         <v>62</v>
       </c>
-      <c r="M18" s="252"/>
-      <c r="N18" s="270">
-        <v>0</v>
-      </c>
-      <c r="O18" s="270">
-        <v>0</v>
-      </c>
-      <c r="P18" s="270">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="270">
-        <v>0</v>
-      </c>
-      <c r="R18" s="270">
-        <v>0</v>
-      </c>
-      <c r="S18" s="270">
-        <v>0</v>
-      </c>
-      <c r="T18" s="271">
+      <c r="M18" s="251"/>
+      <c r="N18" s="269">
+        <v>0</v>
+      </c>
+      <c r="O18" s="269">
+        <v>0</v>
+      </c>
+      <c r="P18" s="269">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="269">
+        <v>0</v>
+      </c>
+      <c r="R18" s="269">
+        <v>0</v>
+      </c>
+      <c r="S18" s="269">
+        <v>0</v>
+      </c>
+      <c r="T18" s="270">
         <v>100000000</v>
       </c>
-      <c r="U18" s="270">
-        <v>0</v>
-      </c>
-      <c r="V18" s="270">
-        <v>0</v>
-      </c>
-      <c r="W18" s="270">
+      <c r="U18" s="269">
+        <v>0</v>
+      </c>
+      <c r="V18" s="269">
+        <v>0</v>
+      </c>
+      <c r="W18" s="269">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:24">
       <c r="C19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="256" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="243">
+        <v>10000000</v>
+      </c>
+      <c r="J19" t="s">
         <v>125</v>
       </c>
-      <c r="E19" s="257" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="244">
-        <v>10000000</v>
-      </c>
-      <c r="J19" t="s">
-        <v>126</v>
-      </c>
-      <c r="L19" s="258" t="s">
+      <c r="L19" s="257" t="s">
         <v>77</v>
       </c>
-      <c r="M19" s="220"/>
-      <c r="N19" s="236">
+      <c r="M19" s="219"/>
+      <c r="N19" s="235">
         <v>1</v>
       </c>
-      <c r="O19" s="236">
+      <c r="O19" s="235">
         <v>2</v>
       </c>
-      <c r="P19" s="236">
+      <c r="P19" s="235">
         <v>3</v>
       </c>
-      <c r="Q19" s="236">
+      <c r="Q19" s="235">
         <v>4</v>
       </c>
-      <c r="R19" s="236">
+      <c r="R19" s="235">
         <v>5</v>
       </c>
-      <c r="S19" s="236">
+      <c r="S19" s="235">
         <v>6</v>
       </c>
-      <c r="T19" s="280">
+      <c r="T19" s="279">
         <v>7</v>
       </c>
-      <c r="U19" s="236">
+      <c r="U19" s="235">
         <v>8</v>
       </c>
-      <c r="V19" s="236">
+      <c r="V19" s="235">
         <v>9</v>
       </c>
-      <c r="W19" s="236">
+      <c r="W19" s="235">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="2:24">
       <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" t="s">
         <v>114</v>
       </c>
-      <c r="E20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G20" s="242">
+      <c r="G20" s="241">
         <v>10</v>
       </c>
       <c r="J20" t="s">
+        <v>126</v>
+      </c>
+      <c r="L20" s="257" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="219"/>
+      <c r="N20" s="260">
+        <v>0.25</v>
+      </c>
+      <c r="O20" s="260">
+        <v>0.25</v>
+      </c>
+      <c r="P20" s="260">
+        <v>0.25</v>
+      </c>
+      <c r="Q20" s="260">
+        <v>0.25</v>
+      </c>
+      <c r="R20" s="260">
+        <v>0.25</v>
+      </c>
+      <c r="S20" s="260">
+        <v>0.25</v>
+      </c>
+      <c r="T20" s="238">
+        <v>0.25</v>
+      </c>
+      <c r="U20" s="260">
+        <v>0.25</v>
+      </c>
+      <c r="V20" s="260">
+        <v>0.25</v>
+      </c>
+      <c r="W20" s="260">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24">
+      <c r="B21" s="276"/>
+      <c r="C21" t="s">
         <v>127</v>
       </c>
-      <c r="L20" s="258" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="220"/>
-      <c r="N20" s="261">
-        <v>0.25</v>
-      </c>
-      <c r="O20" s="261">
-        <v>0.25</v>
-      </c>
-      <c r="P20" s="261">
-        <v>0.25</v>
-      </c>
-      <c r="Q20" s="261">
-        <v>0.25</v>
-      </c>
-      <c r="R20" s="261">
-        <v>0.25</v>
-      </c>
-      <c r="S20" s="261">
-        <v>0.25</v>
-      </c>
-      <c r="T20" s="239">
-        <v>0.25</v>
-      </c>
-      <c r="U20" s="261">
-        <v>0.25</v>
-      </c>
-      <c r="V20" s="261">
-        <v>0.25</v>
-      </c>
-      <c r="W20" s="261">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="21" spans="2:24">
-      <c r="B21" s="277"/>
-      <c r="C21" t="s">
+      <c r="E21" s="256" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="243">
+        <v>0</v>
+      </c>
+      <c r="J21" s="224" t="s">
         <v>128</v>
       </c>
-      <c r="E21" s="257" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="244">
-        <v>0</v>
-      </c>
-      <c r="J21" s="225" t="s">
-        <v>129</v>
-      </c>
-      <c r="K21" s="225"/>
-      <c r="L21" s="232" t="s">
-        <v>115</v>
-      </c>
-      <c r="M21" s="231"/>
-      <c r="N21" s="262">
+      <c r="K21" s="224"/>
+      <c r="L21" s="231" t="s">
+        <v>114</v>
+      </c>
+      <c r="M21" s="230"/>
+      <c r="N21" s="261">
         <v>0.8</v>
       </c>
-      <c r="O21" s="262">
+      <c r="O21" s="261">
         <v>0.64</v>
       </c>
-      <c r="P21" s="262">
+      <c r="P21" s="261">
         <v>0.51200000000000001</v>
       </c>
-      <c r="Q21" s="262">
+      <c r="Q21" s="261">
         <v>0.40960000000000002</v>
       </c>
-      <c r="R21" s="262">
+      <c r="R21" s="261">
         <v>0.32768000000000003</v>
       </c>
-      <c r="S21" s="262">
+      <c r="S21" s="261">
         <v>0.26214399999999999</v>
       </c>
-      <c r="T21" s="281">
+      <c r="T21" s="280">
         <v>0.20971519999999999</v>
       </c>
-      <c r="U21" s="262">
+      <c r="U21" s="261">
         <v>0.16777216</v>
       </c>
-      <c r="V21" s="262">
+      <c r="V21" s="261">
         <v>0.13421772800000001</v>
       </c>
-      <c r="W21" s="262">
+      <c r="W21" s="261">
         <v>0.1073741824</v>
       </c>
-      <c r="X21" s="277"/>
+      <c r="X21" s="276"/>
     </row>
     <row r="22" spans="2:24">
       <c r="C22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="256" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="243">
+        <v>0</v>
+      </c>
+      <c r="J22" s="250" t="s">
         <v>130</v>
       </c>
-      <c r="E22" s="257" t="s">
+      <c r="K22" s="250"/>
+      <c r="L22" s="249" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="244">
-        <v>0</v>
-      </c>
-      <c r="J22" s="251" t="s">
+      <c r="M22" s="250"/>
+      <c r="N22" s="258">
+        <v>0</v>
+      </c>
+      <c r="O22" s="258">
+        <v>0</v>
+      </c>
+      <c r="P22" s="258">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="258">
+        <v>0</v>
+      </c>
+      <c r="R22" s="258">
+        <v>0</v>
+      </c>
+      <c r="S22" s="258">
+        <v>0</v>
+      </c>
+      <c r="T22" s="266">
+        <v>20971520</v>
+      </c>
+      <c r="U22" s="258">
+        <v>0</v>
+      </c>
+      <c r="V22" s="258">
+        <v>0</v>
+      </c>
+      <c r="W22" s="258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24">
+      <c r="B23" s="219"/>
+      <c r="C23" t="s">
         <v>131</v>
-      </c>
-      <c r="K22" s="251"/>
-      <c r="L22" s="250" t="s">
-        <v>62</v>
-      </c>
-      <c r="M22" s="251"/>
-      <c r="N22" s="259">
-        <v>0</v>
-      </c>
-      <c r="O22" s="259">
-        <v>0</v>
-      </c>
-      <c r="P22" s="259">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="259">
-        <v>0</v>
-      </c>
-      <c r="R22" s="259">
-        <v>0</v>
-      </c>
-      <c r="S22" s="259">
-        <v>0</v>
-      </c>
-      <c r="T22" s="267">
-        <v>20971520</v>
-      </c>
-      <c r="U22" s="259">
-        <v>0</v>
-      </c>
-      <c r="V22" s="259">
-        <v>0</v>
-      </c>
-      <c r="W22" s="259">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:24">
-      <c r="B23" s="220"/>
-      <c r="C23" t="s">
-        <v>132</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
       </c>
-      <c r="G23" s="227">
+      <c r="G23" s="226">
         <v>0.25</v>
       </c>
-      <c r="J23" s="264" t="s">
+      <c r="J23" s="263" t="s">
+        <v>132</v>
+      </c>
+      <c r="K23" s="263"/>
+      <c r="L23" s="264" t="s">
+        <v>62</v>
+      </c>
+      <c r="M23" s="265">
+        <v>20971520</v>
+      </c>
+      <c r="N23" s="259"/>
+      <c r="O23" s="259"/>
+      <c r="P23" s="259"/>
+      <c r="Q23" s="259"/>
+      <c r="R23" s="259"/>
+      <c r="S23" s="259"/>
+      <c r="T23" s="259"/>
+      <c r="U23" s="259"/>
+      <c r="V23" s="259"/>
+      <c r="W23" s="259"/>
+      <c r="X23" s="219"/>
+    </row>
+    <row r="24" spans="2:24">
+      <c r="O24" s="259"/>
+      <c r="P24" s="259"/>
+      <c r="Q24" s="259"/>
+      <c r="R24" s="259"/>
+      <c r="S24" s="259"/>
+      <c r="T24" s="259"/>
+      <c r="U24" s="259"/>
+      <c r="V24" s="259"/>
+      <c r="W24" s="259"/>
+    </row>
+    <row r="25" spans="2:24">
+      <c r="C25" s="224"/>
+      <c r="D25" s="224"/>
+      <c r="E25" s="224"/>
+      <c r="F25" s="224"/>
+      <c r="G25" s="224"/>
+      <c r="H25" s="224"/>
+      <c r="I25" s="224"/>
+      <c r="J25" s="224"/>
+      <c r="K25" s="224"/>
+      <c r="L25" s="224"/>
+      <c r="M25" s="224"/>
+      <c r="N25" s="224"/>
+      <c r="O25" s="224"/>
+      <c r="P25" s="224"/>
+      <c r="Q25" s="224"/>
+      <c r="R25" s="224"/>
+      <c r="S25" s="224"/>
+      <c r="T25" s="224"/>
+      <c r="U25" s="224"/>
+      <c r="V25" s="224"/>
+      <c r="W25" s="224"/>
+    </row>
+    <row r="27" spans="2:24">
+      <c r="C27" s="240" t="s">
         <v>133</v>
       </c>
-      <c r="K23" s="264"/>
-      <c r="L23" s="265" t="s">
-        <v>62</v>
-      </c>
-      <c r="M23" s="266">
-        <v>20971520</v>
-      </c>
-      <c r="N23" s="260"/>
-      <c r="O23" s="260"/>
-      <c r="P23" s="260"/>
-      <c r="Q23" s="260"/>
-      <c r="R23" s="260"/>
-      <c r="S23" s="260"/>
-      <c r="T23" s="260"/>
-      <c r="U23" s="260"/>
-      <c r="V23" s="260"/>
-      <c r="W23" s="260"/>
-      <c r="X23" s="220"/>
-    </row>
-    <row r="24" spans="2:24">
-      <c r="O24" s="260"/>
-      <c r="P24" s="260"/>
-      <c r="Q24" s="260"/>
-      <c r="R24" s="260"/>
-      <c r="S24" s="260"/>
-      <c r="T24" s="260"/>
-      <c r="U24" s="260"/>
-      <c r="V24" s="260"/>
-      <c r="W24" s="260"/>
-    </row>
-    <row r="25" spans="2:24">
-      <c r="C25" s="225"/>
-      <c r="D25" s="225"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="225"/>
-      <c r="G25" s="225"/>
-      <c r="H25" s="225"/>
-      <c r="I25" s="225"/>
-      <c r="J25" s="225"/>
-      <c r="K25" s="225"/>
-      <c r="L25" s="225"/>
-      <c r="M25" s="225"/>
-      <c r="N25" s="225"/>
-      <c r="O25" s="225"/>
-      <c r="P25" s="225"/>
-      <c r="Q25" s="225"/>
-      <c r="R25" s="225"/>
-      <c r="S25" s="225"/>
-      <c r="T25" s="225"/>
-      <c r="U25" s="225"/>
-      <c r="V25" s="225"/>
-      <c r="W25" s="225"/>
-    </row>
-    <row r="27" spans="2:24">
-      <c r="C27" s="241" t="s">
+      <c r="J27" s="240" t="s">
         <v>134</v>
       </c>
-      <c r="J27" s="241" t="s">
-        <v>135</v>
-      </c>
-      <c r="K27" s="241"/>
-      <c r="L27" s="220"/>
+      <c r="K27" s="240"/>
+      <c r="L27" s="219"/>
     </row>
     <row r="28" spans="2:24">
       <c r="C28" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" t="s">
         <v>136</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" s="226">
+        <v>0.1</v>
+      </c>
+      <c r="J28" s="219" t="s">
         <v>137</v>
       </c>
-      <c r="G28" s="227">
-        <v>0.1</v>
-      </c>
-      <c r="J28" s="220" t="s">
-        <v>138</v>
-      </c>
-      <c r="K28" s="220"/>
-      <c r="L28" s="276" t="s">
+      <c r="K28" s="219"/>
+      <c r="L28" s="275" t="s">
         <v>62</v>
       </c>
-      <c r="M28" s="259">
-        <v>0</v>
-      </c>
-      <c r="N28" s="259">
-        <v>0</v>
-      </c>
-      <c r="O28" s="259">
-        <v>0</v>
-      </c>
-      <c r="P28" s="259">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="259">
-        <v>0</v>
-      </c>
-      <c r="R28" s="259">
-        <v>0</v>
-      </c>
-      <c r="S28" s="267">
-        <v>0</v>
-      </c>
-      <c r="T28" s="259">
+      <c r="M28" s="258">
+        <v>0</v>
+      </c>
+      <c r="N28" s="258">
+        <v>0</v>
+      </c>
+      <c r="O28" s="258">
+        <v>0</v>
+      </c>
+      <c r="P28" s="258">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="258">
+        <v>0</v>
+      </c>
+      <c r="R28" s="258">
+        <v>0</v>
+      </c>
+      <c r="S28" s="266">
+        <v>0</v>
+      </c>
+      <c r="T28" s="258">
         <v>100000000</v>
       </c>
-      <c r="U28" s="259">
-        <v>0</v>
-      </c>
-      <c r="V28" s="259">
-        <v>0</v>
-      </c>
-      <c r="W28" s="259">
+      <c r="U28" s="258">
+        <v>0</v>
+      </c>
+      <c r="V28" s="258">
+        <v>0</v>
+      </c>
+      <c r="W28" s="258">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:24">
       <c r="C29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" s="274">
+        <v>0</v>
+      </c>
+      <c r="J29" s="219" t="s">
         <v>139</v>
       </c>
-      <c r="E29" t="s">
-        <v>137</v>
-      </c>
-      <c r="G29" s="275">
-        <v>0</v>
-      </c>
-      <c r="J29" s="220" t="s">
-        <v>140</v>
-      </c>
-      <c r="K29" s="220"/>
-      <c r="L29" s="220" t="s">
+      <c r="K29" s="219"/>
+      <c r="L29" s="219" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="272">
+      <c r="M29" s="271">
         <v>0.1</v>
       </c>
-      <c r="N29" s="272">
+      <c r="N29" s="271">
         <v>0.1</v>
       </c>
-      <c r="O29" s="272">
+      <c r="O29" s="271">
         <v>0.1</v>
       </c>
-      <c r="P29" s="272">
+      <c r="P29" s="271">
         <v>0.1</v>
       </c>
-      <c r="Q29" s="273">
+      <c r="Q29" s="272">
         <v>0.1</v>
       </c>
-      <c r="R29" s="272">
+      <c r="R29" s="271">
         <v>0.1</v>
       </c>
-      <c r="S29" s="272">
+      <c r="S29" s="271">
         <v>0.1</v>
       </c>
-      <c r="T29" s="272">
+      <c r="T29" s="271">
         <v>0.1</v>
       </c>
-      <c r="U29" s="272">
-        <v>0</v>
-      </c>
-      <c r="V29" s="272">
-        <v>0</v>
-      </c>
-      <c r="W29" s="272">
+      <c r="U29" s="271">
+        <v>0</v>
+      </c>
+      <c r="V29" s="271">
+        <v>0</v>
+      </c>
+      <c r="W29" s="271">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:24">
       <c r="C30" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="226">
+        <v>0.1</v>
+      </c>
+      <c r="M30" s="253"/>
+      <c r="N30" s="253"/>
+      <c r="O30" s="253"/>
+      <c r="P30" s="253"/>
+      <c r="Q30" s="253"/>
+      <c r="R30" s="253"/>
+      <c r="S30" s="253"/>
+      <c r="T30" s="253"/>
+      <c r="U30" s="253"/>
+      <c r="V30" s="253"/>
+      <c r="W30" s="253"/>
+    </row>
+    <row r="31" spans="2:24">
+      <c r="J31" s="219" t="s">
         <v>141</v>
       </c>
-      <c r="E30" t="s">
-        <v>137</v>
-      </c>
-      <c r="G30" s="227">
-        <v>0.1</v>
-      </c>
-      <c r="M30" s="254"/>
-      <c r="N30" s="254"/>
-      <c r="O30" s="254"/>
-      <c r="P30" s="254"/>
-      <c r="Q30" s="254"/>
-      <c r="R30" s="254"/>
-      <c r="S30" s="254"/>
-      <c r="T30" s="254"/>
-      <c r="U30" s="254"/>
-      <c r="V30" s="254"/>
-      <c r="W30" s="254"/>
-    </row>
-    <row r="31" spans="2:24">
-      <c r="J31" s="220" t="s">
-        <v>142</v>
-      </c>
-      <c r="K31" s="220"/>
-      <c r="M31" s="254"/>
-      <c r="N31" s="254"/>
-      <c r="O31" s="254"/>
-      <c r="P31" s="254"/>
-      <c r="Q31" s="254"/>
-      <c r="R31" s="254"/>
-      <c r="S31" s="254"/>
-      <c r="T31" s="254"/>
-      <c r="U31" s="254"/>
-      <c r="V31" s="254"/>
-      <c r="W31" s="254"/>
+      <c r="K31" s="219"/>
+      <c r="M31" s="253"/>
+      <c r="N31" s="253"/>
+      <c r="O31" s="253"/>
+      <c r="P31" s="253"/>
+      <c r="Q31" s="253"/>
+      <c r="R31" s="253"/>
+      <c r="S31" s="253"/>
+      <c r="T31" s="253"/>
+      <c r="U31" s="253"/>
+      <c r="V31" s="253"/>
+      <c r="W31" s="253"/>
     </row>
     <row r="32" spans="2:24">
       <c r="J32" t="s">
         <v>66</v>
       </c>
-      <c r="L32" s="248" t="s">
+      <c r="L32" s="247" t="s">
         <v>62</v>
       </c>
-      <c r="M32" s="259">
+      <c r="M32" s="258">
         <v>-2097152</v>
       </c>
-      <c r="N32" s="259"/>
-      <c r="O32" s="259"/>
-      <c r="P32" s="259"/>
-      <c r="Q32" s="259"/>
-      <c r="R32" s="259"/>
-      <c r="S32" s="267"/>
-      <c r="T32" s="259"/>
-      <c r="U32" s="259"/>
-      <c r="V32" s="259"/>
-      <c r="W32" s="259"/>
+      <c r="N32" s="258"/>
+      <c r="O32" s="258"/>
+      <c r="P32" s="258"/>
+      <c r="Q32" s="258"/>
+      <c r="R32" s="258"/>
+      <c r="S32" s="266"/>
+      <c r="T32" s="258"/>
+      <c r="U32" s="258"/>
+      <c r="V32" s="258"/>
+      <c r="W32" s="258"/>
     </row>
     <row r="33" spans="2:24">
       <c r="J33" t="s">
+        <v>142</v>
+      </c>
+      <c r="L33" s="247" t="s">
+        <v>62</v>
+      </c>
+      <c r="M33" s="258">
+        <v>0</v>
+      </c>
+      <c r="N33" s="258">
+        <v>0</v>
+      </c>
+      <c r="O33" s="258">
+        <v>0</v>
+      </c>
+      <c r="P33" s="258">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="258">
+        <v>0</v>
+      </c>
+      <c r="R33" s="258">
+        <v>0</v>
+      </c>
+      <c r="S33" s="266">
+        <v>0</v>
+      </c>
+      <c r="T33" s="258">
+        <v>10000000</v>
+      </c>
+      <c r="U33" s="258">
+        <v>0</v>
+      </c>
+      <c r="V33" s="258">
+        <v>0</v>
+      </c>
+      <c r="W33" s="258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24">
+      <c r="J34" s="242" t="s">
+        <v>141</v>
+      </c>
+      <c r="K34" s="242"/>
+      <c r="L34" s="255" t="s">
+        <v>62</v>
+      </c>
+      <c r="M34" s="269">
+        <v>-2097152</v>
+      </c>
+      <c r="N34" s="269">
+        <v>0</v>
+      </c>
+      <c r="O34" s="269">
+        <v>0</v>
+      </c>
+      <c r="P34" s="269">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="269">
+        <v>0</v>
+      </c>
+      <c r="R34" s="269">
+        <v>0</v>
+      </c>
+      <c r="S34" s="270">
+        <v>0</v>
+      </c>
+      <c r="T34" s="269">
+        <v>10000000</v>
+      </c>
+      <c r="U34" s="269">
+        <v>0</v>
+      </c>
+      <c r="V34" s="269">
+        <v>0</v>
+      </c>
+      <c r="W34" s="269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24">
+      <c r="J35" s="281" t="s">
         <v>143</v>
       </c>
-      <c r="L33" s="248" t="s">
-        <v>62</v>
-      </c>
-      <c r="M33" s="259">
-        <v>0</v>
-      </c>
-      <c r="N33" s="259">
-        <v>0</v>
-      </c>
-      <c r="O33" s="259">
-        <v>0</v>
-      </c>
-      <c r="P33" s="259">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="259">
-        <v>0</v>
-      </c>
-      <c r="R33" s="259">
-        <v>0</v>
-      </c>
-      <c r="S33" s="267">
-        <v>0</v>
-      </c>
-      <c r="T33" s="259">
-        <v>10000000</v>
-      </c>
-      <c r="U33" s="259">
-        <v>0</v>
-      </c>
-      <c r="V33" s="259">
-        <v>0</v>
-      </c>
-      <c r="W33" s="259">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24">
-      <c r="J34" s="243" t="s">
-        <v>142</v>
-      </c>
-      <c r="K34" s="243"/>
-      <c r="L34" s="256" t="s">
-        <v>62</v>
-      </c>
-      <c r="M34" s="270">
-        <v>-2097152</v>
-      </c>
-      <c r="N34" s="270">
-        <v>0</v>
-      </c>
-      <c r="O34" s="270">
-        <v>0</v>
-      </c>
-      <c r="P34" s="270">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="270">
-        <v>0</v>
-      </c>
-      <c r="R34" s="270">
-        <v>0</v>
-      </c>
-      <c r="S34" s="271">
-        <v>0</v>
-      </c>
-      <c r="T34" s="270">
-        <v>10000000</v>
-      </c>
-      <c r="U34" s="270">
-        <v>0</v>
-      </c>
-      <c r="V34" s="270">
-        <v>0</v>
-      </c>
-      <c r="W34" s="270">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:24">
-      <c r="J35" s="282" t="s">
+      <c r="K35" s="281"/>
+      <c r="L35" s="281" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="282">
+        <v>0.24999999999999978</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24">
+      <c r="J36" s="219" t="s">
         <v>144</v>
       </c>
-      <c r="K35" s="282"/>
-      <c r="L35" s="282" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="283">
-        <v>0.24999999999999978</v>
-      </c>
-    </row>
-    <row r="36" spans="2:24">
-      <c r="J36" s="220" t="s">
+      <c r="L36" t="s">
         <v>145</v>
       </c>
-      <c r="L36" t="s">
-        <v>146</v>
-      </c>
-      <c r="M36" s="284">
+      <c r="M36" s="283">
         <v>4.76837158203125</v>
       </c>
     </row>
     <row r="37" spans="2:24">
-      <c r="B37" s="225"/>
-      <c r="C37" s="225"/>
-      <c r="D37" s="225"/>
-      <c r="E37" s="225"/>
-      <c r="F37" s="225"/>
-      <c r="G37" s="225"/>
-      <c r="H37" s="225"/>
-      <c r="I37" s="225"/>
-      <c r="J37" s="225"/>
-      <c r="K37" s="225"/>
-      <c r="L37" s="225"/>
-      <c r="M37" s="225"/>
-      <c r="N37" s="225"/>
-      <c r="O37" s="225"/>
-      <c r="P37" s="225"/>
-      <c r="Q37" s="225"/>
-      <c r="R37" s="225"/>
-      <c r="S37" s="225"/>
-      <c r="T37" s="225"/>
-      <c r="U37" s="225"/>
-      <c r="V37" s="225"/>
-      <c r="W37" s="225"/>
-      <c r="X37" s="225"/>
+      <c r="B37" s="224"/>
+      <c r="C37" s="224"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="224"/>
+      <c r="F37" s="224"/>
+      <c r="G37" s="224"/>
+      <c r="H37" s="224"/>
+      <c r="I37" s="224"/>
+      <c r="J37" s="224"/>
+      <c r="K37" s="224"/>
+      <c r="L37" s="224"/>
+      <c r="M37" s="224"/>
+      <c r="N37" s="224"/>
+      <c r="O37" s="224"/>
+      <c r="P37" s="224"/>
+      <c r="Q37" s="224"/>
+      <c r="R37" s="224"/>
+      <c r="S37" s="224"/>
+      <c r="T37" s="224"/>
+      <c r="U37" s="224"/>
+      <c r="V37" s="224"/>
+      <c r="W37" s="224"/>
+      <c r="X37" s="224"/>
     </row>
     <row r="38" spans="2:24">
-      <c r="C38" s="221" t="s">
+      <c r="C38" s="220" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="221"/>
+      <c r="D38" s="220"/>
     </row>
     <row r="39" spans="2:24">
-      <c r="C39" s="278" t="s">
+      <c r="C39" s="277" t="s">
         <v>48</v>
       </c>
-      <c r="D39" s="223"/>
+      <c r="D39" s="222"/>
     </row>
     <row r="42" spans="2:24">
-      <c r="H42" s="220"/>
-      <c r="J42" s="220"/>
-      <c r="K42" s="220"/>
-      <c r="L42" s="220"/>
+      <c r="H42" s="219"/>
+      <c r="J42" s="219"/>
+      <c r="K42" s="219"/>
+      <c r="L42" s="219"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/templates/finance/wacc-calculator.xlsx
+++ b/templates/finance/wacc-calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sheetxl\workbook-templates\templates\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DFA176-C64C-4BF9-9D7B-9242E6B19797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3B1626-34D0-4D92-A7C4-E17CE1C81589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="210" windowWidth="22695" windowHeight="12375" activeTab="3" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
+    <workbookView xWindow="3330" yWindow="210" windowWidth="22695" windowHeight="12375" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
   </bookViews>
   <sheets>
     <sheet name="WACC" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="148">
   <si>
     <t>Notes</t>
   </si>
@@ -482,6 +482,9 @@
   </si>
   <si>
     <t>https://www.efinancialmodels.com</t>
+  </si>
+  <si>
+    <t>https://www.eFinancialModels.com</t>
   </si>
 </sst>
 </file>
@@ -509,7 +512,7 @@
     <numFmt numFmtId="179" formatCode="_(* #,##0.0\x_);_(* \(#,##0.0\x\);_(* &quot;-&quot;?_);_(@_)"/>
     <numFmt numFmtId="180" formatCode="_(* #,##0.0%_);_(* \(#,##0.0%\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="68">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -966,15 +969,6 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2078,7 +2072,6 @@
     </xf>
     <xf numFmtId="3" fontId="19" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="11" applyFont="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2088,6 +2081,18 @@
     </xf>
     <xf numFmtId="178" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="59" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="59" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="59" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2104,18 +2109,7 @@
     <xf numFmtId="173" fontId="48" fillId="0" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="59" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="59" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="59" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3879,14 +3873,14 @@
       <c r="B14" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="285" t="s">
+      <c r="C14" s="288" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="285"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="285"/>
-      <c r="G14" s="285"/>
-      <c r="H14" s="285"/>
+      <c r="D14" s="288"/>
+      <c r="E14" s="288"/>
+      <c r="F14" s="288"/>
+      <c r="G14" s="288"/>
+      <c r="H14" s="288"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -3920,7 +3914,7 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="2:21">
-      <c r="B16" s="284" t="s">
+      <c r="B16" s="287" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="58">
@@ -3955,7 +3949,7 @@
       <c r="U16"/>
     </row>
     <row r="17" spans="2:21">
-      <c r="B17" s="284"/>
+      <c r="B17" s="287"/>
       <c r="C17" s="58">
         <f>+C16+5%</f>
         <v>0.1</v>
@@ -4001,7 +3995,7 @@
       <c r="U17"/>
     </row>
     <row r="18" spans="2:21">
-      <c r="B18" s="284"/>
+      <c r="B18" s="287"/>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C26" si="1">+C17+10%</f>
         <v>0.2</v>
@@ -4049,7 +4043,7 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21">
-      <c r="B19" s="284"/>
+      <c r="B19" s="287"/>
       <c r="C19" s="58">
         <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
@@ -4097,7 +4091,7 @@
       <c r="U19"/>
     </row>
     <row r="20" spans="2:21">
-      <c r="B20" s="284"/>
+      <c r="B20" s="287"/>
       <c r="C20" s="58">
         <f t="shared" si="1"/>
         <v>0.4</v>
@@ -4145,7 +4139,7 @@
       <c r="U20"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="B21" s="284"/>
+      <c r="B21" s="287"/>
       <c r="C21" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
@@ -4193,7 +4187,7 @@
       <c r="U21"/>
     </row>
     <row r="22" spans="2:21">
-      <c r="B22" s="284"/>
+      <c r="B22" s="287"/>
       <c r="C22" s="58">
         <f t="shared" si="1"/>
         <v>0.6</v>
@@ -4241,7 +4235,7 @@
       <c r="U22"/>
     </row>
     <row r="23" spans="2:21">
-      <c r="B23" s="284"/>
+      <c r="B23" s="287"/>
       <c r="C23" s="58">
         <f t="shared" si="1"/>
         <v>0.7</v>
@@ -4287,7 +4281,7 @@
       <c r="U23"/>
     </row>
     <row r="24" spans="2:21">
-      <c r="B24" s="284"/>
+      <c r="B24" s="287"/>
       <c r="C24" s="58">
         <f t="shared" si="1"/>
         <v>0.79999999999999993</v>
@@ -4312,7 +4306,7 @@
       <c r="U24"/>
     </row>
     <row r="25" spans="2:21">
-      <c r="B25" s="284"/>
+      <c r="B25" s="287"/>
       <c r="C25" s="58">
         <f t="shared" si="1"/>
         <v>0.89999999999999991</v>
@@ -4344,7 +4338,7 @@
       <c r="U25"/>
     </row>
     <row r="26" spans="2:21">
-      <c r="B26" s="284"/>
+      <c r="B26" s="287"/>
       <c r="C26" s="58">
         <f t="shared" si="1"/>
         <v>0.99999999999999989</v>
@@ -4824,11 +4818,11 @@
       <c r="F9" s="116"/>
       <c r="G9" s="116"/>
       <c r="H9" s="115"/>
-      <c r="I9" s="286">
+      <c r="I9" s="289">
         <v>4.2087912087912089</v>
       </c>
-      <c r="J9" s="287"/>
-      <c r="K9" s="288"/>
+      <c r="J9" s="290"/>
+      <c r="K9" s="291"/>
       <c r="L9" s="116"/>
       <c r="M9" s="116"/>
       <c r="N9" s="116"/>
@@ -4863,9 +4857,9 @@
       <c r="F10" s="116"/>
       <c r="G10" s="116"/>
       <c r="H10" s="115"/>
-      <c r="I10" s="286"/>
-      <c r="J10" s="287"/>
-      <c r="K10" s="288"/>
+      <c r="I10" s="289"/>
+      <c r="J10" s="290"/>
+      <c r="K10" s="291"/>
       <c r="L10" s="116"/>
       <c r="M10" s="116"/>
       <c r="N10" s="116"/>
@@ -4896,9 +4890,9 @@
       <c r="F11" s="116"/>
       <c r="G11" s="116"/>
       <c r="H11" s="115"/>
-      <c r="I11" s="286"/>
-      <c r="J11" s="287"/>
-      <c r="K11" s="288"/>
+      <c r="I11" s="289"/>
+      <c r="J11" s="290"/>
+      <c r="K11" s="291"/>
       <c r="L11" s="116"/>
       <c r="M11" s="116"/>
       <c r="N11" s="116"/>
@@ -4929,9 +4923,9 @@
       <c r="F12" s="116"/>
       <c r="G12" s="116"/>
       <c r="H12" s="115"/>
-      <c r="I12" s="286"/>
-      <c r="J12" s="287"/>
-      <c r="K12" s="288"/>
+      <c r="I12" s="289"/>
+      <c r="J12" s="290"/>
+      <c r="K12" s="291"/>
       <c r="L12" s="116"/>
       <c r="M12" s="116"/>
       <c r="N12" s="116"/>
@@ -4964,9 +4958,9 @@
       <c r="F13" s="116"/>
       <c r="G13" s="116"/>
       <c r="H13" s="115"/>
-      <c r="I13" s="286"/>
-      <c r="J13" s="287"/>
-      <c r="K13" s="288"/>
+      <c r="I13" s="289"/>
+      <c r="J13" s="290"/>
+      <c r="K13" s="291"/>
       <c r="L13" s="116"/>
       <c r="M13" s="116"/>
       <c r="N13" s="116"/>
@@ -5001,9 +4995,9 @@
       <c r="F14" s="116"/>
       <c r="G14" s="116"/>
       <c r="H14" s="115"/>
-      <c r="I14" s="286"/>
-      <c r="J14" s="287"/>
-      <c r="K14" s="288"/>
+      <c r="I14" s="289"/>
+      <c r="J14" s="290"/>
+      <c r="K14" s="291"/>
       <c r="L14" s="116"/>
       <c r="M14" s="116"/>
       <c r="N14" s="116"/>
@@ -5034,9 +5028,9 @@
       <c r="F15" s="116"/>
       <c r="G15" s="116"/>
       <c r="H15" s="115"/>
-      <c r="I15" s="286"/>
-      <c r="J15" s="287"/>
-      <c r="K15" s="288"/>
+      <c r="I15" s="289"/>
+      <c r="J15" s="290"/>
+      <c r="K15" s="291"/>
       <c r="L15" s="116"/>
       <c r="M15" s="116"/>
       <c r="N15" s="116"/>
@@ -5071,9 +5065,9 @@
       <c r="F16" s="116"/>
       <c r="G16" s="120"/>
       <c r="H16" s="115"/>
-      <c r="I16" s="286"/>
-      <c r="J16" s="287"/>
-      <c r="K16" s="288"/>
+      <c r="I16" s="289"/>
+      <c r="J16" s="290"/>
+      <c r="K16" s="291"/>
       <c r="L16" s="116"/>
       <c r="M16" s="116"/>
       <c r="N16" s="116"/>
@@ -5110,9 +5104,9 @@
         <v>100000</v>
       </c>
       <c r="H17" s="115"/>
-      <c r="I17" s="286"/>
-      <c r="J17" s="287"/>
-      <c r="K17" s="288"/>
+      <c r="I17" s="289"/>
+      <c r="J17" s="290"/>
+      <c r="K17" s="291"/>
       <c r="L17" s="116"/>
       <c r="M17" s="116"/>
       <c r="N17" s="116"/>
@@ -5149,9 +5143,9 @@
         <v>20000</v>
       </c>
       <c r="H18" s="115"/>
-      <c r="I18" s="286"/>
-      <c r="J18" s="287"/>
-      <c r="K18" s="288"/>
+      <c r="I18" s="289"/>
+      <c r="J18" s="290"/>
+      <c r="K18" s="291"/>
       <c r="L18" s="116"/>
       <c r="M18" s="116"/>
       <c r="N18" s="116"/>
@@ -5186,9 +5180,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="115"/>
-      <c r="I19" s="286"/>
-      <c r="J19" s="287"/>
-      <c r="K19" s="288"/>
+      <c r="I19" s="289"/>
+      <c r="J19" s="290"/>
+      <c r="K19" s="291"/>
       <c r="L19" s="116"/>
       <c r="M19" s="116"/>
       <c r="N19" s="116"/>
@@ -5223,9 +5217,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="115"/>
-      <c r="I20" s="286"/>
-      <c r="J20" s="287"/>
-      <c r="K20" s="288"/>
+      <c r="I20" s="289"/>
+      <c r="J20" s="290"/>
+      <c r="K20" s="291"/>
       <c r="L20" s="116"/>
       <c r="M20" s="116"/>
       <c r="N20" s="116"/>
@@ -7025,7 +7019,7 @@
     </row>
     <row r="62" spans="2:32" ht="15.75">
       <c r="B62" s="112"/>
-      <c r="C62" s="292" t="s">
+      <c r="C62" s="283" t="s">
         <v>146</v>
       </c>
       <c r="D62" s="112"/>
@@ -7824,12 +7818,12 @@
       <c r="C8" s="273" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="289" t="s">
+      <c r="D8" s="284" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="290"/>
-      <c r="F8" s="290"/>
-      <c r="G8" s="291"/>
+      <c r="E8" s="285"/>
+      <c r="F8" s="285"/>
+      <c r="G8" s="286"/>
       <c r="H8" s="273"/>
       <c r="I8" s="225"/>
       <c r="J8" s="225" t="s">
@@ -8069,7 +8063,7 @@
       <c r="S14" s="268">
         <v>0</v>
       </c>
-      <c r="T14" s="278">
+      <c r="T14" s="277">
         <v>10</v>
       </c>
       <c r="U14" s="268">
@@ -8307,7 +8301,7 @@
       <c r="S19" s="235">
         <v>6</v>
       </c>
-      <c r="T19" s="279">
+      <c r="T19" s="278">
         <v>7</v>
       </c>
       <c r="U19" s="235">
@@ -8405,7 +8399,7 @@
       <c r="S21" s="261">
         <v>0.26214399999999999</v>
       </c>
-      <c r="T21" s="280">
+      <c r="T21" s="279">
         <v>0.20971519999999999</v>
       </c>
       <c r="U21" s="261">
@@ -8791,14 +8785,14 @@
       </c>
     </row>
     <row r="35" spans="2:24">
-      <c r="J35" s="281" t="s">
+      <c r="J35" s="280" t="s">
         <v>143</v>
       </c>
-      <c r="K35" s="281"/>
-      <c r="L35" s="281" t="s">
+      <c r="K35" s="280"/>
+      <c r="L35" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="282">
+      <c r="M35" s="281">
         <v>0.24999999999999978</v>
       </c>
     </row>
@@ -8809,7 +8803,7 @@
       <c r="L36" t="s">
         <v>145</v>
       </c>
-      <c r="M36" s="283">
+      <c r="M36" s="282">
         <v>4.76837158203125</v>
       </c>
     </row>
@@ -8844,9 +8838,9 @@
       </c>
       <c r="D38" s="220"/>
     </row>
-    <row r="39" spans="2:24">
-      <c r="C39" s="277" t="s">
-        <v>48</v>
+    <row r="39" spans="2:24" ht="15.75">
+      <c r="C39" s="292" t="s">
+        <v>147</v>
       </c>
       <c r="D39" s="222"/>
     </row>

--- a/templates/finance/wacc-calculator.xlsx
+++ b/templates/finance/wacc-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sheetxl\workbook-templates\templates\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3B1626-34D0-4D92-A7C4-E17CE1C81589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50B7E02-C306-4C56-99BA-A9F51AA72C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3330" yWindow="210" windowWidth="22695" windowHeight="12375" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="147">
   <si>
     <t>Notes</t>
   </si>
@@ -185,9 +185,6 @@
   </si>
   <si>
     <t>Payback Period Calculator</t>
-  </si>
-  <si>
-    <t>www.eFinancialModels.com</t>
   </si>
   <si>
     <t>Assumptions</t>
@@ -512,7 +509,7 @@
     <numFmt numFmtId="179" formatCode="_(* #,##0.0\x_);_(* \(#,##0.0\x\);_(* &quot;-&quot;?_);_(@_)"/>
     <numFmt numFmtId="180" formatCode="_(* #,##0.0%_);_(* \(#,##0.0%\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="68">
+  <fonts count="67">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -847,15 +844,6 @@
       <sz val="48"/>
       <color theme="0"/>
       <name val="Calibri (Body)"/>
-    </font>
-    <font>
-      <i/>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -1642,7 +1630,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1953,11 +1941,8 @@
     <xf numFmtId="173" fontId="46" fillId="0" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="37" fontId="53" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="37" fontId="52" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1966,98 +1951,98 @@
     <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="174" fontId="10" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="54" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="53" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="11"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="11"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="58" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="58" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="64" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="63" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="64" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="63" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="63" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="62" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="52" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="51" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="60" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="61" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="64" fillId="59" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="63" fillId="59" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="64" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="63" fillId="59" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="60" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="60" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="60" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="60" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="60" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="60" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="59" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="60" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="60" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="60" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="63" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="62" fillId="58" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="19" fillId="60" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="60" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="19" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="60" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="60" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="59" fillId="63" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="19" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="60" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2085,15 +2070,7 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="59" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="59" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="59" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2109,7 +2086,18 @@
     <xf numFmtId="173" fontId="48" fillId="0" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10"/>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="59" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3873,14 +3861,14 @@
       <c r="B14" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="288" t="s">
+      <c r="C14" s="285" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="288"/>
-      <c r="E14" s="288"/>
-      <c r="F14" s="288"/>
-      <c r="G14" s="288"/>
-      <c r="H14" s="288"/>
+      <c r="D14" s="285"/>
+      <c r="E14" s="285"/>
+      <c r="F14" s="285"/>
+      <c r="G14" s="285"/>
+      <c r="H14" s="285"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -3914,7 +3902,7 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="2:21">
-      <c r="B16" s="287" t="s">
+      <c r="B16" s="284" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="58">
@@ -3949,7 +3937,7 @@
       <c r="U16"/>
     </row>
     <row r="17" spans="2:21">
-      <c r="B17" s="287"/>
+      <c r="B17" s="284"/>
       <c r="C17" s="58">
         <f>+C16+5%</f>
         <v>0.1</v>
@@ -3995,7 +3983,7 @@
       <c r="U17"/>
     </row>
     <row r="18" spans="2:21">
-      <c r="B18" s="287"/>
+      <c r="B18" s="284"/>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C26" si="1">+C17+10%</f>
         <v>0.2</v>
@@ -4043,7 +4031,7 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21">
-      <c r="B19" s="287"/>
+      <c r="B19" s="284"/>
       <c r="C19" s="58">
         <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
@@ -4091,7 +4079,7 @@
       <c r="U19"/>
     </row>
     <row r="20" spans="2:21">
-      <c r="B20" s="287"/>
+      <c r="B20" s="284"/>
       <c r="C20" s="58">
         <f t="shared" si="1"/>
         <v>0.4</v>
@@ -4139,7 +4127,7 @@
       <c r="U20"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="B21" s="287"/>
+      <c r="B21" s="284"/>
       <c r="C21" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
@@ -4187,7 +4175,7 @@
       <c r="U21"/>
     </row>
     <row r="22" spans="2:21">
-      <c r="B22" s="287"/>
+      <c r="B22" s="284"/>
       <c r="C22" s="58">
         <f t="shared" si="1"/>
         <v>0.6</v>
@@ -4235,7 +4223,7 @@
       <c r="U22"/>
     </row>
     <row r="23" spans="2:21">
-      <c r="B23" s="287"/>
+      <c r="B23" s="284"/>
       <c r="C23" s="58">
         <f t="shared" si="1"/>
         <v>0.7</v>
@@ -4281,7 +4269,7 @@
       <c r="U23"/>
     </row>
     <row r="24" spans="2:21">
-      <c r="B24" s="287"/>
+      <c r="B24" s="284"/>
       <c r="C24" s="58">
         <f t="shared" si="1"/>
         <v>0.79999999999999993</v>
@@ -4306,7 +4294,7 @@
       <c r="U24"/>
     </row>
     <row r="25" spans="2:21">
-      <c r="B25" s="287"/>
+      <c r="B25" s="284"/>
       <c r="C25" s="58">
         <f t="shared" si="1"/>
         <v>0.89999999999999991</v>
@@ -4338,7 +4326,7 @@
       <c r="U25"/>
     </row>
     <row r="26" spans="2:21">
-      <c r="B26" s="287"/>
+      <c r="B26" s="284"/>
       <c r="C26" s="58">
         <f t="shared" si="1"/>
         <v>0.99999999999999989</v>
@@ -4583,8 +4571,8 @@
       <c r="Z2" s="112"/>
       <c r="AA2" s="112"/>
       <c r="AB2" s="112"/>
-      <c r="AC2" s="198" t="s">
-        <v>48</v>
+      <c r="AC2" s="292" t="s">
+        <v>146</v>
       </c>
       <c r="AD2" s="112"/>
       <c r="AE2" s="112"/>
@@ -4661,7 +4649,7 @@
     <row r="5" spans="2:32">
       <c r="B5" s="114"/>
       <c r="C5" s="114" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="114"/>
       <c r="E5" s="114"/>
@@ -4673,15 +4661,15 @@
       <c r="K5" s="114"/>
       <c r="L5" s="114"/>
       <c r="M5" s="114" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N5" s="189"/>
       <c r="O5" s="190" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P5" s="114"/>
       <c r="Q5" s="190" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R5" s="114"/>
       <c r="S5" s="189"/>
@@ -4735,7 +4723,7 @@
     <row r="7" spans="2:32" ht="60">
       <c r="B7" s="153"/>
       <c r="C7" s="145" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="116"/>
       <c r="E7" s="116"/>
@@ -4743,7 +4731,7 @@
       <c r="G7" s="116"/>
       <c r="H7" s="115"/>
       <c r="I7" s="191" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J7" s="191"/>
       <c r="K7" s="192"/>
@@ -4772,11 +4760,11 @@
     <row r="8" spans="2:32" ht="61.5">
       <c r="B8" s="153"/>
       <c r="C8" s="116" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="116"/>
       <c r="E8" s="116" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="116"/>
       <c r="G8" s="116"/>
@@ -4809,20 +4797,20 @@
     <row r="9" spans="2:32">
       <c r="B9" s="153"/>
       <c r="C9" s="146" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="116"/>
       <c r="E9" s="117" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="116"/>
       <c r="G9" s="116"/>
       <c r="H9" s="115"/>
-      <c r="I9" s="289">
+      <c r="I9" s="286">
         <v>4.2087912087912089</v>
       </c>
-      <c r="J9" s="290"/>
-      <c r="K9" s="291"/>
+      <c r="J9" s="287"/>
+      <c r="K9" s="288"/>
       <c r="L9" s="116"/>
       <c r="M9" s="116"/>
       <c r="N9" s="116"/>
@@ -4848,18 +4836,18 @@
     <row r="10" spans="2:32">
       <c r="B10" s="153"/>
       <c r="C10" s="147" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" s="116"/>
       <c r="E10" s="117" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" s="116"/>
       <c r="G10" s="116"/>
       <c r="H10" s="115"/>
-      <c r="I10" s="289"/>
-      <c r="J10" s="290"/>
-      <c r="K10" s="291"/>
+      <c r="I10" s="286"/>
+      <c r="J10" s="287"/>
+      <c r="K10" s="288"/>
       <c r="L10" s="116"/>
       <c r="M10" s="116"/>
       <c r="N10" s="116"/>
@@ -4890,9 +4878,9 @@
       <c r="F11" s="116"/>
       <c r="G11" s="116"/>
       <c r="H11" s="115"/>
-      <c r="I11" s="289"/>
-      <c r="J11" s="290"/>
-      <c r="K11" s="291"/>
+      <c r="I11" s="286"/>
+      <c r="J11" s="287"/>
+      <c r="K11" s="288"/>
       <c r="L11" s="116"/>
       <c r="M11" s="116"/>
       <c r="N11" s="116"/>
@@ -4923,9 +4911,9 @@
       <c r="F12" s="116"/>
       <c r="G12" s="116"/>
       <c r="H12" s="115"/>
-      <c r="I12" s="289"/>
-      <c r="J12" s="290"/>
-      <c r="K12" s="291"/>
+      <c r="I12" s="286"/>
+      <c r="J12" s="287"/>
+      <c r="K12" s="288"/>
       <c r="L12" s="116"/>
       <c r="M12" s="116"/>
       <c r="N12" s="116"/>
@@ -4951,16 +4939,16 @@
     <row r="13" spans="2:32">
       <c r="B13" s="153"/>
       <c r="C13" s="145" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" s="116"/>
       <c r="E13" s="116"/>
       <c r="F13" s="116"/>
       <c r="G13" s="116"/>
       <c r="H13" s="115"/>
-      <c r="I13" s="289"/>
-      <c r="J13" s="290"/>
-      <c r="K13" s="291"/>
+      <c r="I13" s="286"/>
+      <c r="J13" s="287"/>
+      <c r="K13" s="288"/>
       <c r="L13" s="116"/>
       <c r="M13" s="116"/>
       <c r="N13" s="116"/>
@@ -4986,18 +4974,18 @@
     <row r="14" spans="2:32">
       <c r="B14" s="153"/>
       <c r="C14" s="116" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D14" s="116"/>
       <c r="E14" s="118" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" s="116"/>
       <c r="G14" s="116"/>
       <c r="H14" s="115"/>
-      <c r="I14" s="289"/>
-      <c r="J14" s="290"/>
-      <c r="K14" s="291"/>
+      <c r="I14" s="286"/>
+      <c r="J14" s="287"/>
+      <c r="K14" s="288"/>
       <c r="L14" s="116"/>
       <c r="M14" s="116"/>
       <c r="N14" s="116"/>
@@ -5028,9 +5016,9 @@
       <c r="F15" s="116"/>
       <c r="G15" s="116"/>
       <c r="H15" s="115"/>
-      <c r="I15" s="289"/>
-      <c r="J15" s="290"/>
-      <c r="K15" s="291"/>
+      <c r="I15" s="286"/>
+      <c r="J15" s="287"/>
+      <c r="K15" s="288"/>
       <c r="L15" s="116"/>
       <c r="M15" s="116"/>
       <c r="N15" s="116"/>
@@ -5058,16 +5046,16 @@
     <row r="16" spans="2:32">
       <c r="B16" s="153"/>
       <c r="C16" s="145" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="116"/>
       <c r="E16" s="116"/>
       <c r="F16" s="116"/>
       <c r="G16" s="120"/>
       <c r="H16" s="115"/>
-      <c r="I16" s="289"/>
-      <c r="J16" s="290"/>
-      <c r="K16" s="291"/>
+      <c r="I16" s="286"/>
+      <c r="J16" s="287"/>
+      <c r="K16" s="288"/>
       <c r="L16" s="116"/>
       <c r="M16" s="116"/>
       <c r="N16" s="116"/>
@@ -5093,20 +5081,20 @@
     <row r="17" spans="2:32">
       <c r="B17" s="153"/>
       <c r="C17" s="121" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="116"/>
       <c r="E17" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F17" s="116"/>
       <c r="G17" s="122">
         <v>100000</v>
       </c>
       <c r="H17" s="115"/>
-      <c r="I17" s="289"/>
-      <c r="J17" s="290"/>
-      <c r="K17" s="291"/>
+      <c r="I17" s="286"/>
+      <c r="J17" s="287"/>
+      <c r="K17" s="288"/>
       <c r="L17" s="116"/>
       <c r="M17" s="116"/>
       <c r="N17" s="116"/>
@@ -5132,20 +5120,20 @@
     <row r="18" spans="2:32">
       <c r="B18" s="153"/>
       <c r="C18" s="121" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" s="116"/>
       <c r="E18" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F18" s="116"/>
       <c r="G18" s="122">
         <v>20000</v>
       </c>
       <c r="H18" s="115"/>
-      <c r="I18" s="289"/>
-      <c r="J18" s="290"/>
-      <c r="K18" s="291"/>
+      <c r="I18" s="286"/>
+      <c r="J18" s="287"/>
+      <c r="K18" s="288"/>
       <c r="L18" s="116"/>
       <c r="M18" s="116"/>
       <c r="N18" s="116"/>
@@ -5173,16 +5161,16 @@
       <c r="C19" s="121"/>
       <c r="D19" s="116"/>
       <c r="E19" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F19" s="116"/>
       <c r="G19" s="122">
         <v>0</v>
       </c>
       <c r="H19" s="115"/>
-      <c r="I19" s="289"/>
-      <c r="J19" s="290"/>
-      <c r="K19" s="291"/>
+      <c r="I19" s="286"/>
+      <c r="J19" s="287"/>
+      <c r="K19" s="288"/>
       <c r="L19" s="116"/>
       <c r="M19" s="116"/>
       <c r="N19" s="116"/>
@@ -5210,16 +5198,16 @@
       <c r="C20" s="121"/>
       <c r="D20" s="116"/>
       <c r="E20" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F20" s="116"/>
       <c r="G20" s="122">
         <v>0</v>
       </c>
       <c r="H20" s="115"/>
-      <c r="I20" s="289"/>
-      <c r="J20" s="290"/>
-      <c r="K20" s="291"/>
+      <c r="I20" s="286"/>
+      <c r="J20" s="287"/>
+      <c r="K20" s="288"/>
       <c r="L20" s="116"/>
       <c r="M20" s="116"/>
       <c r="N20" s="116"/>
@@ -5278,11 +5266,11 @@
     <row r="22" spans="2:32" ht="61.5">
       <c r="B22" s="153"/>
       <c r="C22" s="123" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D22" s="123"/>
       <c r="E22" s="123" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F22" s="123"/>
       <c r="G22" s="124">
@@ -5383,7 +5371,7 @@
     <row r="25" spans="2:32">
       <c r="B25" s="114"/>
       <c r="C25" s="114" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="114"/>
       <c r="E25" s="114"/>
@@ -5453,7 +5441,7 @@
       </c>
       <c r="AB25" s="126"/>
       <c r="AC25" s="126" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AD25" s="126"/>
       <c r="AE25" s="116"/>
@@ -5495,7 +5483,7 @@
     <row r="27" spans="2:32">
       <c r="B27" s="153"/>
       <c r="C27" s="145" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27" s="116"/>
       <c r="E27" s="116"/>
@@ -5530,11 +5518,11 @@
     <row r="28" spans="2:32">
       <c r="B28" s="153"/>
       <c r="C28" s="127" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28" s="116"/>
       <c r="E28" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F28" s="116"/>
       <c r="G28" s="128"/>
@@ -5589,11 +5577,11 @@
     <row r="29" spans="2:32">
       <c r="B29" s="153"/>
       <c r="C29" s="127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29" s="116"/>
       <c r="E29" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F29" s="116"/>
       <c r="G29" s="128"/>
@@ -5661,11 +5649,11 @@
     <row r="31" spans="2:32">
       <c r="B31" s="153"/>
       <c r="C31" s="130" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D31" s="130"/>
       <c r="E31" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F31" s="130"/>
       <c r="G31" s="131"/>
@@ -5773,7 +5761,7 @@
     <row r="33" spans="2:32">
       <c r="B33" s="153"/>
       <c r="C33" s="145" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D33" s="116"/>
       <c r="E33" s="116"/>
@@ -5808,11 +5796,11 @@
     <row r="34" spans="2:32">
       <c r="B34" s="153"/>
       <c r="C34" s="127" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D34" s="116"/>
       <c r="E34" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F34" s="116"/>
       <c r="G34" s="129"/>
@@ -5887,11 +5875,11 @@
     <row r="35" spans="2:32">
       <c r="B35" s="153"/>
       <c r="C35" s="127" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" s="116"/>
       <c r="E35" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F35" s="116"/>
       <c r="G35" s="129"/>
@@ -5966,11 +5954,11 @@
     <row r="36" spans="2:32">
       <c r="B36" s="153"/>
       <c r="C36" s="127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D36" s="116"/>
       <c r="E36" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F36" s="116"/>
       <c r="G36" s="129"/>
@@ -6005,11 +5993,11 @@
     <row r="37" spans="2:32">
       <c r="B37" s="153"/>
       <c r="C37" s="127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D37" s="116"/>
       <c r="E37" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F37" s="116"/>
       <c r="G37" s="129"/>
@@ -6077,11 +6065,11 @@
     <row r="39" spans="2:32">
       <c r="B39" s="153"/>
       <c r="C39" s="130" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D39" s="130"/>
       <c r="E39" s="130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F39" s="130"/>
       <c r="G39" s="144">
@@ -6191,7 +6179,7 @@
     <row r="41" spans="2:32">
       <c r="B41" s="153"/>
       <c r="C41" s="145" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D41" s="116"/>
       <c r="E41" s="116"/>
@@ -6226,7 +6214,7 @@
     <row r="42" spans="2:32">
       <c r="B42" s="153"/>
       <c r="C42" s="116" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="116"/>
       <c r="E42" s="116" t="s">
@@ -6306,11 +6294,11 @@
     <row r="44" spans="2:32">
       <c r="B44" s="153"/>
       <c r="C44" s="116" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D44" s="116"/>
       <c r="E44" s="116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F44" s="116"/>
       <c r="G44" s="128">
@@ -6384,7 +6372,7 @@
     <row r="46" spans="2:32">
       <c r="B46" s="153"/>
       <c r="C46" s="145" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D46" s="116"/>
       <c r="E46" s="116"/>
@@ -6419,7 +6407,7 @@
     <row r="47" spans="2:32">
       <c r="B47" s="167"/>
       <c r="C47" s="136" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D47" s="137"/>
       <c r="E47" s="137"/>
@@ -6498,7 +6486,7 @@
     <row r="48" spans="2:32">
       <c r="B48" s="168"/>
       <c r="C48" s="141" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D48" s="142"/>
       <c r="E48" s="142"/>
@@ -6612,7 +6600,7 @@
     <row r="50" spans="2:32" ht="15.75">
       <c r="B50" s="169"/>
       <c r="C50" s="145" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D50" s="112"/>
       <c r="E50" s="112"/>
@@ -6647,11 +6635,11 @@
     <row r="51" spans="2:32" ht="15.75">
       <c r="B51" s="170"/>
       <c r="C51" s="148" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D51" s="148"/>
       <c r="E51" s="148" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F51" s="148"/>
       <c r="G51" s="148"/>
@@ -6759,7 +6747,7 @@
     <row r="53" spans="2:32">
       <c r="B53" s="153"/>
       <c r="C53" s="145" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D53" s="134"/>
       <c r="E53" s="134"/>
@@ -6794,7 +6782,7 @@
     <row r="54" spans="2:32">
       <c r="B54" s="153"/>
       <c r="C54" s="116" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D54" s="134"/>
       <c r="E54" s="179" t="b">
@@ -6873,7 +6861,7 @@
     <row r="55" spans="2:32">
       <c r="B55" s="153"/>
       <c r="C55" s="116" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D55" s="134"/>
       <c r="E55" s="177" t="b">
@@ -6984,8 +6972,8 @@
     </row>
     <row r="61" spans="2:32" ht="15.75">
       <c r="B61" s="112"/>
-      <c r="C61" s="199" t="s">
-        <v>79</v>
+      <c r="C61" s="198" t="s">
+        <v>78</v>
       </c>
       <c r="D61" s="112"/>
       <c r="E61" s="112"/>
@@ -7019,8 +7007,8 @@
     </row>
     <row r="62" spans="2:32" ht="15.75">
       <c r="B62" s="112"/>
-      <c r="C62" s="283" t="s">
-        <v>146</v>
+      <c r="C62" s="282" t="s">
+        <v>145</v>
       </c>
       <c r="D62" s="112"/>
       <c r="E62" s="112"/>
@@ -7133,108 +7121,108 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="23.25">
-      <c r="B2" s="200" t="s">
+      <c r="B2" s="199" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="199"/>
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" s="200"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200">
+        <v>0</v>
+      </c>
+      <c r="E3" s="200">
+        <v>1</v>
+      </c>
+      <c r="F3" s="200">
+        <v>2</v>
+      </c>
+      <c r="G3" s="200">
+        <v>3</v>
+      </c>
+      <c r="H3" s="200">
+        <v>4</v>
+      </c>
+      <c r="I3" s="200">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" s="201"/>
+      <c r="C4" s="201"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" s="202" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-    </row>
-    <row r="3" spans="2:9">
-      <c r="B3" s="201"/>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201">
-        <v>0</v>
-      </c>
-      <c r="E3" s="201">
-        <v>1</v>
-      </c>
-      <c r="F3" s="201">
-        <v>2</v>
-      </c>
-      <c r="G3" s="201">
-        <v>3</v>
-      </c>
-      <c r="H3" s="201">
-        <v>4</v>
-      </c>
-      <c r="I3" s="201">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="202"/>
-      <c r="C4" s="202"/>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="202"/>
-      <c r="H4" s="202"/>
-      <c r="I4" s="202"/>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="203" t="s">
+      <c r="C5" s="202"/>
+      <c r="D5" s="203" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="203"/>
-      <c r="D5" s="204" t="s">
+      <c r="E5" s="201"/>
+      <c r="F5" s="201"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="201"/>
+      <c r="I5" s="201"/>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="202" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="202"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="202"/>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" s="203" t="s">
+      <c r="C6" s="202"/>
+      <c r="D6" s="203" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="203"/>
-      <c r="D6" s="204" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="202"/>
+      <c r="E6" s="201"/>
+      <c r="F6" s="201"/>
+      <c r="G6" s="201"/>
+      <c r="H6" s="201"/>
+      <c r="I6" s="201"/>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="202"/>
-      <c r="C7" s="202"/>
-      <c r="D7" s="202"/>
-      <c r="E7" s="202"/>
-      <c r="F7" s="202"/>
-      <c r="G7" s="202"/>
-      <c r="H7" s="202"/>
-      <c r="I7" s="202"/>
+      <c r="B7" s="201"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="H7" s="201"/>
+      <c r="I7" s="201"/>
     </row>
     <row r="8" spans="2:9" s="14" customFormat="1">
       <c r="B8" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="205">
+        <v>84</v>
+      </c>
+      <c r="D8" s="204">
         <v>150000</v>
       </c>
     </row>
     <row r="9" spans="2:9" s="14" customFormat="1">
       <c r="B9" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="205">
+        <v>85</v>
+      </c>
+      <c r="D9" s="204">
         <v>500</v>
       </c>
     </row>
     <row r="10" spans="2:9" s="14" customFormat="1">
       <c r="B10" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="205">
+        <v>86</v>
+      </c>
+      <c r="D10" s="204">
         <f>+D8/D9</f>
         <v>300</v>
       </c>
@@ -7242,96 +7230,96 @@
     <row r="11" spans="2:9" s="14" customFormat="1"/>
     <row r="12" spans="2:9" s="14" customFormat="1">
       <c r="B12" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="205">
+        <v>87</v>
+      </c>
+      <c r="E12" s="204">
         <v>500</v>
       </c>
-      <c r="F12" s="205">
+      <c r="F12" s="204">
         <f>+E12+500</f>
         <v>1000</v>
       </c>
-      <c r="G12" s="205">
+      <c r="G12" s="204">
         <f t="shared" ref="G12:I12" si="0">+F12+500</f>
         <v>1500</v>
       </c>
-      <c r="H12" s="205">
+      <c r="H12" s="204">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="I12" s="205">
+      <c r="I12" s="204">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
     </row>
     <row r="13" spans="2:9" s="14" customFormat="1">
       <c r="B13" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="205">
+        <v>88</v>
+      </c>
+      <c r="E13" s="204">
         <v>300</v>
       </c>
-      <c r="F13" s="205">
+      <c r="F13" s="204">
         <v>600</v>
       </c>
-      <c r="G13" s="205">
+      <c r="G13" s="204">
         <v>900</v>
       </c>
-      <c r="H13" s="205">
+      <c r="H13" s="204">
         <v>1200</v>
       </c>
-      <c r="I13" s="205">
+      <c r="I13" s="204">
         <v>1500</v>
       </c>
     </row>
     <row r="14" spans="2:9" s="14" customFormat="1">
       <c r="B14" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="206">
+        <v>89</v>
+      </c>
+      <c r="E14" s="205">
         <f>+E12-E13</f>
         <v>200</v>
       </c>
-      <c r="F14" s="206">
+      <c r="F14" s="205">
         <f>+F12-F13</f>
         <v>400</v>
       </c>
-      <c r="G14" s="206">
+      <c r="G14" s="205">
         <f>+G12-G13</f>
         <v>600</v>
       </c>
-      <c r="H14" s="206">
+      <c r="H14" s="205">
         <f>+H12-H13</f>
         <v>800</v>
       </c>
-      <c r="I14" s="206">
+      <c r="I14" s="205">
         <f>+I12-I13</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="2:9" s="209" customFormat="1" ht="16.5">
-      <c r="B15" s="207" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="207"/>
-      <c r="D15" s="207"/>
-      <c r="E15" s="208">
+    <row r="15" spans="2:9" s="208" customFormat="1" ht="16.5">
+      <c r="B15" s="206" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="207">
         <f>+E13/E12</f>
         <v>0.6</v>
       </c>
-      <c r="F15" s="208">
+      <c r="F15" s="207">
         <f t="shared" ref="F15:I15" si="1">+F13/F12</f>
         <v>0.6</v>
       </c>
-      <c r="G15" s="208">
+      <c r="G15" s="207">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H15" s="208">
+      <c r="H15" s="207">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="I15" s="208">
+      <c r="I15" s="207">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
@@ -7339,45 +7327,45 @@
     <row r="16" spans="2:9" s="14" customFormat="1"/>
     <row r="17" spans="2:9" s="14" customFormat="1">
       <c r="B17" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" s="210">
+        <v>91</v>
+      </c>
+      <c r="E17" s="209">
         <v>1</v>
       </c>
-      <c r="F17" s="210">
+      <c r="F17" s="209">
         <v>0.8</v>
       </c>
-      <c r="G17" s="210">
+      <c r="G17" s="209">
         <v>0.75</v>
       </c>
-      <c r="H17" s="210">
+      <c r="H17" s="209">
         <v>0.7</v>
       </c>
-      <c r="I17" s="210">
+      <c r="I17" s="209">
         <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="2:9" s="14" customFormat="1">
       <c r="B18" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="211">
+        <v>92</v>
+      </c>
+      <c r="E18" s="210">
         <f>+E17</f>
         <v>1</v>
       </c>
-      <c r="F18" s="212">
+      <c r="F18" s="211">
         <f>+F17*E18</f>
         <v>0.8</v>
       </c>
-      <c r="G18" s="212">
+      <c r="G18" s="211">
         <f>+G17*F18</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H18" s="212">
+      <c r="H18" s="211">
         <f t="shared" ref="H18" si="2">+H17*G18</f>
         <v>0.42000000000000004</v>
       </c>
-      <c r="I18" s="212">
+      <c r="I18" s="211">
         <f>+I17*H18</f>
         <v>0.252</v>
       </c>
@@ -7385,9 +7373,9 @@
     <row r="19" spans="2:9" s="14" customFormat="1"/>
     <row r="20" spans="2:9" s="14" customFormat="1">
       <c r="B20" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="213">
+        <v>93</v>
+      </c>
+      <c r="E20" s="212">
         <f>+E18*E14</f>
         <v>200</v>
       </c>
@@ -7411,28 +7399,28 @@
     <row r="21" spans="2:9" s="14" customFormat="1"/>
     <row r="22" spans="2:9" s="14" customFormat="1">
       <c r="B22" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" s="214">
+        <v>94</v>
+      </c>
+      <c r="D22" s="213">
         <v>0.2</v>
       </c>
-      <c r="E22" s="215">
+      <c r="E22" s="214">
         <f>1/(1+$D$22)^E3</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="F22" s="215">
+      <c r="F22" s="214">
         <f>1/(1+$D$22)^F3</f>
         <v>0.69444444444444442</v>
       </c>
-      <c r="G22" s="215">
+      <c r="G22" s="214">
         <f>1/(1+$D$22)^G3</f>
         <v>0.57870370370370372</v>
       </c>
-      <c r="H22" s="215">
+      <c r="H22" s="214">
         <f>1/(1+$D$22)^H3</f>
         <v>0.48225308641975312</v>
       </c>
-      <c r="I22" s="215">
+      <c r="I22" s="214">
         <f>1/(1+$D$22)^I3</f>
         <v>0.4018775720164609</v>
       </c>
@@ -7440,90 +7428,90 @@
     <row r="23" spans="2:9" s="14" customFormat="1"/>
     <row r="24" spans="2:9" s="14" customFormat="1">
       <c r="B24" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24" s="15"/>
-      <c r="D24" s="216">
+      <c r="D24" s="215">
         <f>+-D10</f>
         <v>-300</v>
       </c>
-      <c r="E24" s="217">
+      <c r="E24" s="216">
         <f>+E22*E20</f>
         <v>166.66666666666669</v>
       </c>
-      <c r="F24" s="217">
+      <c r="F24" s="216">
         <f>+F22*F20</f>
         <v>222.22222222222223</v>
       </c>
-      <c r="G24" s="217">
+      <c r="G24" s="216">
         <f t="shared" ref="G24:I24" si="3">+G22*G20</f>
         <v>208.33333333333337</v>
       </c>
-      <c r="H24" s="217">
+      <c r="H24" s="216">
         <f t="shared" si="3"/>
         <v>162.03703703703707</v>
       </c>
-      <c r="I24" s="217">
+      <c r="I24" s="216">
         <f t="shared" si="3"/>
         <v>101.27314814814815</v>
       </c>
     </row>
     <row r="25" spans="2:9" s="14" customFormat="1">
       <c r="B25" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" s="15"/>
-      <c r="D25" s="218">
+      <c r="D25" s="217">
         <f>+D24</f>
         <v>-300</v>
       </c>
-      <c r="E25" s="218">
+      <c r="E25" s="217">
         <f>+D25+E24</f>
         <v>-133.33333333333331</v>
       </c>
-      <c r="F25" s="218">
+      <c r="F25" s="217">
         <f t="shared" ref="F25:I25" si="4">+E25+F24</f>
         <v>88.888888888888914</v>
       </c>
-      <c r="G25" s="218">
+      <c r="G25" s="217">
         <f t="shared" si="4"/>
         <v>297.22222222222229</v>
       </c>
-      <c r="H25" s="218">
+      <c r="H25" s="217">
         <f t="shared" si="4"/>
         <v>459.25925925925935</v>
       </c>
-      <c r="I25" s="218">
+      <c r="I25" s="217">
         <f t="shared" si="4"/>
         <v>560.5324074074075</v>
       </c>
     </row>
     <row r="26" spans="2:9" s="14" customFormat="1">
       <c r="B26" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" s="15"/>
-      <c r="D26" s="218">
+      <c r="D26" s="217">
         <f>+D25/-$D$25</f>
         <v>-1</v>
       </c>
-      <c r="E26" s="218">
+      <c r="E26" s="217">
         <f>+E25/-$D$25</f>
         <v>-0.44444444444444436</v>
       </c>
-      <c r="F26" s="218">
+      <c r="F26" s="217">
         <f>+F25/-$D$25</f>
         <v>0.29629629629629639</v>
       </c>
-      <c r="G26" s="218">
+      <c r="G26" s="217">
         <f t="shared" ref="G26:H26" si="5">+G25/-$D$25</f>
         <v>0.99074074074074092</v>
       </c>
-      <c r="H26" s="218">
+      <c r="H26" s="217">
         <f t="shared" si="5"/>
         <v>1.5308641975308646</v>
       </c>
-      <c r="I26" s="218">
+      <c r="I26" s="217">
         <f>+I25/-$D$25</f>
         <v>1.8684413580246917</v>
       </c>
@@ -7531,202 +7519,202 @@
     <row r="27" spans="2:9" s="14" customFormat="1">
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
-      <c r="D27" s="218"/>
-      <c r="E27" s="218"/>
-      <c r="F27" s="218"/>
-      <c r="G27" s="218"/>
-      <c r="H27" s="218"/>
-      <c r="I27" s="218"/>
+      <c r="D27" s="217"/>
+      <c r="E27" s="217"/>
+      <c r="F27" s="217"/>
+      <c r="G27" s="217"/>
+      <c r="H27" s="217"/>
+      <c r="I27" s="217"/>
     </row>
     <row r="28" spans="2:9" s="14" customFormat="1">
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
-      <c r="D28" s="218"/>
-      <c r="E28" s="218"/>
-      <c r="F28" s="218"/>
-      <c r="G28" s="218"/>
-      <c r="H28" s="218"/>
-      <c r="I28" s="218"/>
+      <c r="D28" s="217"/>
+      <c r="E28" s="217"/>
+      <c r="F28" s="217"/>
+      <c r="G28" s="217"/>
+      <c r="H28" s="217"/>
+      <c r="I28" s="217"/>
     </row>
     <row r="29" spans="2:9" s="14" customFormat="1">
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
-      <c r="D29" s="218"/>
-      <c r="E29" s="218"/>
-      <c r="F29" s="218"/>
-      <c r="G29" s="218"/>
-      <c r="H29" s="218"/>
-      <c r="I29" s="218"/>
+      <c r="D29" s="217"/>
+      <c r="E29" s="217"/>
+      <c r="F29" s="217"/>
+      <c r="G29" s="217"/>
+      <c r="H29" s="217"/>
+      <c r="I29" s="217"/>
     </row>
     <row r="30" spans="2:9" s="14" customFormat="1">
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
-      <c r="D30" s="218"/>
-      <c r="E30" s="218"/>
-      <c r="F30" s="218"/>
-      <c r="G30" s="218"/>
-      <c r="H30" s="218"/>
-      <c r="I30" s="218"/>
+      <c r="D30" s="217"/>
+      <c r="E30" s="217"/>
+      <c r="F30" s="217"/>
+      <c r="G30" s="217"/>
+      <c r="H30" s="217"/>
+      <c r="I30" s="217"/>
     </row>
     <row r="31" spans="2:9" s="14" customFormat="1">
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
-      <c r="D31" s="218"/>
-      <c r="E31" s="218"/>
-      <c r="F31" s="218"/>
-      <c r="G31" s="218"/>
-      <c r="H31" s="218"/>
-      <c r="I31" s="218"/>
+      <c r="D31" s="217"/>
+      <c r="E31" s="217"/>
+      <c r="F31" s="217"/>
+      <c r="G31" s="217"/>
+      <c r="H31" s="217"/>
+      <c r="I31" s="217"/>
     </row>
     <row r="32" spans="2:9" s="14" customFormat="1">
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
-      <c r="D32" s="218"/>
-      <c r="E32" s="218"/>
-      <c r="F32" s="218"/>
-      <c r="G32" s="218"/>
-      <c r="H32" s="218"/>
-      <c r="I32" s="218"/>
+      <c r="D32" s="217"/>
+      <c r="E32" s="217"/>
+      <c r="F32" s="217"/>
+      <c r="G32" s="217"/>
+      <c r="H32" s="217"/>
+      <c r="I32" s="217"/>
     </row>
     <row r="33" spans="2:9" s="14" customFormat="1">
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="218"/>
-      <c r="F33" s="218"/>
-      <c r="G33" s="218"/>
-      <c r="H33" s="218"/>
-      <c r="I33" s="218"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="217"/>
+      <c r="G33" s="217"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="217"/>
     </row>
     <row r="34" spans="2:9" s="14" customFormat="1">
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
+      <c r="D34" s="217"/>
+      <c r="E34" s="217"/>
+      <c r="F34" s="217"/>
+      <c r="G34" s="217"/>
+      <c r="H34" s="217"/>
+      <c r="I34" s="217"/>
     </row>
     <row r="35" spans="2:9" s="14" customFormat="1">
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
-      <c r="D35" s="218"/>
-      <c r="E35" s="218"/>
-      <c r="F35" s="218"/>
-      <c r="G35" s="218"/>
-      <c r="H35" s="218"/>
-      <c r="I35" s="218"/>
+      <c r="D35" s="217"/>
+      <c r="E35" s="217"/>
+      <c r="F35" s="217"/>
+      <c r="G35" s="217"/>
+      <c r="H35" s="217"/>
+      <c r="I35" s="217"/>
     </row>
     <row r="36" spans="2:9" s="14" customFormat="1">
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="218"/>
-      <c r="I36" s="218"/>
+      <c r="D36" s="217"/>
+      <c r="E36" s="217"/>
+      <c r="F36" s="217"/>
+      <c r="G36" s="217"/>
+      <c r="H36" s="217"/>
+      <c r="I36" s="217"/>
     </row>
     <row r="37" spans="2:9" s="14" customFormat="1">
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
-      <c r="D37" s="218"/>
-      <c r="E37" s="218"/>
-      <c r="F37" s="218"/>
-      <c r="G37" s="218"/>
-      <c r="H37" s="218"/>
-      <c r="I37" s="218"/>
+      <c r="D37" s="217"/>
+      <c r="E37" s="217"/>
+      <c r="F37" s="217"/>
+      <c r="G37" s="217"/>
+      <c r="H37" s="217"/>
+      <c r="I37" s="217"/>
     </row>
     <row r="38" spans="2:9" s="14" customFormat="1">
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
-      <c r="D38" s="218"/>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
-      <c r="H38" s="218"/>
-      <c r="I38" s="218"/>
+      <c r="D38" s="217"/>
+      <c r="E38" s="217"/>
+      <c r="F38" s="217"/>
+      <c r="G38" s="217"/>
+      <c r="H38" s="217"/>
+      <c r="I38" s="217"/>
     </row>
     <row r="39" spans="2:9" s="14" customFormat="1">
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
-      <c r="D39" s="218"/>
-      <c r="E39" s="218"/>
-      <c r="F39" s="218"/>
-      <c r="G39" s="218"/>
-      <c r="H39" s="218"/>
-      <c r="I39" s="218"/>
+      <c r="D39" s="217"/>
+      <c r="E39" s="217"/>
+      <c r="F39" s="217"/>
+      <c r="G39" s="217"/>
+      <c r="H39" s="217"/>
+      <c r="I39" s="217"/>
     </row>
     <row r="40" spans="2:9" s="14" customFormat="1">
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
-      <c r="D40" s="218"/>
-      <c r="E40" s="218"/>
-      <c r="F40" s="218"/>
-      <c r="G40" s="218"/>
-      <c r="H40" s="218"/>
-      <c r="I40" s="218"/>
+      <c r="D40" s="217"/>
+      <c r="E40" s="217"/>
+      <c r="F40" s="217"/>
+      <c r="G40" s="217"/>
+      <c r="H40" s="217"/>
+      <c r="I40" s="217"/>
     </row>
     <row r="41" spans="2:9" s="14" customFormat="1">
       <c r="B41" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C41" s="15"/>
-      <c r="D41" s="218"/>
-      <c r="E41" s="218"/>
-      <c r="F41" s="218"/>
-      <c r="G41" s="218"/>
-      <c r="H41" s="218"/>
-      <c r="I41" s="218"/>
+      <c r="D41" s="217"/>
+      <c r="E41" s="217"/>
+      <c r="F41" s="217"/>
+      <c r="G41" s="217"/>
+      <c r="H41" s="217"/>
+      <c r="I41" s="217"/>
     </row>
     <row r="42" spans="2:9" s="14" customFormat="1">
       <c r="B42" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42" s="15"/>
-      <c r="D42" s="218"/>
-      <c r="E42" s="218"/>
-      <c r="F42" s="218"/>
-      <c r="G42" s="218"/>
-      <c r="H42" s="218"/>
-      <c r="I42" s="218"/>
+      <c r="D42" s="217"/>
+      <c r="E42" s="217"/>
+      <c r="F42" s="217"/>
+      <c r="G42" s="217"/>
+      <c r="H42" s="217"/>
+      <c r="I42" s="217"/>
     </row>
     <row r="43" spans="2:9" s="14" customFormat="1">
       <c r="B43" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" s="15"/>
-      <c r="D43" s="218"/>
-      <c r="E43" s="218"/>
-      <c r="F43" s="218"/>
-      <c r="G43" s="218"/>
-      <c r="H43" s="218"/>
-      <c r="I43" s="218"/>
+      <c r="D43" s="217"/>
+      <c r="E43" s="217"/>
+      <c r="F43" s="217"/>
+      <c r="G43" s="217"/>
+      <c r="H43" s="217"/>
+      <c r="I43" s="217"/>
     </row>
     <row r="44" spans="2:9" s="14" customFormat="1">
       <c r="B44" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" s="15"/>
-      <c r="D44" s="218"/>
-      <c r="E44" s="218"/>
-      <c r="F44" s="218"/>
-      <c r="G44" s="218"/>
-      <c r="H44" s="218"/>
-      <c r="I44" s="218"/>
+      <c r="D44" s="217"/>
+      <c r="E44" s="217"/>
+      <c r="F44" s="217"/>
+      <c r="G44" s="217"/>
+      <c r="H44" s="217"/>
+      <c r="I44" s="217"/>
     </row>
     <row r="45" spans="2:9" s="14" customFormat="1">
       <c r="B45" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C45" s="15"/>
-      <c r="D45" s="218"/>
-      <c r="E45" s="218"/>
-      <c r="F45" s="218"/>
-      <c r="G45" s="218"/>
-      <c r="H45" s="218"/>
-      <c r="I45" s="218"/>
+      <c r="D45" s="217"/>
+      <c r="E45" s="217"/>
+      <c r="F45" s="217"/>
+      <c r="G45" s="217"/>
+      <c r="H45" s="217"/>
+      <c r="I45" s="217"/>
     </row>
     <row r="46" spans="2:9" ht="16.5" thickBot="1">
       <c r="B46" s="17"/>
@@ -7756,1099 +7744,1099 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:24" ht="26.25">
-      <c r="B3" s="223"/>
-      <c r="C3" s="223" t="s">
+      <c r="B3" s="222"/>
+      <c r="C3" s="222" t="s">
+        <v>101</v>
+      </c>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="222"/>
+      <c r="N3" s="222"/>
+      <c r="O3" s="222"/>
+      <c r="P3" s="222"/>
+      <c r="Q3" s="222"/>
+      <c r="R3" s="222"/>
+      <c r="S3" s="222"/>
+      <c r="T3" s="222"/>
+      <c r="U3" s="222"/>
+      <c r="V3" s="222"/>
+      <c r="W3" s="222"/>
+      <c r="X3" s="222"/>
+    </row>
+    <row r="5" spans="2:24" ht="21">
+      <c r="C5" s="235" t="s">
         <v>102</v>
       </c>
-      <c r="K3" s="223"/>
-      <c r="L3" s="223"/>
-      <c r="M3" s="223"/>
-      <c r="N3" s="223"/>
-      <c r="O3" s="223"/>
-      <c r="P3" s="223"/>
-      <c r="Q3" s="223"/>
-      <c r="R3" s="223"/>
-      <c r="S3" s="223"/>
-      <c r="T3" s="223"/>
-      <c r="U3" s="223"/>
-      <c r="V3" s="223"/>
-      <c r="W3" s="223"/>
-      <c r="X3" s="223"/>
-    </row>
-    <row r="5" spans="2:24" ht="21">
-      <c r="C5" s="236" t="s">
+      <c r="K5" s="235"/>
+      <c r="L5" s="236"/>
+    </row>
+    <row r="7" spans="2:24">
+      <c r="B7" s="253"/>
+      <c r="C7" s="272"/>
+      <c r="D7" s="272"/>
+      <c r="E7" s="272"/>
+      <c r="F7" s="272"/>
+      <c r="G7" s="272"/>
+      <c r="H7" s="272"/>
+      <c r="I7" s="224"/>
+      <c r="J7" s="224"/>
+      <c r="K7" s="224"/>
+      <c r="L7" s="224"/>
+      <c r="M7" s="253"/>
+      <c r="N7" s="253"/>
+      <c r="O7" s="253"/>
+      <c r="P7" s="253"/>
+      <c r="Q7" s="253"/>
+      <c r="R7" s="253"/>
+      <c r="S7" s="253"/>
+      <c r="T7" s="253"/>
+      <c r="U7" s="253">
+        <v>1905</v>
+      </c>
+      <c r="V7" s="253">
+        <v>1905</v>
+      </c>
+      <c r="W7" s="253">
+        <v>1905</v>
+      </c>
+      <c r="X7" s="253"/>
+    </row>
+    <row r="8" spans="2:24">
+      <c r="B8" s="253"/>
+      <c r="C8" s="272" t="s">
         <v>103</v>
       </c>
-      <c r="K5" s="236"/>
-      <c r="L5" s="237"/>
-    </row>
-    <row r="7" spans="2:24">
-      <c r="B7" s="254"/>
-      <c r="C7" s="273"/>
-      <c r="D7" s="273"/>
-      <c r="E7" s="273"/>
-      <c r="F7" s="273"/>
-      <c r="G7" s="273"/>
-      <c r="H7" s="273"/>
-      <c r="I7" s="225"/>
-      <c r="J7" s="225"/>
-      <c r="K7" s="225"/>
-      <c r="L7" s="225"/>
-      <c r="M7" s="254"/>
-      <c r="N7" s="254"/>
-      <c r="O7" s="254"/>
-      <c r="P7" s="254"/>
-      <c r="Q7" s="254"/>
-      <c r="R7" s="254"/>
-      <c r="S7" s="254"/>
-      <c r="T7" s="254"/>
-      <c r="U7" s="254">
-        <v>1905</v>
-      </c>
-      <c r="V7" s="254">
-        <v>1905</v>
-      </c>
-      <c r="W7" s="254">
-        <v>1905</v>
-      </c>
-      <c r="X7" s="254"/>
-    </row>
-    <row r="8" spans="2:24">
-      <c r="B8" s="254"/>
-      <c r="C8" s="273" t="s">
+      <c r="D8" s="289" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="284" t="s">
+      <c r="E8" s="290"/>
+      <c r="F8" s="290"/>
+      <c r="G8" s="291"/>
+      <c r="H8" s="272"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="224" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="285"/>
-      <c r="F8" s="285"/>
-      <c r="G8" s="286"/>
-      <c r="H8" s="273"/>
-      <c r="I8" s="225"/>
-      <c r="J8" s="225" t="s">
+      <c r="K8" s="224"/>
+      <c r="L8" s="224" t="s">
         <v>106</v>
       </c>
-      <c r="K8" s="225"/>
-      <c r="L8" s="225" t="s">
+      <c r="M8" s="253">
+        <v>2023</v>
+      </c>
+      <c r="N8" s="253">
+        <v>2024</v>
+      </c>
+      <c r="O8" s="253">
+        <v>2025</v>
+      </c>
+      <c r="P8" s="253">
+        <v>2026</v>
+      </c>
+      <c r="Q8" s="253">
+        <v>2027</v>
+      </c>
+      <c r="R8" s="253">
+        <v>2028</v>
+      </c>
+      <c r="S8" s="253">
+        <v>2029</v>
+      </c>
+      <c r="T8" s="253">
+        <v>2030</v>
+      </c>
+      <c r="U8" s="253">
+        <v>2031</v>
+      </c>
+      <c r="V8" s="253">
+        <v>2032</v>
+      </c>
+      <c r="W8" s="253">
+        <v>2033</v>
+      </c>
+      <c r="X8" s="253"/>
+    </row>
+    <row r="9" spans="2:24">
+      <c r="B9" s="228"/>
+      <c r="C9" s="272"/>
+      <c r="D9" s="272"/>
+      <c r="E9" s="272"/>
+      <c r="F9" s="272"/>
+      <c r="G9" s="272"/>
+      <c r="H9" s="272"/>
+      <c r="I9" s="224"/>
+      <c r="J9" s="224" t="s">
         <v>107</v>
       </c>
-      <c r="M8" s="254">
-        <v>2023</v>
-      </c>
-      <c r="N8" s="254">
-        <v>2024</v>
-      </c>
-      <c r="O8" s="254">
-        <v>2025</v>
-      </c>
-      <c r="P8" s="254">
-        <v>2026</v>
-      </c>
-      <c r="Q8" s="254">
-        <v>2027</v>
-      </c>
-      <c r="R8" s="254">
-        <v>2028</v>
-      </c>
-      <c r="S8" s="254">
-        <v>2029</v>
-      </c>
-      <c r="T8" s="254">
-        <v>2030</v>
-      </c>
-      <c r="U8" s="254">
-        <v>2031</v>
-      </c>
-      <c r="V8" s="254">
-        <v>2032</v>
-      </c>
-      <c r="W8" s="254">
-        <v>2033</v>
-      </c>
-      <c r="X8" s="254"/>
-    </row>
-    <row r="9" spans="2:24">
-      <c r="B9" s="229"/>
-      <c r="C9" s="273"/>
-      <c r="D9" s="273"/>
-      <c r="E9" s="273"/>
-      <c r="F9" s="273"/>
-      <c r="G9" s="273"/>
-      <c r="H9" s="273"/>
-      <c r="I9" s="225"/>
-      <c r="J9" s="225" t="s">
+      <c r="K9" s="224"/>
+      <c r="L9" s="224"/>
+      <c r="M9" s="228">
+        <v>45291</v>
+      </c>
+      <c r="N9" s="228">
+        <v>45657</v>
+      </c>
+      <c r="O9" s="228">
+        <v>46022</v>
+      </c>
+      <c r="P9" s="228">
+        <v>46387</v>
+      </c>
+      <c r="Q9" s="228">
+        <v>46752</v>
+      </c>
+      <c r="R9" s="228">
+        <v>47118</v>
+      </c>
+      <c r="S9" s="228">
+        <v>47483</v>
+      </c>
+      <c r="T9" s="228">
+        <v>47848</v>
+      </c>
+      <c r="U9" s="228">
+        <v>48213</v>
+      </c>
+      <c r="V9" s="228">
+        <v>48579</v>
+      </c>
+      <c r="W9" s="228">
+        <v>48944</v>
+      </c>
+      <c r="X9" s="228"/>
+    </row>
+    <row r="10" spans="2:24">
+      <c r="B10" s="231"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="233"/>
+      <c r="G10" s="233"/>
+      <c r="H10" s="233"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="K9" s="225"/>
-      <c r="L9" s="225"/>
-      <c r="M9" s="229">
-        <v>45291</v>
-      </c>
-      <c r="N9" s="229">
-        <v>45657</v>
-      </c>
-      <c r="O9" s="229">
-        <v>46022</v>
-      </c>
-      <c r="P9" s="229">
-        <v>46387</v>
-      </c>
-      <c r="Q9" s="229">
-        <v>46752</v>
-      </c>
-      <c r="R9" s="229">
-        <v>47118</v>
-      </c>
-      <c r="S9" s="229">
-        <v>47483</v>
-      </c>
-      <c r="T9" s="229">
-        <v>47848</v>
-      </c>
-      <c r="U9" s="229">
-        <v>48213</v>
-      </c>
-      <c r="V9" s="229">
-        <v>48579</v>
-      </c>
-      <c r="W9" s="229">
-        <v>48944</v>
-      </c>
-      <c r="X9" s="229"/>
-    </row>
-    <row r="10" spans="2:24">
-      <c r="B10" s="232"/>
-      <c r="C10" s="234"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="234"/>
-      <c r="F10" s="234"/>
-      <c r="G10" s="234"/>
-      <c r="H10" s="234"/>
-      <c r="I10" s="234"/>
-      <c r="J10" s="234" t="s">
+      <c r="K10" s="233"/>
+      <c r="L10" s="232"/>
+      <c r="M10" s="231">
+        <v>0</v>
+      </c>
+      <c r="N10" s="231">
+        <v>1</v>
+      </c>
+      <c r="O10" s="231">
+        <v>2</v>
+      </c>
+      <c r="P10" s="231">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="231">
+        <v>4</v>
+      </c>
+      <c r="R10" s="231">
+        <v>5</v>
+      </c>
+      <c r="S10" s="231">
+        <v>6</v>
+      </c>
+      <c r="T10" s="231">
+        <v>7</v>
+      </c>
+      <c r="U10" s="231">
+        <v>8</v>
+      </c>
+      <c r="V10" s="231">
+        <v>9</v>
+      </c>
+      <c r="W10" s="231">
+        <v>10</v>
+      </c>
+      <c r="X10" s="231"/>
+    </row>
+    <row r="12" spans="2:24">
+      <c r="C12" s="239" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="239" t="s">
         <v>109</v>
       </c>
-      <c r="K10" s="234"/>
-      <c r="L10" s="233"/>
-      <c r="M10" s="232">
-        <v>0</v>
-      </c>
-      <c r="N10" s="232">
+      <c r="K12" s="239"/>
+      <c r="L12" s="261"/>
+      <c r="M12" s="218"/>
+      <c r="N12" s="238"/>
+      <c r="O12" s="238"/>
+      <c r="P12" s="238"/>
+      <c r="Q12" s="238"/>
+      <c r="R12" s="238"/>
+      <c r="S12" s="238"/>
+      <c r="T12" s="238"/>
+      <c r="U12" s="238"/>
+      <c r="V12" s="238"/>
+      <c r="W12" s="238"/>
+    </row>
+    <row r="13" spans="2:24">
+      <c r="C13" s="218" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="226">
         <v>1</v>
       </c>
-      <c r="O10" s="232">
-        <v>2</v>
-      </c>
-      <c r="P10" s="232">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="232">
-        <v>4</v>
-      </c>
-      <c r="R10" s="232">
-        <v>5</v>
-      </c>
-      <c r="S10" s="232">
-        <v>6</v>
-      </c>
-      <c r="T10" s="232">
-        <v>7</v>
-      </c>
-      <c r="U10" s="232">
-        <v>8</v>
-      </c>
-      <c r="V10" s="232">
-        <v>9</v>
-      </c>
-      <c r="W10" s="232">
+      <c r="J13" s="246" t="s">
+        <v>111</v>
+      </c>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="274"/>
+      <c r="N13" s="265">
+        <v>0</v>
+      </c>
+      <c r="O13" s="265">
+        <v>0</v>
+      </c>
+      <c r="P13" s="265">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="265">
+        <v>0</v>
+      </c>
+      <c r="R13" s="265">
+        <v>0</v>
+      </c>
+      <c r="S13" s="265">
+        <v>0</v>
+      </c>
+      <c r="T13" s="265">
+        <v>10000000</v>
+      </c>
+      <c r="U13" s="265">
+        <v>0</v>
+      </c>
+      <c r="V13" s="265">
+        <v>0</v>
+      </c>
+      <c r="W13" s="265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24">
+      <c r="J14" s="243" t="s">
+        <v>112</v>
+      </c>
+      <c r="K14" s="243"/>
+      <c r="L14" s="244" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" s="245"/>
+      <c r="N14" s="267">
+        <v>0</v>
+      </c>
+      <c r="O14" s="267">
+        <v>0</v>
+      </c>
+      <c r="P14" s="267">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="267">
+        <v>0</v>
+      </c>
+      <c r="R14" s="267">
+        <v>0</v>
+      </c>
+      <c r="S14" s="267">
+        <v>0</v>
+      </c>
+      <c r="T14" s="276">
         <v>10</v>
       </c>
-      <c r="X10" s="232"/>
-    </row>
-    <row r="12" spans="2:24">
-      <c r="C12" s="240" t="s">
-        <v>49</v>
-      </c>
-      <c r="J12" s="240" t="s">
-        <v>110</v>
-      </c>
-      <c r="K12" s="240"/>
-      <c r="L12" s="262"/>
-      <c r="M12" s="219"/>
-      <c r="N12" s="239"/>
-      <c r="O12" s="239"/>
-      <c r="P12" s="239"/>
-      <c r="Q12" s="239"/>
-      <c r="R12" s="239"/>
-      <c r="S12" s="239"/>
-      <c r="T12" s="239"/>
-      <c r="U12" s="239"/>
-      <c r="V12" s="239"/>
-      <c r="W12" s="239"/>
-    </row>
-    <row r="13" spans="2:24">
-      <c r="C13" s="219" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" t="s">
-        <v>111</v>
-      </c>
-      <c r="G13" s="227">
-        <v>1</v>
-      </c>
-      <c r="J13" s="247" t="s">
-        <v>112</v>
-      </c>
-      <c r="K13" s="247"/>
-      <c r="L13" s="247" t="s">
-        <v>62</v>
-      </c>
-      <c r="M13" s="275"/>
-      <c r="N13" s="266">
-        <v>0</v>
-      </c>
-      <c r="O13" s="266">
-        <v>0</v>
-      </c>
-      <c r="P13" s="266">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="266">
-        <v>0</v>
-      </c>
-      <c r="R13" s="266">
-        <v>0</v>
-      </c>
-      <c r="S13" s="266">
-        <v>0</v>
-      </c>
-      <c r="T13" s="266">
-        <v>10000000</v>
-      </c>
-      <c r="U13" s="266">
-        <v>0</v>
-      </c>
-      <c r="V13" s="266">
-        <v>0</v>
-      </c>
-      <c r="W13" s="266">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:24">
-      <c r="J14" s="244" t="s">
-        <v>113</v>
-      </c>
-      <c r="K14" s="244"/>
-      <c r="L14" s="245" t="s">
+      <c r="U14" s="267">
+        <v>0</v>
+      </c>
+      <c r="V14" s="267">
+        <v>0</v>
+      </c>
+      <c r="W14" s="267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:24">
+      <c r="C15" s="218" t="s">
         <v>114</v>
       </c>
-      <c r="M14" s="246"/>
-      <c r="N14" s="268">
-        <v>0</v>
-      </c>
-      <c r="O14" s="268">
-        <v>0</v>
-      </c>
-      <c r="P14" s="268">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="268">
-        <v>0</v>
-      </c>
-      <c r="R14" s="268">
-        <v>0</v>
-      </c>
-      <c r="S14" s="268">
-        <v>0</v>
-      </c>
-      <c r="T14" s="277">
-        <v>10</v>
-      </c>
-      <c r="U14" s="268">
-        <v>0</v>
-      </c>
-      <c r="V14" s="268">
-        <v>0</v>
-      </c>
-      <c r="W14" s="268">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:24">
-      <c r="C15" s="219" t="s">
+      <c r="J15" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="250" t="s">
+      <c r="K15" s="249"/>
+      <c r="L15" s="274" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="249"/>
+      <c r="N15" s="257">
+        <v>0</v>
+      </c>
+      <c r="O15" s="257">
+        <v>0</v>
+      </c>
+      <c r="P15" s="257">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="257">
+        <v>0</v>
+      </c>
+      <c r="R15" s="257">
+        <v>0</v>
+      </c>
+      <c r="S15" s="257">
+        <v>0</v>
+      </c>
+      <c r="T15" s="265">
+        <v>100000000</v>
+      </c>
+      <c r="U15" s="257">
+        <v>0</v>
+      </c>
+      <c r="V15" s="257">
+        <v>0</v>
+      </c>
+      <c r="W15" s="257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="C16" s="220" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="220"/>
+      <c r="E16" s="220"/>
+      <c r="F16" s="220"/>
+      <c r="G16" s="226" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="247" t="s">
         <v>116</v>
       </c>
-      <c r="K15" s="250"/>
-      <c r="L15" s="275" t="s">
-        <v>62</v>
-      </c>
-      <c r="M15" s="250"/>
-      <c r="N15" s="258">
-        <v>0</v>
-      </c>
-      <c r="O15" s="258">
-        <v>0</v>
-      </c>
-      <c r="P15" s="258">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="258">
-        <v>0</v>
-      </c>
-      <c r="R15" s="258">
-        <v>0</v>
-      </c>
-      <c r="S15" s="258">
-        <v>0</v>
-      </c>
-      <c r="T15" s="266">
-        <v>100000000</v>
-      </c>
-      <c r="U15" s="258">
-        <v>0</v>
-      </c>
-      <c r="V15" s="258">
-        <v>0</v>
-      </c>
-      <c r="W15" s="258">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:24">
-      <c r="C16" s="221" t="s">
+      <c r="K16" s="247"/>
+      <c r="L16" s="246" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="221"/>
-      <c r="E16" s="221"/>
-      <c r="F16" s="221"/>
-      <c r="G16" s="227" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="248" t="s">
-        <v>117</v>
-      </c>
-      <c r="K16" s="248"/>
-      <c r="L16" s="247" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" s="250"/>
-      <c r="N16" s="267">
-        <v>0</v>
-      </c>
-      <c r="O16" s="267">
-        <v>0</v>
-      </c>
-      <c r="P16" s="267">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="267">
-        <v>0</v>
-      </c>
-      <c r="R16" s="267">
-        <v>0</v>
-      </c>
-      <c r="S16" s="267">
-        <v>0</v>
-      </c>
-      <c r="T16" s="267">
-        <v>0</v>
-      </c>
-      <c r="U16" s="267">
-        <v>0</v>
-      </c>
-      <c r="V16" s="267">
-        <v>0</v>
-      </c>
-      <c r="W16" s="267">
+      <c r="M16" s="249"/>
+      <c r="N16" s="266">
+        <v>0</v>
+      </c>
+      <c r="O16" s="266">
+        <v>0</v>
+      </c>
+      <c r="P16" s="266">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="266">
+        <v>0</v>
+      </c>
+      <c r="R16" s="266">
+        <v>0</v>
+      </c>
+      <c r="S16" s="266">
+        <v>0</v>
+      </c>
+      <c r="T16" s="266">
+        <v>0</v>
+      </c>
+      <c r="U16" s="266">
+        <v>0</v>
+      </c>
+      <c r="V16" s="266">
+        <v>0</v>
+      </c>
+      <c r="W16" s="266">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:24">
       <c r="C17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" t="s">
         <v>118</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" s="227">
+        <v>45291</v>
+      </c>
+      <c r="J17" s="247" t="s">
         <v>119</v>
       </c>
-      <c r="G17" s="228">
-        <v>45291</v>
-      </c>
-      <c r="J17" s="248" t="s">
-        <v>120</v>
-      </c>
-      <c r="K17" s="248"/>
-      <c r="L17" s="247" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="250"/>
-      <c r="N17" s="267">
-        <v>0</v>
-      </c>
-      <c r="O17" s="267">
-        <v>0</v>
-      </c>
-      <c r="P17" s="267">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="267">
-        <v>0</v>
-      </c>
-      <c r="R17" s="267">
-        <v>0</v>
-      </c>
-      <c r="S17" s="267">
-        <v>0</v>
-      </c>
-      <c r="T17" s="267">
-        <v>0</v>
-      </c>
-      <c r="U17" s="267">
-        <v>0</v>
-      </c>
-      <c r="V17" s="267">
-        <v>0</v>
-      </c>
-      <c r="W17" s="267">
+      <c r="K17" s="247"/>
+      <c r="L17" s="246" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="249"/>
+      <c r="N17" s="266">
+        <v>0</v>
+      </c>
+      <c r="O17" s="266">
+        <v>0</v>
+      </c>
+      <c r="P17" s="266">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="266">
+        <v>0</v>
+      </c>
+      <c r="R17" s="266">
+        <v>0</v>
+      </c>
+      <c r="S17" s="266">
+        <v>0</v>
+      </c>
+      <c r="T17" s="266">
+        <v>0</v>
+      </c>
+      <c r="U17" s="266">
+        <v>0</v>
+      </c>
+      <c r="V17" s="266">
+        <v>0</v>
+      </c>
+      <c r="W17" s="266">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:24">
       <c r="C18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
         <v>121</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" s="226">
+        <v>7</v>
+      </c>
+      <c r="J18" s="250" t="s">
         <v>122</v>
       </c>
-      <c r="G18" s="227">
-        <v>7</v>
-      </c>
-      <c r="J18" s="251" t="s">
-        <v>123</v>
-      </c>
-      <c r="K18" s="251"/>
-      <c r="L18" s="252" t="s">
-        <v>62</v>
-      </c>
-      <c r="M18" s="251"/>
-      <c r="N18" s="269">
-        <v>0</v>
-      </c>
-      <c r="O18" s="269">
-        <v>0</v>
-      </c>
-      <c r="P18" s="269">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="269">
-        <v>0</v>
-      </c>
-      <c r="R18" s="269">
-        <v>0</v>
-      </c>
-      <c r="S18" s="269">
-        <v>0</v>
-      </c>
-      <c r="T18" s="270">
+      <c r="K18" s="250"/>
+      <c r="L18" s="251" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="250"/>
+      <c r="N18" s="268">
+        <v>0</v>
+      </c>
+      <c r="O18" s="268">
+        <v>0</v>
+      </c>
+      <c r="P18" s="268">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="268">
+        <v>0</v>
+      </c>
+      <c r="R18" s="268">
+        <v>0</v>
+      </c>
+      <c r="S18" s="268">
+        <v>0</v>
+      </c>
+      <c r="T18" s="269">
         <v>100000000</v>
       </c>
-      <c r="U18" s="269">
-        <v>0</v>
-      </c>
-      <c r="V18" s="269">
-        <v>0</v>
-      </c>
-      <c r="W18" s="269">
+      <c r="U18" s="268">
+        <v>0</v>
+      </c>
+      <c r="V18" s="268">
+        <v>0</v>
+      </c>
+      <c r="W18" s="268">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:24">
       <c r="C19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="255" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="242">
+        <v>10000000</v>
+      </c>
+      <c r="J19" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="256" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="243">
-        <v>10000000</v>
-      </c>
-      <c r="J19" t="s">
-        <v>125</v>
-      </c>
-      <c r="L19" s="257" t="s">
-        <v>77</v>
-      </c>
-      <c r="M19" s="219"/>
-      <c r="N19" s="235">
+      <c r="L19" s="256" t="s">
+        <v>76</v>
+      </c>
+      <c r="M19" s="218"/>
+      <c r="N19" s="234">
         <v>1</v>
       </c>
-      <c r="O19" s="235">
+      <c r="O19" s="234">
         <v>2</v>
       </c>
-      <c r="P19" s="235">
+      <c r="P19" s="234">
         <v>3</v>
       </c>
-      <c r="Q19" s="235">
+      <c r="Q19" s="234">
         <v>4</v>
       </c>
-      <c r="R19" s="235">
+      <c r="R19" s="234">
         <v>5</v>
       </c>
-      <c r="S19" s="235">
+      <c r="S19" s="234">
         <v>6</v>
       </c>
-      <c r="T19" s="278">
+      <c r="T19" s="277">
         <v>7</v>
       </c>
-      <c r="U19" s="235">
+      <c r="U19" s="234">
         <v>8</v>
       </c>
-      <c r="V19" s="235">
+      <c r="V19" s="234">
         <v>9</v>
       </c>
-      <c r="W19" s="235">
+      <c r="W19" s="234">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="2:24">
       <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" t="s">
         <v>113</v>
       </c>
-      <c r="E20" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" s="241">
+      <c r="G20" s="240">
         <v>10</v>
       </c>
       <c r="J20" t="s">
+        <v>125</v>
+      </c>
+      <c r="L20" s="256" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="218"/>
+      <c r="N20" s="259">
+        <v>0.25</v>
+      </c>
+      <c r="O20" s="259">
+        <v>0.25</v>
+      </c>
+      <c r="P20" s="259">
+        <v>0.25</v>
+      </c>
+      <c r="Q20" s="259">
+        <v>0.25</v>
+      </c>
+      <c r="R20" s="259">
+        <v>0.25</v>
+      </c>
+      <c r="S20" s="259">
+        <v>0.25</v>
+      </c>
+      <c r="T20" s="237">
+        <v>0.25</v>
+      </c>
+      <c r="U20" s="259">
+        <v>0.25</v>
+      </c>
+      <c r="V20" s="259">
+        <v>0.25</v>
+      </c>
+      <c r="W20" s="259">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24">
+      <c r="B21" s="275"/>
+      <c r="C21" t="s">
         <v>126</v>
       </c>
-      <c r="L20" s="257" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="219"/>
-      <c r="N20" s="260">
-        <v>0.25</v>
-      </c>
-      <c r="O20" s="260">
-        <v>0.25</v>
-      </c>
-      <c r="P20" s="260">
-        <v>0.25</v>
-      </c>
-      <c r="Q20" s="260">
-        <v>0.25</v>
-      </c>
-      <c r="R20" s="260">
-        <v>0.25</v>
-      </c>
-      <c r="S20" s="260">
-        <v>0.25</v>
-      </c>
-      <c r="T20" s="238">
-        <v>0.25</v>
-      </c>
-      <c r="U20" s="260">
-        <v>0.25</v>
-      </c>
-      <c r="V20" s="260">
-        <v>0.25</v>
-      </c>
-      <c r="W20" s="260">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="21" spans="2:24">
-      <c r="B21" s="276"/>
-      <c r="C21" t="s">
+      <c r="E21" s="255" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="242">
+        <v>0</v>
+      </c>
+      <c r="J21" s="223" t="s">
         <v>127</v>
       </c>
-      <c r="E21" s="256" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="243">
-        <v>0</v>
-      </c>
-      <c r="J21" s="224" t="s">
-        <v>128</v>
-      </c>
-      <c r="K21" s="224"/>
-      <c r="L21" s="231" t="s">
-        <v>114</v>
-      </c>
-      <c r="M21" s="230"/>
-      <c r="N21" s="261">
+      <c r="K21" s="223"/>
+      <c r="L21" s="230" t="s">
+        <v>113</v>
+      </c>
+      <c r="M21" s="229"/>
+      <c r="N21" s="260">
         <v>0.8</v>
       </c>
-      <c r="O21" s="261">
+      <c r="O21" s="260">
         <v>0.64</v>
       </c>
-      <c r="P21" s="261">
+      <c r="P21" s="260">
         <v>0.51200000000000001</v>
       </c>
-      <c r="Q21" s="261">
+      <c r="Q21" s="260">
         <v>0.40960000000000002</v>
       </c>
-      <c r="R21" s="261">
+      <c r="R21" s="260">
         <v>0.32768000000000003</v>
       </c>
-      <c r="S21" s="261">
+      <c r="S21" s="260">
         <v>0.26214399999999999</v>
       </c>
-      <c r="T21" s="279">
+      <c r="T21" s="278">
         <v>0.20971519999999999</v>
       </c>
-      <c r="U21" s="261">
+      <c r="U21" s="260">
         <v>0.16777216</v>
       </c>
-      <c r="V21" s="261">
+      <c r="V21" s="260">
         <v>0.13421772800000001</v>
       </c>
-      <c r="W21" s="261">
+      <c r="W21" s="260">
         <v>0.1073741824</v>
       </c>
-      <c r="X21" s="276"/>
+      <c r="X21" s="275"/>
     </row>
     <row r="22" spans="2:24">
       <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="255" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="242">
+        <v>0</v>
+      </c>
+      <c r="J22" s="249" t="s">
         <v>129</v>
       </c>
-      <c r="E22" s="256" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" s="243">
-        <v>0</v>
-      </c>
-      <c r="J22" s="250" t="s">
+      <c r="K22" s="249"/>
+      <c r="L22" s="248" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="249"/>
+      <c r="N22" s="257">
+        <v>0</v>
+      </c>
+      <c r="O22" s="257">
+        <v>0</v>
+      </c>
+      <c r="P22" s="257">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="257">
+        <v>0</v>
+      </c>
+      <c r="R22" s="257">
+        <v>0</v>
+      </c>
+      <c r="S22" s="257">
+        <v>0</v>
+      </c>
+      <c r="T22" s="265">
+        <v>20971520</v>
+      </c>
+      <c r="U22" s="257">
+        <v>0</v>
+      </c>
+      <c r="V22" s="257">
+        <v>0</v>
+      </c>
+      <c r="W22" s="257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24">
+      <c r="B23" s="218"/>
+      <c r="C23" t="s">
         <v>130</v>
-      </c>
-      <c r="K22" s="250"/>
-      <c r="L22" s="249" t="s">
-        <v>62</v>
-      </c>
-      <c r="M22" s="250"/>
-      <c r="N22" s="258">
-        <v>0</v>
-      </c>
-      <c r="O22" s="258">
-        <v>0</v>
-      </c>
-      <c r="P22" s="258">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="258">
-        <v>0</v>
-      </c>
-      <c r="R22" s="258">
-        <v>0</v>
-      </c>
-      <c r="S22" s="258">
-        <v>0</v>
-      </c>
-      <c r="T22" s="266">
-        <v>20971520</v>
-      </c>
-      <c r="U22" s="258">
-        <v>0</v>
-      </c>
-      <c r="V22" s="258">
-        <v>0</v>
-      </c>
-      <c r="W22" s="258">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:24">
-      <c r="B23" s="219"/>
-      <c r="C23" t="s">
-        <v>131</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
       </c>
-      <c r="G23" s="226">
+      <c r="G23" s="225">
         <v>0.25</v>
       </c>
-      <c r="J23" s="263" t="s">
+      <c r="J23" s="262" t="s">
+        <v>131</v>
+      </c>
+      <c r="K23" s="262"/>
+      <c r="L23" s="263" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="264">
+        <v>20971520</v>
+      </c>
+      <c r="N23" s="258"/>
+      <c r="O23" s="258"/>
+      <c r="P23" s="258"/>
+      <c r="Q23" s="258"/>
+      <c r="R23" s="258"/>
+      <c r="S23" s="258"/>
+      <c r="T23" s="258"/>
+      <c r="U23" s="258"/>
+      <c r="V23" s="258"/>
+      <c r="W23" s="258"/>
+      <c r="X23" s="218"/>
+    </row>
+    <row r="24" spans="2:24">
+      <c r="O24" s="258"/>
+      <c r="P24" s="258"/>
+      <c r="Q24" s="258"/>
+      <c r="R24" s="258"/>
+      <c r="S24" s="258"/>
+      <c r="T24" s="258"/>
+      <c r="U24" s="258"/>
+      <c r="V24" s="258"/>
+      <c r="W24" s="258"/>
+    </row>
+    <row r="25" spans="2:24">
+      <c r="C25" s="223"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="223"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="223"/>
+      <c r="H25" s="223"/>
+      <c r="I25" s="223"/>
+      <c r="J25" s="223"/>
+      <c r="K25" s="223"/>
+      <c r="L25" s="223"/>
+      <c r="M25" s="223"/>
+      <c r="N25" s="223"/>
+      <c r="O25" s="223"/>
+      <c r="P25" s="223"/>
+      <c r="Q25" s="223"/>
+      <c r="R25" s="223"/>
+      <c r="S25" s="223"/>
+      <c r="T25" s="223"/>
+      <c r="U25" s="223"/>
+      <c r="V25" s="223"/>
+      <c r="W25" s="223"/>
+    </row>
+    <row r="27" spans="2:24">
+      <c r="C27" s="239" t="s">
         <v>132</v>
       </c>
-      <c r="K23" s="263"/>
-      <c r="L23" s="264" t="s">
-        <v>62</v>
-      </c>
-      <c r="M23" s="265">
-        <v>20971520</v>
-      </c>
-      <c r="N23" s="259"/>
-      <c r="O23" s="259"/>
-      <c r="P23" s="259"/>
-      <c r="Q23" s="259"/>
-      <c r="R23" s="259"/>
-      <c r="S23" s="259"/>
-      <c r="T23" s="259"/>
-      <c r="U23" s="259"/>
-      <c r="V23" s="259"/>
-      <c r="W23" s="259"/>
-      <c r="X23" s="219"/>
-    </row>
-    <row r="24" spans="2:24">
-      <c r="O24" s="259"/>
-      <c r="P24" s="259"/>
-      <c r="Q24" s="259"/>
-      <c r="R24" s="259"/>
-      <c r="S24" s="259"/>
-      <c r="T24" s="259"/>
-      <c r="U24" s="259"/>
-      <c r="V24" s="259"/>
-      <c r="W24" s="259"/>
-    </row>
-    <row r="25" spans="2:24">
-      <c r="C25" s="224"/>
-      <c r="D25" s="224"/>
-      <c r="E25" s="224"/>
-      <c r="F25" s="224"/>
-      <c r="G25" s="224"/>
-      <c r="H25" s="224"/>
-      <c r="I25" s="224"/>
-      <c r="J25" s="224"/>
-      <c r="K25" s="224"/>
-      <c r="L25" s="224"/>
-      <c r="M25" s="224"/>
-      <c r="N25" s="224"/>
-      <c r="O25" s="224"/>
-      <c r="P25" s="224"/>
-      <c r="Q25" s="224"/>
-      <c r="R25" s="224"/>
-      <c r="S25" s="224"/>
-      <c r="T25" s="224"/>
-      <c r="U25" s="224"/>
-      <c r="V25" s="224"/>
-      <c r="W25" s="224"/>
-    </row>
-    <row r="27" spans="2:24">
-      <c r="C27" s="240" t="s">
+      <c r="J27" s="239" t="s">
         <v>133</v>
       </c>
-      <c r="J27" s="240" t="s">
-        <v>134</v>
-      </c>
-      <c r="K27" s="240"/>
-      <c r="L27" s="219"/>
+      <c r="K27" s="239"/>
+      <c r="L27" s="218"/>
     </row>
     <row r="28" spans="2:24">
       <c r="C28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
         <v>135</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" s="225">
+        <v>0.1</v>
+      </c>
+      <c r="J28" s="218" t="s">
         <v>136</v>
       </c>
-      <c r="G28" s="226">
-        <v>0.1</v>
-      </c>
-      <c r="J28" s="219" t="s">
-        <v>137</v>
-      </c>
-      <c r="K28" s="219"/>
-      <c r="L28" s="275" t="s">
-        <v>62</v>
-      </c>
-      <c r="M28" s="258">
-        <v>0</v>
-      </c>
-      <c r="N28" s="258">
-        <v>0</v>
-      </c>
-      <c r="O28" s="258">
-        <v>0</v>
-      </c>
-      <c r="P28" s="258">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="258">
-        <v>0</v>
-      </c>
-      <c r="R28" s="258">
-        <v>0</v>
-      </c>
-      <c r="S28" s="266">
-        <v>0</v>
-      </c>
-      <c r="T28" s="258">
+      <c r="K28" s="218"/>
+      <c r="L28" s="274" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="257">
+        <v>0</v>
+      </c>
+      <c r="N28" s="257">
+        <v>0</v>
+      </c>
+      <c r="O28" s="257">
+        <v>0</v>
+      </c>
+      <c r="P28" s="257">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="257">
+        <v>0</v>
+      </c>
+      <c r="R28" s="257">
+        <v>0</v>
+      </c>
+      <c r="S28" s="265">
+        <v>0</v>
+      </c>
+      <c r="T28" s="257">
         <v>100000000</v>
       </c>
-      <c r="U28" s="258">
-        <v>0</v>
-      </c>
-      <c r="V28" s="258">
-        <v>0</v>
-      </c>
-      <c r="W28" s="258">
+      <c r="U28" s="257">
+        <v>0</v>
+      </c>
+      <c r="V28" s="257">
+        <v>0</v>
+      </c>
+      <c r="W28" s="257">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:24">
       <c r="C29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" s="273">
+        <v>0</v>
+      </c>
+      <c r="J29" s="218" t="s">
         <v>138</v>
       </c>
-      <c r="E29" t="s">
-        <v>136</v>
-      </c>
-      <c r="G29" s="274">
-        <v>0</v>
-      </c>
-      <c r="J29" s="219" t="s">
-        <v>139</v>
-      </c>
-      <c r="K29" s="219"/>
-      <c r="L29" s="219" t="s">
+      <c r="K29" s="218"/>
+      <c r="L29" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="271">
+      <c r="M29" s="270">
         <v>0.1</v>
       </c>
-      <c r="N29" s="271">
+      <c r="N29" s="270">
         <v>0.1</v>
       </c>
-      <c r="O29" s="271">
+      <c r="O29" s="270">
         <v>0.1</v>
       </c>
-      <c r="P29" s="271">
+      <c r="P29" s="270">
         <v>0.1</v>
       </c>
-      <c r="Q29" s="272">
+      <c r="Q29" s="271">
         <v>0.1</v>
       </c>
-      <c r="R29" s="271">
+      <c r="R29" s="270">
         <v>0.1</v>
       </c>
-      <c r="S29" s="271">
+      <c r="S29" s="270">
         <v>0.1</v>
       </c>
-      <c r="T29" s="271">
+      <c r="T29" s="270">
         <v>0.1</v>
       </c>
-      <c r="U29" s="271">
-        <v>0</v>
-      </c>
-      <c r="V29" s="271">
-        <v>0</v>
-      </c>
-      <c r="W29" s="271">
+      <c r="U29" s="270">
+        <v>0</v>
+      </c>
+      <c r="V29" s="270">
+        <v>0</v>
+      </c>
+      <c r="W29" s="270">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:24">
       <c r="C30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" s="225">
+        <v>0.1</v>
+      </c>
+      <c r="M30" s="252"/>
+      <c r="N30" s="252"/>
+      <c r="O30" s="252"/>
+      <c r="P30" s="252"/>
+      <c r="Q30" s="252"/>
+      <c r="R30" s="252"/>
+      <c r="S30" s="252"/>
+      <c r="T30" s="252"/>
+      <c r="U30" s="252"/>
+      <c r="V30" s="252"/>
+      <c r="W30" s="252"/>
+    </row>
+    <row r="31" spans="2:24">
+      <c r="J31" s="218" t="s">
         <v>140</v>
       </c>
-      <c r="E30" t="s">
-        <v>136</v>
-      </c>
-      <c r="G30" s="226">
-        <v>0.1</v>
-      </c>
-      <c r="M30" s="253"/>
-      <c r="N30" s="253"/>
-      <c r="O30" s="253"/>
-      <c r="P30" s="253"/>
-      <c r="Q30" s="253"/>
-      <c r="R30" s="253"/>
-      <c r="S30" s="253"/>
-      <c r="T30" s="253"/>
-      <c r="U30" s="253"/>
-      <c r="V30" s="253"/>
-      <c r="W30" s="253"/>
-    </row>
-    <row r="31" spans="2:24">
-      <c r="J31" s="219" t="s">
-        <v>141</v>
-      </c>
-      <c r="K31" s="219"/>
-      <c r="M31" s="253"/>
-      <c r="N31" s="253"/>
-      <c r="O31" s="253"/>
-      <c r="P31" s="253"/>
-      <c r="Q31" s="253"/>
-      <c r="R31" s="253"/>
-      <c r="S31" s="253"/>
-      <c r="T31" s="253"/>
-      <c r="U31" s="253"/>
-      <c r="V31" s="253"/>
-      <c r="W31" s="253"/>
+      <c r="K31" s="218"/>
+      <c r="M31" s="252"/>
+      <c r="N31" s="252"/>
+      <c r="O31" s="252"/>
+      <c r="P31" s="252"/>
+      <c r="Q31" s="252"/>
+      <c r="R31" s="252"/>
+      <c r="S31" s="252"/>
+      <c r="T31" s="252"/>
+      <c r="U31" s="252"/>
+      <c r="V31" s="252"/>
+      <c r="W31" s="252"/>
     </row>
     <row r="32" spans="2:24">
       <c r="J32" t="s">
-        <v>66</v>
-      </c>
-      <c r="L32" s="247" t="s">
-        <v>62</v>
-      </c>
-      <c r="M32" s="258">
+        <v>65</v>
+      </c>
+      <c r="L32" s="246" t="s">
+        <v>61</v>
+      </c>
+      <c r="M32" s="257">
         <v>-2097152</v>
       </c>
-      <c r="N32" s="258"/>
-      <c r="O32" s="258"/>
-      <c r="P32" s="258"/>
-      <c r="Q32" s="258"/>
-      <c r="R32" s="258"/>
-      <c r="S32" s="266"/>
-      <c r="T32" s="258"/>
-      <c r="U32" s="258"/>
-      <c r="V32" s="258"/>
-      <c r="W32" s="258"/>
+      <c r="N32" s="257"/>
+      <c r="O32" s="257"/>
+      <c r="P32" s="257"/>
+      <c r="Q32" s="257"/>
+      <c r="R32" s="257"/>
+      <c r="S32" s="265"/>
+      <c r="T32" s="257"/>
+      <c r="U32" s="257"/>
+      <c r="V32" s="257"/>
+      <c r="W32" s="257"/>
     </row>
     <row r="33" spans="2:24">
       <c r="J33" t="s">
+        <v>141</v>
+      </c>
+      <c r="L33" s="246" t="s">
+        <v>61</v>
+      </c>
+      <c r="M33" s="257">
+        <v>0</v>
+      </c>
+      <c r="N33" s="257">
+        <v>0</v>
+      </c>
+      <c r="O33" s="257">
+        <v>0</v>
+      </c>
+      <c r="P33" s="257">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="257">
+        <v>0</v>
+      </c>
+      <c r="R33" s="257">
+        <v>0</v>
+      </c>
+      <c r="S33" s="265">
+        <v>0</v>
+      </c>
+      <c r="T33" s="257">
+        <v>10000000</v>
+      </c>
+      <c r="U33" s="257">
+        <v>0</v>
+      </c>
+      <c r="V33" s="257">
+        <v>0</v>
+      </c>
+      <c r="W33" s="257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24">
+      <c r="J34" s="241" t="s">
+        <v>140</v>
+      </c>
+      <c r="K34" s="241"/>
+      <c r="L34" s="254" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="268">
+        <v>-2097152</v>
+      </c>
+      <c r="N34" s="268">
+        <v>0</v>
+      </c>
+      <c r="O34" s="268">
+        <v>0</v>
+      </c>
+      <c r="P34" s="268">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="268">
+        <v>0</v>
+      </c>
+      <c r="R34" s="268">
+        <v>0</v>
+      </c>
+      <c r="S34" s="269">
+        <v>0</v>
+      </c>
+      <c r="T34" s="268">
+        <v>10000000</v>
+      </c>
+      <c r="U34" s="268">
+        <v>0</v>
+      </c>
+      <c r="V34" s="268">
+        <v>0</v>
+      </c>
+      <c r="W34" s="268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24">
+      <c r="J35" s="279" t="s">
         <v>142</v>
       </c>
-      <c r="L33" s="247" t="s">
-        <v>62</v>
-      </c>
-      <c r="M33" s="258">
-        <v>0</v>
-      </c>
-      <c r="N33" s="258">
-        <v>0</v>
-      </c>
-      <c r="O33" s="258">
-        <v>0</v>
-      </c>
-      <c r="P33" s="258">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="258">
-        <v>0</v>
-      </c>
-      <c r="R33" s="258">
-        <v>0</v>
-      </c>
-      <c r="S33" s="266">
-        <v>0</v>
-      </c>
-      <c r="T33" s="258">
-        <v>10000000</v>
-      </c>
-      <c r="U33" s="258">
-        <v>0</v>
-      </c>
-      <c r="V33" s="258">
-        <v>0</v>
-      </c>
-      <c r="W33" s="258">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24">
-      <c r="J34" s="242" t="s">
-        <v>141</v>
-      </c>
-      <c r="K34" s="242"/>
-      <c r="L34" s="255" t="s">
-        <v>62</v>
-      </c>
-      <c r="M34" s="269">
-        <v>-2097152</v>
-      </c>
-      <c r="N34" s="269">
-        <v>0</v>
-      </c>
-      <c r="O34" s="269">
-        <v>0</v>
-      </c>
-      <c r="P34" s="269">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="269">
-        <v>0</v>
-      </c>
-      <c r="R34" s="269">
-        <v>0</v>
-      </c>
-      <c r="S34" s="270">
-        <v>0</v>
-      </c>
-      <c r="T34" s="269">
-        <v>10000000</v>
-      </c>
-      <c r="U34" s="269">
-        <v>0</v>
-      </c>
-      <c r="V34" s="269">
-        <v>0</v>
-      </c>
-      <c r="W34" s="269">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:24">
-      <c r="J35" s="280" t="s">
+      <c r="K35" s="279"/>
+      <c r="L35" s="279" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="280">
+        <v>0.24999999999999978</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24">
+      <c r="J36" s="218" t="s">
         <v>143</v>
       </c>
-      <c r="K35" s="280"/>
-      <c r="L35" s="280" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="281">
-        <v>0.24999999999999978</v>
-      </c>
-    </row>
-    <row r="36" spans="2:24">
-      <c r="J36" s="219" t="s">
+      <c r="L36" t="s">
         <v>144</v>
       </c>
-      <c r="L36" t="s">
-        <v>145</v>
-      </c>
-      <c r="M36" s="282">
+      <c r="M36" s="281">
         <v>4.76837158203125</v>
       </c>
     </row>
     <row r="37" spans="2:24">
-      <c r="B37" s="224"/>
-      <c r="C37" s="224"/>
-      <c r="D37" s="224"/>
-      <c r="E37" s="224"/>
-      <c r="F37" s="224"/>
-      <c r="G37" s="224"/>
-      <c r="H37" s="224"/>
-      <c r="I37" s="224"/>
-      <c r="J37" s="224"/>
-      <c r="K37" s="224"/>
-      <c r="L37" s="224"/>
-      <c r="M37" s="224"/>
-      <c r="N37" s="224"/>
-      <c r="O37" s="224"/>
-      <c r="P37" s="224"/>
-      <c r="Q37" s="224"/>
-      <c r="R37" s="224"/>
-      <c r="S37" s="224"/>
-      <c r="T37" s="224"/>
-      <c r="U37" s="224"/>
-      <c r="V37" s="224"/>
-      <c r="W37" s="224"/>
-      <c r="X37" s="224"/>
+      <c r="B37" s="223"/>
+      <c r="C37" s="223"/>
+      <c r="D37" s="223"/>
+      <c r="E37" s="223"/>
+      <c r="F37" s="223"/>
+      <c r="G37" s="223"/>
+      <c r="H37" s="223"/>
+      <c r="I37" s="223"/>
+      <c r="J37" s="223"/>
+      <c r="K37" s="223"/>
+      <c r="L37" s="223"/>
+      <c r="M37" s="223"/>
+      <c r="N37" s="223"/>
+      <c r="O37" s="223"/>
+      <c r="P37" s="223"/>
+      <c r="Q37" s="223"/>
+      <c r="R37" s="223"/>
+      <c r="S37" s="223"/>
+      <c r="T37" s="223"/>
+      <c r="U37" s="223"/>
+      <c r="V37" s="223"/>
+      <c r="W37" s="223"/>
+      <c r="X37" s="223"/>
     </row>
     <row r="38" spans="2:24">
-      <c r="C38" s="220" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="220"/>
+      <c r="C38" s="219" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="219"/>
     </row>
     <row r="39" spans="2:24" ht="15.75">
-      <c r="C39" s="292" t="s">
-        <v>147</v>
-      </c>
-      <c r="D39" s="222"/>
+      <c r="C39" s="283" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="221"/>
     </row>
     <row r="42" spans="2:24">
-      <c r="H42" s="219"/>
-      <c r="J42" s="219"/>
-      <c r="K42" s="219"/>
-      <c r="L42" s="219"/>
+      <c r="H42" s="218"/>
+      <c r="J42" s="218"/>
+      <c r="K42" s="218"/>
+      <c r="L42" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/templates/finance/wacc-calculator.xlsx
+++ b/templates/finance/wacc-calculator.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50B7E02-C306-4C56-99BA-A9F51AA72C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="210" windowWidth="22695" windowHeight="12375" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5F1ED4BD-F4B9-457B-9C48-4FFC768BA210}"/>
   </bookViews>
   <sheets>
     <sheet name="WACC" sheetId="1" r:id="rId1"/>
@@ -2071,6 +2071,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2094,9 +2097,6 @@
     </xf>
     <xf numFmtId="0" fontId="64" fillId="59" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -3861,14 +3861,14 @@
       <c r="B14" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="285" t="s">
+      <c r="C14" s="286" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="285"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="285"/>
-      <c r="G14" s="285"/>
-      <c r="H14" s="285"/>
+      <c r="D14" s="286"/>
+      <c r="E14" s="286"/>
+      <c r="F14" s="286"/>
+      <c r="G14" s="286"/>
+      <c r="H14" s="286"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -3902,7 +3902,7 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="2:21">
-      <c r="B16" s="284" t="s">
+      <c r="B16" s="285" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="58">
@@ -3937,7 +3937,7 @@
       <c r="U16"/>
     </row>
     <row r="17" spans="2:21">
-      <c r="B17" s="284"/>
+      <c r="B17" s="285"/>
       <c r="C17" s="58">
         <f>+C16+5%</f>
         <v>0.1</v>
@@ -3983,7 +3983,7 @@
       <c r="U17"/>
     </row>
     <row r="18" spans="2:21">
-      <c r="B18" s="284"/>
+      <c r="B18" s="285"/>
       <c r="C18" s="58">
         <f t="shared" ref="C18:C26" si="1">+C17+10%</f>
         <v>0.2</v>
@@ -4031,7 +4031,7 @@
       <c r="U18"/>
     </row>
     <row r="19" spans="2:21">
-      <c r="B19" s="284"/>
+      <c r="B19" s="285"/>
       <c r="C19" s="58">
         <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
@@ -4079,7 +4079,7 @@
       <c r="U19"/>
     </row>
     <row r="20" spans="2:21">
-      <c r="B20" s="284"/>
+      <c r="B20" s="285"/>
       <c r="C20" s="58">
         <f t="shared" si="1"/>
         <v>0.4</v>
@@ -4127,7 +4127,7 @@
       <c r="U20"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="B21" s="284"/>
+      <c r="B21" s="285"/>
       <c r="C21" s="58">
         <f t="shared" si="1"/>
         <v>0.5</v>
@@ -4175,7 +4175,7 @@
       <c r="U21"/>
     </row>
     <row r="22" spans="2:21">
-      <c r="B22" s="284"/>
+      <c r="B22" s="285"/>
       <c r="C22" s="58">
         <f t="shared" si="1"/>
         <v>0.6</v>
@@ -4223,7 +4223,7 @@
       <c r="U22"/>
     </row>
     <row r="23" spans="2:21">
-      <c r="B23" s="284"/>
+      <c r="B23" s="285"/>
       <c r="C23" s="58">
         <f t="shared" si="1"/>
         <v>0.7</v>
@@ -4269,7 +4269,7 @@
       <c r="U23"/>
     </row>
     <row r="24" spans="2:21">
-      <c r="B24" s="284"/>
+      <c r="B24" s="285"/>
       <c r="C24" s="58">
         <f t="shared" si="1"/>
         <v>0.79999999999999993</v>
@@ -4294,7 +4294,7 @@
       <c r="U24"/>
     </row>
     <row r="25" spans="2:21">
-      <c r="B25" s="284"/>
+      <c r="B25" s="285"/>
       <c r="C25" s="58">
         <f t="shared" si="1"/>
         <v>0.89999999999999991</v>
@@ -4326,7 +4326,7 @@
       <c r="U25"/>
     </row>
     <row r="26" spans="2:21">
-      <c r="B26" s="284"/>
+      <c r="B26" s="285"/>
       <c r="C26" s="58">
         <f t="shared" si="1"/>
         <v>0.99999999999999989</v>
@@ -4571,7 +4571,7 @@
       <c r="Z2" s="112"/>
       <c r="AA2" s="112"/>
       <c r="AB2" s="112"/>
-      <c r="AC2" s="292" t="s">
+      <c r="AC2" s="284" t="s">
         <v>146</v>
       </c>
       <c r="AD2" s="112"/>
@@ -4806,11 +4806,11 @@
       <c r="F9" s="116"/>
       <c r="G9" s="116"/>
       <c r="H9" s="115"/>
-      <c r="I9" s="286">
+      <c r="I9" s="287">
         <v>4.2087912087912089</v>
       </c>
-      <c r="J9" s="287"/>
-      <c r="K9" s="288"/>
+      <c r="J9" s="288"/>
+      <c r="K9" s="289"/>
       <c r="L9" s="116"/>
       <c r="M9" s="116"/>
       <c r="N9" s="116"/>
@@ -4845,9 +4845,9 @@
       <c r="F10" s="116"/>
       <c r="G10" s="116"/>
       <c r="H10" s="115"/>
-      <c r="I10" s="286"/>
-      <c r="J10" s="287"/>
-      <c r="K10" s="288"/>
+      <c r="I10" s="287"/>
+      <c r="J10" s="288"/>
+      <c r="K10" s="289"/>
       <c r="L10" s="116"/>
       <c r="M10" s="116"/>
       <c r="N10" s="116"/>
@@ -4878,9 +4878,9 @@
       <c r="F11" s="116"/>
       <c r="G11" s="116"/>
       <c r="H11" s="115"/>
-      <c r="I11" s="286"/>
-      <c r="J11" s="287"/>
-      <c r="K11" s="288"/>
+      <c r="I11" s="287"/>
+      <c r="J11" s="288"/>
+      <c r="K11" s="289"/>
       <c r="L11" s="116"/>
       <c r="M11" s="116"/>
       <c r="N11" s="116"/>
@@ -4911,9 +4911,9 @@
       <c r="F12" s="116"/>
       <c r="G12" s="116"/>
       <c r="H12" s="115"/>
-      <c r="I12" s="286"/>
-      <c r="J12" s="287"/>
-      <c r="K12" s="288"/>
+      <c r="I12" s="287"/>
+      <c r="J12" s="288"/>
+      <c r="K12" s="289"/>
       <c r="L12" s="116"/>
       <c r="M12" s="116"/>
       <c r="N12" s="116"/>
@@ -4946,9 +4946,9 @@
       <c r="F13" s="116"/>
       <c r="G13" s="116"/>
       <c r="H13" s="115"/>
-      <c r="I13" s="286"/>
-      <c r="J13" s="287"/>
-      <c r="K13" s="288"/>
+      <c r="I13" s="287"/>
+      <c r="J13" s="288"/>
+      <c r="K13" s="289"/>
       <c r="L13" s="116"/>
       <c r="M13" s="116"/>
       <c r="N13" s="116"/>
@@ -4983,9 +4983,9 @@
       <c r="F14" s="116"/>
       <c r="G14" s="116"/>
       <c r="H14" s="115"/>
-      <c r="I14" s="286"/>
-      <c r="J14" s="287"/>
-      <c r="K14" s="288"/>
+      <c r="I14" s="287"/>
+      <c r="J14" s="288"/>
+      <c r="K14" s="289"/>
       <c r="L14" s="116"/>
       <c r="M14" s="116"/>
       <c r="N14" s="116"/>
@@ -5016,9 +5016,9 @@
       <c r="F15" s="116"/>
       <c r="G15" s="116"/>
       <c r="H15" s="115"/>
-      <c r="I15" s="286"/>
-      <c r="J15" s="287"/>
-      <c r="K15" s="288"/>
+      <c r="I15" s="287"/>
+      <c r="J15" s="288"/>
+      <c r="K15" s="289"/>
       <c r="L15" s="116"/>
       <c r="M15" s="116"/>
       <c r="N15" s="116"/>
@@ -5053,9 +5053,9 @@
       <c r="F16" s="116"/>
       <c r="G16" s="120"/>
       <c r="H16" s="115"/>
-      <c r="I16" s="286"/>
-      <c r="J16" s="287"/>
-      <c r="K16" s="288"/>
+      <c r="I16" s="287"/>
+      <c r="J16" s="288"/>
+      <c r="K16" s="289"/>
       <c r="L16" s="116"/>
       <c r="M16" s="116"/>
       <c r="N16" s="116"/>
@@ -5092,9 +5092,9 @@
         <v>100000</v>
       </c>
       <c r="H17" s="115"/>
-      <c r="I17" s="286"/>
-      <c r="J17" s="287"/>
-      <c r="K17" s="288"/>
+      <c r="I17" s="287"/>
+      <c r="J17" s="288"/>
+      <c r="K17" s="289"/>
       <c r="L17" s="116"/>
       <c r="M17" s="116"/>
       <c r="N17" s="116"/>
@@ -5131,9 +5131,9 @@
         <v>20000</v>
       </c>
       <c r="H18" s="115"/>
-      <c r="I18" s="286"/>
-      <c r="J18" s="287"/>
-      <c r="K18" s="288"/>
+      <c r="I18" s="287"/>
+      <c r="J18" s="288"/>
+      <c r="K18" s="289"/>
       <c r="L18" s="116"/>
       <c r="M18" s="116"/>
       <c r="N18" s="116"/>
@@ -5168,9 +5168,9 @@
         <v>0</v>
       </c>
       <c r="H19" s="115"/>
-      <c r="I19" s="286"/>
-      <c r="J19" s="287"/>
-      <c r="K19" s="288"/>
+      <c r="I19" s="287"/>
+      <c r="J19" s="288"/>
+      <c r="K19" s="289"/>
       <c r="L19" s="116"/>
       <c r="M19" s="116"/>
       <c r="N19" s="116"/>
@@ -5205,9 +5205,9 @@
         <v>0</v>
       </c>
       <c r="H20" s="115"/>
-      <c r="I20" s="286"/>
-      <c r="J20" s="287"/>
-      <c r="K20" s="288"/>
+      <c r="I20" s="287"/>
+      <c r="J20" s="288"/>
+      <c r="K20" s="289"/>
       <c r="L20" s="116"/>
       <c r="M20" s="116"/>
       <c r="N20" s="116"/>
@@ -7806,12 +7806,12 @@
       <c r="C8" s="272" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="289" t="s">
+      <c r="D8" s="290" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="290"/>
-      <c r="F8" s="290"/>
-      <c r="G8" s="291"/>
+      <c r="E8" s="291"/>
+      <c r="F8" s="291"/>
+      <c r="G8" s="292"/>
       <c r="H8" s="272"/>
       <c r="I8" s="224"/>
       <c r="J8" s="224" t="s">
